--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -6,8 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VERİLER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="BIST" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ÖZET" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VERİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BIST" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -813,6 +814,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30.06.2026 10:21:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Veri Kaynağı</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tradingview</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KAPALI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Yeni AL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Güncellenen Satır</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Yeni Kapanan İşlem</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Toplam İşlem</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Açık İşlem</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STOP İşlem</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KAR STOP İşlem</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Script Versiyon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>tarama.py 2026-06-08 ESv4-revised</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -1006,7 +1155,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.54</v>
+        <v>23.74</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1040,7 +1189,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-14.9</v>
+        <v>-14.17</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1168,7 +1317,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>183</v>
+        <v>183.4</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1202,7 +1351,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-4.14</v>
+        <v>-3.93</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1249,7 +1398,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.47</v>
+        <v>13.24</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1328,7 +1477,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1407,7 +1556,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>70.5</v>
+        <v>72.95</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1441,7 +1590,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-9.85</v>
+        <v>-6.71</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1488,7 +1637,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>24.1</v>
+        <v>23.92</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1501,13 +1650,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>24.06</v>
+        <v>23.88</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-10.42</v>
+        <v>-11.09</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1522,7 +1671,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-5.56</v>
+        <v>-6.27</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1569,7 +1718,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>43.22</v>
+        <v>43.14</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1603,7 +1752,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-6.65</v>
+        <v>-6.83</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1650,7 +1799,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>40.26</v>
+        <v>40.58</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1684,7 +1833,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-8.5</v>
+        <v>-7.77</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1812,7 +1961,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>115</v>
+        <v>115.2</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1825,13 +1974,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-9.73</v>
+        <v>-10.52</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1846,7 +1995,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-4.96</v>
+        <v>-4.79</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -1893,7 +2042,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>150.7</v>
+        <v>151</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -1903,13 +2052,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>150.7</v>
+        <v>155</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>17.28</v>
+        <v>20.62</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -1927,7 +2076,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>23.42</v>
+        <v>23.67</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -1974,7 +2123,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>20.08</v>
+        <v>19.73</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2008,7 +2157,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>15.07</v>
+        <v>13.07</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2055,7 +2204,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>70.55</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2089,7 +2238,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>9.460000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2128,14 +2277,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>136.8</v>
+        <v>138.9</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>10.32</v>
+        <v>12.02</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>140.9</v>
@@ -2159,7 +2308,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>13.41</v>
+        <v>15.11</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2207,7 +2356,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2241,7 +2390,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-11.81</v>
+        <v>-11.92</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2288,7 +2437,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2322,7 +2471,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-4.75</v>
+        <v>-4.13</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2361,14 +2510,14 @@
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="5" t="n">
-        <v>19.25</v>
+        <v>19.37</v>
       </c>
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n">
-        <v>-2.68</v>
+        <v>-2.07</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>20.44</v>
@@ -2392,7 +2541,7 @@
         <v>-0.4</v>
       </c>
       <c r="W19" s="5" t="n">
-        <v>-2.28</v>
+        <v>-1.67</v>
       </c>
       <c r="X19" s="5" t="n"/>
       <c r="Y19" s="6" t="n"/>
@@ -2440,7 +2589,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.34</v>
+        <v>7.27</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2474,7 +2623,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>4.41</v>
+        <v>3.41</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2513,14 +2662,14 @@
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="5" t="n">
-        <v>5.33</v>
+        <v>5.18</v>
       </c>
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n">
-        <v>3.5</v>
+        <v>0.58</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>5.5</v>
@@ -2544,7 +2693,7 @@
         <v>0.1</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>3.4</v>
+        <v>0.48</v>
       </c>
       <c r="X21" s="5" t="n"/>
       <c r="Y21" s="6" t="n"/>
@@ -2592,7 +2741,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2626,7 +2775,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-3.54</v>
+        <v>-3.03</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2665,26 +2814,26 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>29.38</v>
+        <v>29.08</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>-2.07</v>
+        <v>-3.07</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>30.2</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>29.24</v>
+        <v>29.08</v>
       </c>
       <c r="R23" s="5" t="n">
         <v>0.67</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>-2.53</v>
+        <v>-3.07</v>
       </c>
       <c r="T23" s="5" t="n">
         <v>14274.02</v>
@@ -2696,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-2.07</v>
+        <v>-3.07</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2732,25 +2881,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5365</v>
+        <v>5425</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>5680</v>
+        <v>5425</v>
       </c>
       <c r="Q24" t="n">
-        <v>5260</v>
+        <v>5310</v>
       </c>
       <c r="R24" t="n">
-        <v>5.87</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.96</v>
+        <v>-1.03</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2762,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2801,25 +2950,25 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>20.16</v>
+        <v>20</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.62</v>
+        <v>19.96</v>
       </c>
       <c r="R25" t="n">
-        <v>7.14</v>
+        <v>2.18</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.68</v>
+        <v>-0.99</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -2831,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2870,25 +3019,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>99.05</v>
+        <v>99.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>99.40000000000001</v>
+        <v>99.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>97.45</v>
+        <v>99</v>
       </c>
       <c r="R26" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.62</v>
+        <v>-0.05</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -2900,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2917,7 +3066,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -106,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,6 +128,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -841,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.06.2026 10:21:43</t>
+          <t>30.06.2026 20:27:05</t>
         </is>
       </c>
     </row>
@@ -876,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -906,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -916,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -962,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1155,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.74</v>
+        <v>23.96</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1168,13 +1170,13 @@
         <v>29.8</v>
       </c>
       <c r="Q2" s="16" t="n">
-        <v>23.5</v>
+        <v>23.48</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>2.76</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>-18.97</v>
+        <v>-19.03</v>
       </c>
       <c r="T2" s="8" t="n">
         <v>13744.64</v>
@@ -1189,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-14.17</v>
+        <v>-13.38</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1236,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47.34</v>
+        <v>47.18</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1249,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>47.22</v>
+        <v>47.1</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-24.16</v>
+        <v>-24.35</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1270,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-19.98</v>
+        <v>-20.25</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1317,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>183.4</v>
+        <v>179.3</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1330,13 +1332,13 @@
         <v>209.1</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>182.5</v>
+        <v>178.7</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>4.08</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-9.16</v>
+        <v>-11.05</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>13744.64</v>
@@ -1351,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.93</v>
+        <v>-6.08</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1398,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.24</v>
+        <v>14.2</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1477,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.95</v>
+        <v>6.48</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1556,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>72.95</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1590,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-6.71</v>
+        <v>-7.42</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1637,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.92</v>
+        <v>23.82</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1650,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>23.88</v>
+        <v>23.78</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-11.09</v>
+        <v>-11.47</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1671,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-6.27</v>
+        <v>-6.66</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1718,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>43.14</v>
+        <v>42.94</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1731,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>42.94</v>
+        <v>42.72</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-11.9</v>
+        <v>-12.35</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1752,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-6.83</v>
+        <v>-7.26</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1799,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>40.58</v>
+        <v>38.84</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1812,13 +1814,13 @@
         <v>46.74</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>39.44</v>
+        <v>38.8</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.91</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>-14.85</v>
+        <v>-16.23</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>14493.09</v>
@@ -1833,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-7.77</v>
+        <v>-11.73</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1880,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1914,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>0.84</v>
+        <v>1.57</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1961,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>115.2</v>
+        <v>111.2</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1974,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>114</v>
+        <v>110.1</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-10.52</v>
+        <v>-13.58</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1995,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-4.79</v>
+        <v>-8.1</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2042,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2052,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>155</v>
+        <v>159.1</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>20.62</v>
+        <v>23.81</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2076,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>23.67</v>
+        <v>27.76</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2123,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>19.73</v>
+        <v>18.37</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2157,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>13.07</v>
+        <v>5.27</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2204,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2238,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>6.05</v>
+        <v>12.02</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2277,23 +2279,23 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>138.9</v>
+        <v>138.6</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>12.02</v>
+        <v>11.77</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>8</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>140.9</v>
+        <v>141.3</v>
       </c>
       <c r="Q16" s="8" t="n">
         <v>121.4</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>13.63</v>
+        <v>13.95</v>
       </c>
       <c r="S16" s="8" t="n">
         <v>-2.1</v>
@@ -2308,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>15.11</v>
+        <v>14.86</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2356,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>85</v>
+        <v>89.7</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2390,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-11.92</v>
+        <v>-7.05</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2437,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.64</v>
+        <v>4.59</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2450,13 +2452,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-9.43</v>
+        <v>-10.02</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2471,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-4.13</v>
+        <v>-5.17</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2510,11 +2512,11 @@
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="5" t="n">
-        <v>19.37</v>
+        <v>19.05</v>
       </c>
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n">
-        <v>-2.07</v>
+        <v>-3.69</v>
       </c>
       <c r="O19" s="5" t="n">
         <v>6</v>
@@ -2541,7 +2543,7 @@
         <v>-0.4</v>
       </c>
       <c r="W19" s="5" t="n">
-        <v>-1.67</v>
+        <v>-3.29</v>
       </c>
       <c r="X19" s="5" t="n"/>
       <c r="Y19" s="6" t="n"/>
@@ -2589,7 +2591,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.27</v>
+        <v>6.86</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2602,13 +2604,13 @@
         <v>7.64</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>3.24</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-5.41</v>
+        <v>-7.3</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2623,7 +2625,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>3.41</v>
+        <v>-2.42</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2662,11 +2664,11 @@
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="5" t="n">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n">
-        <v>0.58</v>
+        <v>-0.19</v>
       </c>
       <c r="O21" s="5" t="n">
         <v>5</v>
@@ -2693,7 +2695,7 @@
         <v>0.1</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>0.48</v>
+        <v>-0.29</v>
       </c>
       <c r="X21" s="5" t="n"/>
       <c r="Y21" s="6" t="n"/>
@@ -2741,7 +2743,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2754,13 +2756,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-6.83</v>
+        <v>-7.8</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2775,7 +2777,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-3.03</v>
+        <v>-4.55</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2814,26 +2816,26 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>29.08</v>
+        <v>30.54</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>-3.07</v>
+        <v>1.8</v>
       </c>
       <c r="O23" s="5" t="n">
         <v>4</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>30.2</v>
+        <v>32.3</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>29.08</v>
+        <v>29.04</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>0.67</v>
+        <v>7.67</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>-3.07</v>
+        <v>-3.2</v>
       </c>
       <c r="T23" s="5" t="n">
         <v>14274.02</v>
@@ -2845,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-3.07</v>
+        <v>1.8</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2881,25 +2883,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5425</v>
+        <v>5377.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.12</v>
+        <v>0.23</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>5425</v>
+        <v>5492.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>5310</v>
+        <v>5170</v>
       </c>
       <c r="R24" t="n">
-        <v>1.12</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.03</v>
+        <v>-3.63</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2911,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>0.23</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2950,25 +2952,25 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>21.26</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.79</v>
+        <v>5.46</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>20.6</v>
+        <v>21.44</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.96</v>
+        <v>19.39</v>
       </c>
       <c r="R25" t="n">
-        <v>2.18</v>
+        <v>6.35</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.99</v>
+        <v>-3.82</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -2980,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.79</v>
+        <v>5.46</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -3019,25 +3021,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>99.55</v>
+        <v>100.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>99</v>
+        <v>98.95</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3049,9 +3051,69 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="Y26" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ISLEM-000026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="G27" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.06.2026 20:27:05</t>
+          <t>01.07.2026 22:07:08</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.96</v>
+        <v>23.44</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1170,13 +1170,13 @@
         <v>29.8</v>
       </c>
       <c r="Q2" s="16" t="n">
-        <v>23.48</v>
+        <v>23.36</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>2.76</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>-19.03</v>
+        <v>-19.45</v>
       </c>
       <c r="T2" s="8" t="n">
         <v>13744.64</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-13.38</v>
+        <v>-15.26</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47.18</v>
+        <v>47.64</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>47.1</v>
+        <v>46.24</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-24.35</v>
+        <v>-25.73</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-20.25</v>
+        <v>-19.47</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>179.3</v>
+        <v>184.6</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-6.08</v>
+        <v>-3.3</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14.2</v>
+        <v>14.02</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.48</v>
+        <v>6.91</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>72.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-7.42</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.82</v>
+        <v>23.4</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>23.78</v>
+        <v>23.06</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-11.47</v>
+        <v>-14.15</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-6.66</v>
+        <v>-8.31</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>42.94</v>
+        <v>44.2</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-7.26</v>
+        <v>-4.54</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.84</v>
+        <v>39.2</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1814,13 +1814,13 @@
         <v>46.74</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>38.8</v>
+        <v>38.54</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.91</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>-16.23</v>
+        <v>-16.8</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>14493.09</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-11.73</v>
+        <v>-10.91</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.42</v>
+        <v>8.57</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>1.57</v>
+        <v>3.38</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>111.2</v>
+        <v>107.8</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>110.1</v>
+        <v>107.7</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-13.58</v>
+        <v>-15.46</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-8.1</v>
+        <v>-10.91</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>156</v>
+        <v>155.5</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>159.1</v>
+        <v>160.8</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>23.81</v>
+        <v>25.14</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>27.76</v>
+        <v>27.35</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>18.37</v>
+        <v>17.72</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2138,13 +2138,13 @@
         <v>20.32</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>17.02</v>
+        <v>17</v>
       </c>
       <c r="R14" s="8" t="n">
         <v>10.62</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>-7.35</v>
+        <v>-7.46</v>
       </c>
       <c r="T14" s="8" t="n">
         <v>14734.5</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>5.27</v>
+        <v>1.55</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>72.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>12.02</v>
+        <v>22.73</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,23 +2279,23 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>138.6</v>
+        <v>135.5</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>11.77</v>
+        <v>9.27</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>141.3</v>
+        <v>141.5</v>
       </c>
       <c r="Q16" s="8" t="n">
         <v>121.4</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>13.95</v>
+        <v>14.11</v>
       </c>
       <c r="S16" s="8" t="n">
         <v>-2.1</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>14.86</v>
+        <v>12.36</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>89.7</v>
+        <v>86.5</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-7.05</v>
+        <v>-10.36</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-5.17</v>
+        <v>-4.55</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2505,33 +2505,41 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="6" t="n"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="L19" s="5" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n">
-        <v>-3.69</v>
-      </c>
+        <v>18.25</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>20.44</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>18.81</v>
+        <v>18.12</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>3.34</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-4.9</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2543,9 +2551,11 @@
         <v>-0.4</v>
       </c>
       <c r="W19" s="5" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="X19" s="5" t="n"/>
+        <v>-4.61</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>-2.87</v>
+      </c>
       <c r="Y19" s="6" t="n"/>
     </row>
     <row r="20" ht="23.4" customHeight="1">
@@ -2591,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.86</v>
+        <v>6.99</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2604,13 +2614,13 @@
         <v>7.64</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.86</v>
+        <v>6.82</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>3.24</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-7.3</v>
+        <v>-7.84</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2625,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-2.42</v>
+        <v>-0.57</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2664,14 +2674,14 @@
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="5" t="n">
-        <v>5.14</v>
+        <v>5.27</v>
       </c>
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n">
-        <v>-0.19</v>
+        <v>2.33</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>5.5</v>
@@ -2695,7 +2705,7 @@
         <v>0.1</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>-0.29</v>
+        <v>2.23</v>
       </c>
       <c r="X21" s="5" t="n"/>
       <c r="Y21" s="6" t="n"/>
@@ -2756,13 +2766,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-7.8</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2816,14 +2826,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>30.54</v>
+        <v>30.32</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2847,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2883,22 +2893,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5377.5</v>
+        <v>5387.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>5492.5</v>
+        <v>5577.5</v>
       </c>
       <c r="Q24" t="n">
         <v>5170</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>3.96</v>
       </c>
       <c r="S24" t="n">
         <v>-3.63</v>
@@ -2913,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2952,22 +2962,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21.26</v>
+        <v>22.86</v>
       </c>
       <c r="N25" t="n">
-        <v>5.46</v>
+        <v>13.39</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>21.44</v>
+        <v>23.2</v>
       </c>
       <c r="Q25" t="n">
         <v>19.39</v>
       </c>
       <c r="R25" t="n">
-        <v>6.35</v>
+        <v>15.08</v>
       </c>
       <c r="S25" t="n">
         <v>-3.82</v>
@@ -2982,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>5.46</v>
+        <v>13.39</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -3021,25 +3031,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>99.45</v>
       </c>
       <c r="N26" t="n">
-        <v>0.96</v>
+        <v>0.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
         <v>100.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>98.95</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1</v>
+        <v>-0.45</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3051,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.96</v>
+        <v>0.4</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3090,30 +3100,99 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.04</v>
+        <v>20.86</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>21.04</v>
+        <v>21.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.04</v>
+        <v>20.66</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-1.81</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U27" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.86</v>
+      </c>
       <c r="Y27" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ISLEM-000027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TDGYO</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.07.2026 22:07:08</t>
+          <t>02.07.2026 22:42:39</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.44</v>
+        <v>24.26</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1170,13 +1170,13 @@
         <v>29.8</v>
       </c>
       <c r="Q2" s="16" t="n">
-        <v>23.36</v>
+        <v>22.54</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>2.76</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>-19.45</v>
+        <v>-22.28</v>
       </c>
       <c r="T2" s="8" t="n">
         <v>13744.64</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-15.26</v>
+        <v>-12.29</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47.64</v>
+        <v>47.3</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-19.47</v>
+        <v>-20.05</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>184.6</v>
+        <v>184.3</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.3</v>
+        <v>-3.46</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14.02</v>
+        <v>14</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.91</v>
+        <v>6.8</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>70.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-9.970000000000001</v>
+        <v>-10.74</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.4</v>
+        <v>23.28</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-8.31</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>44.2</v>
+        <v>45.7</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-4.54</v>
+        <v>-1.3</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>39.2</v>
+        <v>39.92</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-10.91</v>
+        <v>-9.27</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.57</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>3.38</v>
+        <v>3.86</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>107.8</v>
+        <v>108.2</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-10.91</v>
+        <v>-10.58</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>155.5</v>
+        <v>156.7</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>160.8</v>
+        <v>161.7</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>25.14</v>
+        <v>25.84</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>27.35</v>
+        <v>28.34</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>17.72</v>
+        <v>17.27</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>1.55</v>
+        <v>-1.03</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>79.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2216,13 +2216,13 @@
         <v>3</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>59.25</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>17.76</v>
+        <v>28.22</v>
       </c>
       <c r="S15" s="5" t="n">
         <v>-12.68</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>22.73</v>
+        <v>33.28</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>135.5</v>
+        <v>135.8</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>9.27</v>
+        <v>9.52</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>12.36</v>
+        <v>12.61</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-10.36</v>
+        <v>-10.88</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2452,13 +2452,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-10.02</v>
+        <v>-10.22</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-4.55</v>
+        <v>-4.75</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>18.25</v>
+        <v>17.6</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2533,13 +2533,13 @@
         <v>20.44</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>18.12</v>
+        <v>17.55</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>3.34</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-8.390000000000001</v>
+        <v>-11.27</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-2.87</v>
+        <v>-6.33</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.99</v>
+        <v>7.68</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2611,13 +2611,13 @@
         <v>1</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>7.64</v>
+        <v>7.68</v>
       </c>
       <c r="Q20" s="8" t="n">
         <v>6.82</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>3.24</v>
+        <v>3.78</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>-7.84</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-0.57</v>
+        <v>9.25</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2667,33 +2667,41 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="6" t="n"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>46205</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="L21" s="5" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n">
-        <v>2.33</v>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>5.07</v>
+        <v>4.75</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-1.55</v>
+        <v>-7.77</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2705,9 +2713,11 @@
         <v>0.1</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="X21" s="5" t="n"/>
+        <v>-5.15</v>
+      </c>
+      <c r="X21" s="5" t="n">
+        <v>-2.86</v>
+      </c>
       <c r="Y21" s="6" t="n"/>
     </row>
     <row r="22" ht="23.4" customHeight="1">
@@ -2826,14 +2836,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>30.32</v>
+        <v>30.38</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2857,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2893,13 +2903,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5387.5</v>
+        <v>5280</v>
       </c>
       <c r="N24" t="n">
-        <v>0.42</v>
+        <v>-1.58</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
         <v>5577.5</v>
@@ -2923,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.42</v>
+        <v>-1.58</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2962,22 +2972,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>22.86</v>
+        <v>25.14</v>
       </c>
       <c r="N25" t="n">
-        <v>13.39</v>
+        <v>24.7</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>25.14</v>
       </c>
       <c r="Q25" t="n">
         <v>19.39</v>
       </c>
       <c r="R25" t="n">
-        <v>15.08</v>
+        <v>24.7</v>
       </c>
       <c r="S25" t="n">
         <v>-3.82</v>
@@ -2992,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>13.39</v>
+        <v>24.7</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -3031,25 +3041,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>99.45</v>
+        <v>97.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4</v>
+        <v>-1.26</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>100.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>98.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.45</v>
+        <v>-2.68</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3061,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.4</v>
+        <v>-1.26</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3100,25 +3110,25 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.86</v>
+        <v>20.5</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.86</v>
+        <v>-2.57</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
         <v>21.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.66</v>
+        <v>20.24</v>
       </c>
       <c r="R27" t="n">
         <v>1.05</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.81</v>
+        <v>-3.8</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3130,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.86</v>
+        <v>-2.57</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3169,30 +3179,279 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.57</v>
+        <v>15.98</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>-3.56</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>16.57</v>
+        <v>16.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>16.57</v>
+        <v>15.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-4.04</v>
       </c>
       <c r="T28" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U28" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-3.56</v>
+      </c>
       <c r="Y28" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ISLEM-000028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KLGYO</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ISLEM-000029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KLNMA</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ISLEM-000030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SANEL</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>81.61</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ISLEM-000031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SNGYO</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02.07.2026 22:42:39</t>
+          <t>03.07.2026 19:12:52</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>24.26</v>
+        <v>23.64</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-12.29</v>
+        <v>-14.53</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47.3</v>
+        <v>47.24</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-20.05</v>
+        <v>-20.15</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>184.3</v>
+        <v>186.4</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.46</v>
+        <v>-2.36</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1410,13 +1410,13 @@
         <v>15</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>14.97</v>
+        <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>12.32</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>16.32</v>
+        <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
         <v>-4.27</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>69.8</v>
+        <v>70.75</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-10.74</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.28</v>
+        <v>24</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-8.779999999999999</v>
+        <v>-5.96</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>45.7</v>
+        <v>43.76</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-1.3</v>
+        <v>-5.49</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>39.92</v>
+        <v>40.7</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-9.27</v>
+        <v>-7.5</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.609999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1892,13 +1892,13 @@
         <v>13</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>8.16</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="S11" s="5" t="n">
         <v>-6.53</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>3.86</v>
+        <v>6.15</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>108.2</v>
+        <v>113.9</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-10.58</v>
+        <v>-5.87</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>156.7</v>
+        <v>165.6</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>161.7</v>
+        <v>169.7</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>25.84</v>
+        <v>32.06</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>28.34</v>
+        <v>35.63</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>17.27</v>
+        <v>17.15</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2138,13 +2138,13 @@
         <v>20.32</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>17</v>
+        <v>16.14</v>
       </c>
       <c r="R14" s="8" t="n">
         <v>10.62</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>-7.46</v>
+        <v>-12.14</v>
       </c>
       <c r="T14" s="8" t="n">
         <v>14734.5</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>-1.03</v>
+        <v>-1.72</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2216,13 +2216,13 @@
         <v>3</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>87</v>
+        <v>88.7</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>59.25</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>28.22</v>
+        <v>30.73</v>
       </c>
       <c r="S15" s="5" t="n">
         <v>-12.68</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>33.28</v>
+        <v>30.1</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>135.8</v>
+        <v>137.9</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>9.52</v>
+        <v>11.21</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>12.61</v>
+        <v>14.3</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>86</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-10.88</v>
+        <v>-9.43</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2533,13 +2533,13 @@
         <v>20.44</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17.55</v>
+        <v>17.49</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>3.34</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-11.27</v>
+        <v>-11.58</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.68</v>
+        <v>7.38</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2611,13 +2611,13 @@
         <v>1</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>7.68</v>
+        <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
         <v>6.82</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>3.78</v>
+        <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>-7.84</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>9.25</v>
+        <v>4.98</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2695,13 +2695,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>4.75</v>
+        <v>4.38</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-7.77</v>
+        <v>-14.95</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-2.86</v>
+        <v>-4.5</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-4.55</v>
+        <v>-3.03</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,14 +2836,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>30.38</v>
+        <v>30.16</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>1.27</v>
+        <v>0.53</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>1.27</v>
+        <v>0.53</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2903,22 +2903,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5280</v>
+        <v>5650</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.58</v>
+        <v>5.31</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>5577.5</v>
+        <v>5725</v>
       </c>
       <c r="Q24" t="n">
         <v>5170</v>
       </c>
       <c r="R24" t="n">
-        <v>3.96</v>
+        <v>6.71</v>
       </c>
       <c r="S24" t="n">
         <v>-3.63</v>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.58</v>
+        <v>5.31</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2968,26 +2968,37 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>46206</v>
+      </c>
+      <c r="J25" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>25.14</v>
-      </c>
-      <c r="N25" t="n">
-        <v>24.7</v>
+        <v>22.92</v>
+      </c>
+      <c r="M25" t="n">
+        <v>13.69</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>25.14</v>
+        <v>27.6</v>
       </c>
       <c r="Q25" t="n">
         <v>19.39</v>
       </c>
       <c r="R25" t="n">
-        <v>24.7</v>
+        <v>36.9</v>
       </c>
       <c r="S25" t="n">
         <v>-3.82</v>
@@ -3002,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>24.7</v>
+        <v>13.69</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -3041,22 +3052,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>97.8</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.26</v>
+        <v>0.1</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>100.4</v>
+        <v>101.2</v>
       </c>
       <c r="Q26" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>2.17</v>
       </c>
       <c r="S26" t="n">
         <v>-2.68</v>
@@ -3071,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.26</v>
+        <v>0.1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3116,7 +3127,7 @@
         <v>-2.57</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
         <v>21.26</v>
@@ -3175,29 +3186,40 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>46206</v>
+      </c>
+      <c r="J28" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-3.56</v>
+        <v>16.1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-5.01</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
         <v>16.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.9</v>
+        <v>15.55</v>
       </c>
       <c r="R28" t="n">
         <v>0.18</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.04</v>
+        <v>-6.16</v>
       </c>
       <c r="T28" t="n">
         <v>14274.02</v>
@@ -3209,7 +3231,10 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>-3.56</v>
+        <v>-5.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.29</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3248,29 +3273,38 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.27</v>
+        <v>5.13</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-2.66</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.27</v>
+        <v>5.11</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>-3.04</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U29" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-2.66</v>
+      </c>
       <c r="Y29" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -3304,33 +3338,56 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>46206</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
         <v>10.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>10.6</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>-7.64</v>
       </c>
       <c r="T30" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U30" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -3364,33 +3421,56 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>46206</v>
+      </c>
+      <c r="J31" t="n">
+        <v>81.61</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
+        <v>83.84999999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-4.99</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>85.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>85.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>-6.87</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U31" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.74</v>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -3428,30 +3508,219 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>-3.25</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U32" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-3</v>
+      </c>
       <c r="Y32" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ISLEM-000032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>KOZAL</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ISLEM-000033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>METRO</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ISLEM-000034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MOGAN</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03.07.2026 19:12:52</t>
+          <t>06.07.2026 21:31:01</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.64</v>
+        <v>24</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-14.53</v>
+        <v>-13.23</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47.24</v>
+        <v>45.88</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>46.24</v>
+        <v>45.66</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-25.73</v>
+        <v>-26.66</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-20.15</v>
+        <v>-22.45</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>186.4</v>
+        <v>184.6</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-2.36</v>
+        <v>-3.3</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>70.75</v>
+        <v>69.45</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-9.529999999999999</v>
+        <v>-11.19</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>24</v>
+        <v>24.7</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-5.96</v>
+        <v>-3.21</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>43.76</v>
+        <v>43.8</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-5.49</v>
+        <v>-5.4</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>40.7</v>
+        <v>39.76</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-7.5</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1892,13 +1892,13 @@
         <v>13</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>8.16</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
         <v>-6.53</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>6.15</v>
+        <v>3.74</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>113.9</v>
+        <v>108.8</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-5.87</v>
+        <v>-10.08</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>165.6</v>
+        <v>182.1</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>169.7</v>
+        <v>182.1</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>32.06</v>
+        <v>41.71</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>35.63</v>
+        <v>49.14</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>17.15</v>
+        <v>16.84</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>-1.72</v>
+        <v>-3.5</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>83.84999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>30.1</v>
+        <v>17.15</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>137.9</v>
+        <v>136.3</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>11.21</v>
+        <v>9.92</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>14.3</v>
+        <v>13.01</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>85.95</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-9.43</v>
+        <v>-10.93</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2452,13 +2452,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-10.22</v>
+        <v>-10.61</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-4.75</v>
+        <v>-5.17</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17.6</v>
+        <v>19.34</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-6.33</v>
+        <v>2.93</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.38</v>
+        <v>7.1</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>4.98</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.67</v>
+        <v>4.49</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-4.5</v>
+        <v>-8.18</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-3.03</v>
+        <v>-4.55</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,14 +2836,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>30.16</v>
+        <v>29.9</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>0.53</v>
+        <v>-0.33</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>0.53</v>
+        <v>-0.33</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5650</v>
+        <v>5310</v>
       </c>
       <c r="N24" t="n">
-        <v>5.31</v>
+        <v>-1.03</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
         <v>5725</v>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>5.31</v>
+        <v>-1.03</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>22.92</v>
+        <v>21.14</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>99.15000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
         <v>101.2</v>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3121,25 +3121,25 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.5</v>
+        <v>20.22</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.57</v>
+        <v>-3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
         <v>21.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.24</v>
+        <v>20.06</v>
       </c>
       <c r="R27" t="n">
         <v>1.05</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.8</v>
+        <v>-4.66</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>-2.57</v>
+        <v>-3.9</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.1</v>
+        <v>17.47</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3210,13 +3210,13 @@
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>16.6</v>
+        <v>17.58</v>
       </c>
       <c r="Q28" t="n">
         <v>15.55</v>
       </c>
       <c r="R28" t="n">
-        <v>0.18</v>
+        <v>6.1</v>
       </c>
       <c r="S28" t="n">
         <v>-6.16</v>
@@ -3234,7 +3234,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>2.29</v>
+        <v>10.99</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3273,25 +3273,25 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.13</v>
+        <v>5.05</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.66</v>
+        <v>-4.17</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
         <v>5.29</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.11</v>
+        <v>5.03</v>
       </c>
       <c r="R29" t="n">
         <v>0.38</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.04</v>
+        <v>-4.55</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>-2.66</v>
+        <v>-4.17</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3362,13 +3362,13 @@
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>10.6</v>
+        <v>10.47</v>
       </c>
       <c r="Q30" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>-1.23</v>
       </c>
       <c r="S30" t="n">
         <v>-7.64</v>
@@ -3386,7 +3386,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.7</v>
+        <v>2.28</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>83.84999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3448,13 +3448,13 @@
         <v>88.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>80</v>
+        <v>75.5</v>
       </c>
       <c r="R31" t="n">
         <v>3.26</v>
       </c>
       <c r="S31" t="n">
-        <v>-6.87</v>
+        <v>-12.11</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3469,7 +3469,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>2.74</v>
+        <v>-7.49</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3504,29 +3504,40 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>46209</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-3</v>
+        <v>3.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-5</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-3.25</v>
+        <v>-6.25</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3538,7 +3549,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>-3</v>
+        <v>-5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-1.32</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3577,29 +3591,38 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>50.6</v>
+        <v>52.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U33" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.19</v>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -3637,29 +3660,38 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.970000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>8.970000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.970000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U34" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-1.11</v>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -3697,30 +3729,219 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>15.5</v>
+        <v>15.86</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>15.5</v>
+        <v>16.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>15.5</v>
+        <v>15.26</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>-1.55</v>
       </c>
       <c r="T35" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U35" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.32</v>
+      </c>
       <c r="Y35" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ISLEM-000035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NUHCM</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="G36" t="n">
+        <v>217.45</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ISLEM-000036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SKBNK</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="G37" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ISLEM-000037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>347</v>
+      </c>
+      <c r="G38" t="n">
+        <v>329.65</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>347</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>347</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06.07.2026 21:31:01</t>
+          <t>07.07.2026 22:22:16</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>24</v>
+        <v>23.86</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-13.23</v>
+        <v>-13.74</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>45.88</v>
+        <v>46.38</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>45.66</v>
+        <v>45.38</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-26.66</v>
+        <v>-27.11</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-22.45</v>
+        <v>-21.6</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>184.6</v>
+        <v>184.2</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.3</v>
+        <v>-3.51</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.9</v>
+        <v>13.46</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.38</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>69.45</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-11.19</v>
+        <v>-2.37</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>24.7</v>
+        <v>23.84</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-3.21</v>
+        <v>-6.58</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>43.8</v>
+        <v>43.44</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-5.4</v>
+        <v>-6.18</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>39.76</v>
+        <v>39.62</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-9.640000000000001</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.6</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>3.74</v>
+        <v>3.02</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>108.8</v>
+        <v>109</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>107.7</v>
+        <v>107</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-15.46</v>
+        <v>-16.01</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-10.08</v>
+        <v>-9.92</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>182.1</v>
+        <v>174.8</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>182.1</v>
+        <v>191.7</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>41.71</v>
+        <v>49.18</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>49.14</v>
+        <v>43.16</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>16.84</v>
+        <v>18.52</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>-3.5</v>
+        <v>6.13</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>75.5</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>17.15</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>136.3</v>
+        <v>135</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>9.92</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>13.01</v>
+        <v>11.96</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>85.95</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-10.93</v>
+        <v>-10.78</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-5.17</v>
+        <v>-4.75</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>19.34</v>
+        <v>19.99</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2530,13 +2530,13 @@
         <v>7</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>20.44</v>
+        <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>17.49</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>3.34</v>
+        <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
         <v>-11.58</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>2.93</v>
+        <v>6.39</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.1</v>
+        <v>7.17</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>1</v>
+        <v>1.99</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-8.18</v>
+        <v>-5.93</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2776,13 +2776,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-8.289999999999999</v>
+        <v>-10.24</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-4.55</v>
+        <v>-6.57</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,14 +2836,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>-0.33</v>
+        <v>-0.67</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-0.33</v>
+        <v>-0.67</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2899,29 +2899,40 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>46210</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5096.75</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5310</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-1.03</v>
+        <v>5170</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-5</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P24" t="n">
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>5170</v>
+        <v>5095</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.63</v>
+        <v>-5.03</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2933,7 +2944,10 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.03</v>
+        <v>-5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.44</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2983,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21.14</v>
+        <v>22.16</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3052,22 +3066,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>98.5</v>
+        <v>101.3</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.27</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>101.2</v>
+        <v>102.4</v>
       </c>
       <c r="Q26" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>2.17</v>
+        <v>3.38</v>
       </c>
       <c r="S26" t="n">
         <v>-2.68</v>
@@ -3082,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.27</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3121,13 +3135,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.22</v>
+        <v>20.52</v>
       </c>
       <c r="N27" t="n">
-        <v>-3.9</v>
+        <v>-2.47</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
         <v>21.26</v>
@@ -3151,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>-3.9</v>
+        <v>-2.47</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3201,7 +3215,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>17.47</v>
+        <v>15.73</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3210,13 +3224,13 @@
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>17.58</v>
+        <v>19.21</v>
       </c>
       <c r="Q28" t="n">
         <v>15.55</v>
       </c>
       <c r="R28" t="n">
-        <v>6.1</v>
+        <v>15.93</v>
       </c>
       <c r="S28" t="n">
         <v>-6.16</v>
@@ -3234,7 +3248,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>10.99</v>
+        <v>-0.06</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3269,29 +3283,40 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>46210</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-4.17</v>
+        <v>5.1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-4.93</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
-        <v>5.29</v>
+        <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>0.38</v>
+        <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-4.55</v>
+        <v>-5.12</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3303,7 +3328,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>-4.17</v>
+        <v>-4.93</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3353,7 +3381,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3386,7 +3414,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>2.28</v>
+        <v>-2.68</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3436,7 +3464,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>75.5</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3448,13 +3476,13 @@
         <v>88.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>75.5</v>
+        <v>69.5</v>
       </c>
       <c r="R31" t="n">
         <v>3.26</v>
       </c>
       <c r="S31" t="n">
-        <v>-12.11</v>
+        <v>-19.09</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3469,7 +3497,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-7.49</v>
+        <v>-14.41</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3519,7 +3547,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3531,13 +3559,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-6.25</v>
+        <v>-7.75</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3552,7 +3580,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-1.32</v>
+        <v>-0.26</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3591,22 +3619,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>3.16</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>52.3</v>
+        <v>53.45</v>
       </c>
       <c r="Q33" t="n">
         <v>50.5</v>
       </c>
       <c r="R33" t="n">
-        <v>3.36</v>
+        <v>5.63</v>
       </c>
       <c r="S33" t="n">
         <v>-0.2</v>
@@ -3621,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.19</v>
+        <v>3.16</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3660,25 +3688,25 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.869999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="N34" t="n">
-        <v>-1.11</v>
+        <v>-1.78</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.789999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-2.01</v>
+        <v>-3.46</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3690,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>-1.11</v>
+        <v>-1.78</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3729,13 +3757,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>15.86</v>
+        <v>16.03</v>
       </c>
       <c r="N35" t="n">
-        <v>2.32</v>
+        <v>3.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
         <v>16.38</v>
@@ -3759,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.32</v>
+        <v>3.42</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3798,29 +3826,38 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>228.9</v>
+        <v>227.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>228.9</v>
+        <v>231</v>
       </c>
       <c r="Q36" t="n">
-        <v>228.9</v>
+        <v>226.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U36" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-0.57</v>
+      </c>
       <c r="Y36" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -3858,29 +3895,38 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>19.08</v>
+        <v>19.1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>19.08</v>
+        <v>19.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>19.08</v>
+        <v>18.73</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>-1.83</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U37" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Y37" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -3918,30 +3964,159 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>347</v>
+        <v>348.25</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>347</v>
+        <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>347</v>
+        <v>345.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U38" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.36</v>
+      </c>
       <c r="Y38" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ISLEM-000038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ISLEM-000039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MAKIM</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G40" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07.07.2026 22:22:16</t>
+          <t>08.07.2026 20:20:22</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.86</v>
+        <v>23.58</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-13.74</v>
+        <v>-14.75</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>46.38</v>
+        <v>44.68</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>45.38</v>
+        <v>44.52</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-27.11</v>
+        <v>-28.49</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-21.6</v>
+        <v>-24.48</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>184.2</v>
+        <v>182.1</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.51</v>
+        <v>-4.61</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.46</v>
+        <v>13.18</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>8.109999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1489,13 +1489,13 @@
         <v>8</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>8.609999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>3.85</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>117.42</v>
+        <v>125.25</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>-2.78</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>83.95</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-2.37</v>
+        <v>7.35</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.84</v>
+        <v>22.84</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>23.06</v>
+        <v>22.84</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-14.15</v>
+        <v>-14.97</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-6.58</v>
+        <v>-10.5</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>43.44</v>
+        <v>41.94</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>42.72</v>
+        <v>41.86</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-12.35</v>
+        <v>-14.12</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-6.18</v>
+        <v>-9.42</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>39.62</v>
+        <v>37.78</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1814,13 +1814,13 @@
         <v>46.74</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>38.54</v>
+        <v>37.78</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.91</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>-16.8</v>
+        <v>-18.44</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>14493.09</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-9.949999999999999</v>
+        <v>-14.14</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.539999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>8.16</v>
+        <v>8.08</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-6.53</v>
+        <v>-7.45</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>3.02</v>
+        <v>-2.29</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>109</v>
+        <v>103.7</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>107</v>
+        <v>103.7</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-16.01</v>
+        <v>-18.6</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-9.92</v>
+        <v>-14.3</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>174.8</v>
+        <v>164.9</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>43.16</v>
+        <v>35.05</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>18.52</v>
+        <v>20.36</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2135,13 +2135,13 @@
         <v>4</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>20.32</v>
+        <v>20.36</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>16.14</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>10.62</v>
+        <v>10.83</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>-12.14</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>6.13</v>
+        <v>16.68</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>69.84999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>14.04</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>135</v>
+        <v>134.5</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>11.96</v>
+        <v>11.56</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2371,13 +2371,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>84.8</v>
+        <v>83.55</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-16.54</v>
+        <v>-17.77</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-10.78</v>
+        <v>-12.85</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.61</v>
+        <v>4.43</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2452,13 +2452,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-10.61</v>
+        <v>-12.97</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-4.75</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>19.99</v>
+        <v>19</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>6.39</v>
+        <v>1.12</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.17</v>
+        <v>7.13</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2695,13 +2695,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-14.95</v>
+        <v>-15.73</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-5.93</v>
+        <v>-11.04</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2776,13 +2776,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-10.24</v>
+        <v>-12.68</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-6.57</v>
+        <v>-8.59</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2843,7 +2843,7 @@
         <v>-0.67</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5170</v>
+        <v>5122.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2947,7 +2947,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>1.44</v>
+        <v>0.51</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>22.16</v>
+        <v>20.1</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>101.3</v>
+        <v>98.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.27</v>
+        <v>-0.25</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P26" t="n">
         <v>102.4</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.27</v>
+        <v>-0.25</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3131,29 +3131,40 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>46211</v>
+      </c>
+      <c r="J27" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-2.47</v>
+        <v>20.14</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-4.99</v>
       </c>
       <c r="O27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P27" t="n">
         <v>21.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.06</v>
+        <v>19.99</v>
       </c>
       <c r="R27" t="n">
         <v>1.05</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.66</v>
+        <v>-4.99</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3165,7 +3176,10 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>-2.47</v>
+        <v>-4.99</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.75</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3215,7 +3229,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15.73</v>
+        <v>14.98</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3227,13 +3241,13 @@
         <v>19.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.55</v>
+        <v>14.66</v>
       </c>
       <c r="R28" t="n">
         <v>15.93</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.16</v>
+        <v>-11.53</v>
       </c>
       <c r="T28" t="n">
         <v>14274.02</v>
@@ -3248,7 +3262,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.06</v>
+        <v>-4.83</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3298,7 +3312,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3310,13 +3324,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-5.12</v>
+        <v>-5.5</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3331,7 +3345,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3381,7 +3395,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3414,7 +3428,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-2.68</v>
+        <v>-2.78</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3464,7 +3478,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>69.84999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3497,7 +3511,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-14.41</v>
+        <v>-9.94</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3547,7 +3561,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3580,7 +3594,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.26</v>
+        <v>-2.63</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3619,13 +3633,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>52.2</v>
+        <v>51.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3.16</v>
+        <v>1.28</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
         <v>53.45</v>
@@ -3649,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>3.16</v>
+        <v>1.28</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3684,29 +3698,40 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="n">
+        <v>46211</v>
+      </c>
+      <c r="J34" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-1.78</v>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-5.02</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.66</v>
+        <v>8.49</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-3.46</v>
+        <v>-5.35</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3718,7 +3743,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>-1.78</v>
+        <v>-5.02</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.12</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3757,13 +3785,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>16.03</v>
+        <v>15.6</v>
       </c>
       <c r="N35" t="n">
-        <v>3.42</v>
+        <v>0.65</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
         <v>16.38</v>
@@ -3787,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.42</v>
+        <v>0.65</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3826,25 +3854,25 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>227.6</v>
+        <v>222.7</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.57</v>
+        <v>-2.71</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
         <v>231</v>
       </c>
       <c r="Q36" t="n">
-        <v>226.8</v>
+        <v>222.3</v>
       </c>
       <c r="R36" t="n">
         <v>0.92</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.92</v>
+        <v>-2.88</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
@@ -3856,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.57</v>
+        <v>-2.71</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3895,22 +3923,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>19.1</v>
+        <v>19.43</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1</v>
+        <v>1.83</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>19.35</v>
+        <v>19.65</v>
       </c>
       <c r="Q37" t="n">
         <v>18.73</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>2.99</v>
       </c>
       <c r="S37" t="n">
         <v>-1.83</v>
@@ -3925,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.1</v>
+        <v>1.83</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -3964,25 +3992,25 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>348.25</v>
+        <v>332</v>
       </c>
       <c r="N38" t="n">
-        <v>0.36</v>
+        <v>-4.32</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>345.25</v>
+        <v>330.25</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.5</v>
+        <v>-4.83</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -3994,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.36</v>
+        <v>-4.32</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4033,29 +4061,38 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>89.84999999999999</v>
+        <v>89</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>89.84999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>89.84999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="T39" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U39" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-0.95</v>
+      </c>
       <c r="Y39" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -4089,34 +4126,117 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>46211</v>
+      </c>
+      <c r="J40" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-5</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>19.99</v>
+        <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>19.99</v>
+        <v>18.86</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>-5.65</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U40" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.05</v>
+      </c>
       <c r="Y40" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ISLEM-000040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DOBUR</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>318</v>
+      </c>
+      <c r="G41" t="n">
+        <v>302.1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>318</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>318</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08.07.2026 20:20:22</t>
+          <t>10.07.2026 10:37:59</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.58</v>
+        <v>23.38</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-14.75</v>
+        <v>-15.47</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>44.68</v>
+        <v>45.14</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>44.52</v>
+        <v>44.3</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-28.49</v>
+        <v>-28.85</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-24.48</v>
+        <v>-23.7</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>182.1</v>
+        <v>183.7</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-4.61</v>
+        <v>-3.77</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.18</v>
+        <v>14.71</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>8.48</v>
+        <v>6.88</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>83.95</v>
+        <v>80.75</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1568,13 +1568,13 @@
         <v>5</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>84.5</v>
+        <v>85.95</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>68.55</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>2.67</v>
+        <v>4.43</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>-16.71</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>7.35</v>
+        <v>3.26</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>22.84</v>
+        <v>23.2</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>22.84</v>
+        <v>22.76</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-14.97</v>
+        <v>-15.26</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.09</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>41.94</v>
+        <v>41.86</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>41.86</v>
+        <v>41.2</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-14.12</v>
+        <v>-15.47</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-9.42</v>
+        <v>-9.59</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>37.78</v>
+        <v>38.62</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1814,13 +1814,13 @@
         <v>46.74</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>37.78</v>
+        <v>37.48</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.91</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>-18.44</v>
+        <v>-19.08</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>14493.09</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-14.14</v>
+        <v>-12.23</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.1</v>
+        <v>8.26</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>8.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-7.45</v>
+        <v>-7.79</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-2.29</v>
+        <v>-0.36</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>103.7</v>
+        <v>105.5</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>103.7</v>
+        <v>103.5</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-18.6</v>
+        <v>-18.76</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-14.3</v>
+        <v>-12.81</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>164.9</v>
+        <v>167.9</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>35.05</v>
+        <v>37.51</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>20.36</v>
+        <v>23.3</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2135,13 +2135,13 @@
         <v>4</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>20.36</v>
+        <v>23.7</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>16.14</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>10.83</v>
+        <v>29.01</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>-12.14</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>16.68</v>
+        <v>33.52</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>73.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2216,13 +2216,13 @@
         <v>3</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>88.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>59.25</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>30.73</v>
+        <v>31.02</v>
       </c>
       <c r="S15" s="5" t="n">
         <v>-12.68</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>14.04</v>
+        <v>37.94</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>134.5</v>
+        <v>135</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>8.470000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>11.56</v>
+        <v>11.96</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>84.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2371,13 +2371,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>83.55</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-17.77</v>
+        <v>-21.36</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-12.85</v>
+        <v>-13.68</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2452,13 +2452,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.43</v>
+        <v>4.36</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-12.97</v>
+        <v>-14.34</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.68</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>19</v>
+        <v>19.03</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.13</v>
+        <v>7.26</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>1.42</v>
+        <v>3.27</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.35</v>
+        <v>4.54</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2695,13 +2695,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-15.73</v>
+        <v>-20.39</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-11.04</v>
+        <v>-7.16</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2776,13 +2776,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-12.68</v>
+        <v>-13.17</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2836,14 +2836,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5122.5</v>
+        <v>5110</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2926,13 +2926,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>5095</v>
+        <v>5050</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.03</v>
+        <v>-5.87</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2947,7 +2947,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>20.1</v>
+        <v>19.79</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>98.8</v>
+        <v>102.2</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.25</v>
+        <v>3.18</v>
       </c>
       <c r="O26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P26" t="n">
-        <v>102.4</v>
+        <v>103.2</v>
       </c>
       <c r="Q26" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>3.38</v>
+        <v>4.19</v>
       </c>
       <c r="S26" t="n">
         <v>-2.68</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.25</v>
+        <v>3.18</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.14</v>
+        <v>20.4</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3158,13 +3158,13 @@
         <v>21.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.99</v>
+        <v>19.42</v>
       </c>
       <c r="R27" t="n">
         <v>1.05</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.99</v>
+        <v>-7.7</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3179,7 +3179,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>0.75</v>
+        <v>2.05</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>14.98</v>
+        <v>14.88</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3241,13 +3241,13 @@
         <v>19.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>14.66</v>
+        <v>14.35</v>
       </c>
       <c r="R28" t="n">
         <v>15.93</v>
       </c>
       <c r="S28" t="n">
-        <v>-11.53</v>
+        <v>-13.4</v>
       </c>
       <c r="T28" t="n">
         <v>14274.02</v>
@@ -3262,7 +3262,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>-4.83</v>
+        <v>-5.46</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3324,13 +3324,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-5.5</v>
+        <v>-6.26</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3345,7 +3345,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.789999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3428,7 +3428,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-2.78</v>
+        <v>-1.19</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>73.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3487,13 +3487,13 @@
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>88.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
         <v>69.5</v>
       </c>
       <c r="R31" t="n">
-        <v>3.26</v>
+        <v>3.49</v>
       </c>
       <c r="S31" t="n">
         <v>-19.09</v>
@@ -3511,7 +3511,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-9.94</v>
+        <v>8.93</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3573,13 +3573,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-7.75</v>
+        <v>-8.5</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3594,7 +3594,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-2.63</v>
+        <v>-2.11</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3633,22 +3633,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>51.25</v>
+        <v>54.4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.28</v>
+        <v>7.51</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>53.45</v>
+        <v>54.6</v>
       </c>
       <c r="Q33" t="n">
         <v>50.5</v>
       </c>
       <c r="R33" t="n">
-        <v>5.63</v>
+        <v>7.91</v>
       </c>
       <c r="S33" t="n">
         <v>-0.2</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>7.51</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.529999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3725,13 +3725,13 @@
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.49</v>
+        <v>8.4</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-5.35</v>
+        <v>-6.35</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3746,7 +3746,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>0.12</v>
+        <v>1.53</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>15.6</v>
+        <v>15.52</v>
       </c>
       <c r="N35" t="n">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P35" t="n">
         <v>16.38</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>222.7</v>
+        <v>222.1</v>
       </c>
       <c r="N36" t="n">
-        <v>-2.71</v>
+        <v>-2.97</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
         <v>231</v>
       </c>
       <c r="Q36" t="n">
-        <v>222.3</v>
+        <v>217.9</v>
       </c>
       <c r="R36" t="n">
         <v>0.92</v>
       </c>
       <c r="S36" t="n">
-        <v>-2.88</v>
+        <v>-4.81</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>-2.71</v>
+        <v>-2.97</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3919,29 +3919,40 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>46212</v>
+      </c>
+      <c r="J37" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.83</v>
+        <v>18.12</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-4.98</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
         <v>19.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>18.73</v>
+        <v>17.51</v>
       </c>
       <c r="R37" t="n">
         <v>2.99</v>
       </c>
       <c r="S37" t="n">
-        <v>-1.83</v>
+        <v>-8.23</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -3953,7 +3964,10 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.83</v>
+        <v>-4.98</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-0.06</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -3992,13 +4006,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>332</v>
+        <v>341.75</v>
       </c>
       <c r="N38" t="n">
-        <v>-4.32</v>
+        <v>-1.51</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
         <v>355.5</v>
@@ -4022,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>-4.32</v>
+        <v>-1.51</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4061,25 +4075,25 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>89</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.95</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>90.7</v>
+        <v>92.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0.95</v>
+        <v>3.28</v>
       </c>
       <c r="S39" t="n">
-        <v>-2.5</v>
+        <v>-2.62</v>
       </c>
       <c r="T39" t="n">
         <v>14274.02</v>
@@ -4091,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.95</v>
+        <v>2.5</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -4141,7 +4155,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>19</v>
+        <v>19.03</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4153,13 +4167,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>18.86</v>
+        <v>18.62</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-5.65</v>
+        <v>-6.85</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4174,7 +4188,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4213,28 +4227,37 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>318</v>
+        <v>355.75</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>11.87</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="Q41" t="n">
         <v>318</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>13.52</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>14274.02</v>
+      </c>
+      <c r="U41" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11.87</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.07.2026 10:37:59</t>
+          <t>10.07.2026 20:54:16</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.38</v>
+        <v>23.4</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-15.47</v>
+        <v>-15.4</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>45.14</v>
+        <v>45.98</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-23.7</v>
+        <v>-22.28</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>183.7</v>
+        <v>186</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.77</v>
+        <v>-2.57</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14.71</v>
+        <v>14.42</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>80.75</v>
+        <v>80.2</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>3.26</v>
+        <v>2.56</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.2</v>
+        <v>23.52</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-9.09</v>
+        <v>-7.84</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>41.86</v>
+        <v>40.52</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>41.2</v>
+        <v>40.36</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-15.47</v>
+        <v>-17.19</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-9.59</v>
+        <v>-12.48</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.62</v>
+        <v>38.54</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-12.23</v>
+        <v>-12.41</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.26</v>
+        <v>8.23</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-0.36</v>
+        <v>-0.72</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>105.5</v>
+        <v>108.5</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-12.81</v>
+        <v>-10.33</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>167.9</v>
+        <v>179.9</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>37.51</v>
+        <v>47.34</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>23.3</v>
+        <v>22.12</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>33.52</v>
+        <v>26.76</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>88.90000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>37.94</v>
+        <v>21.57</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,11 +2279,11 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>8.869999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>18</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>11.96</v>
+        <v>13.57</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-13.68</v>
+        <v>-13.99</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-8.68</v>
+        <v>-6.61</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>19.03</v>
+        <v>18.35</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>1.28</v>
+        <v>-2.34</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.26</v>
+        <v>7.15</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>3.27</v>
+        <v>1.71</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.54</v>
+        <v>4.81</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-7.16</v>
+        <v>-1.64</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-8.59</v>
+        <v>-9.09</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,11 +2836,11 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>30</v>
+        <v>29.68</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>0</v>
+        <v>-1.07</v>
       </c>
       <c r="O23" s="5" t="n">
         <v>14</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>0</v>
+        <v>-1.07</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5110</v>
+        <v>5107.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2947,7 +2947,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>19.79</v>
+        <v>19.37</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3009,13 +3009,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.39</v>
+        <v>19.34</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.82</v>
+        <v>-4.07</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>102.2</v>
+        <v>101.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="O26" t="n">
         <v>11</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.4</v>
+        <v>20.46</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3179,7 +3179,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>14.88</v>
+        <v>14.9</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3262,7 +3262,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>-5.46</v>
+        <v>-5.34</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3345,7 +3345,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.949999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3407,13 +3407,13 @@
         <v>10.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.789999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R30" t="n">
         <v>-1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>-7.64</v>
+        <v>-8.49</v>
       </c>
       <c r="T30" t="n">
         <v>14274.02</v>
@@ -3428,7 +3428,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-1.19</v>
+        <v>-3.67</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>88.90000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3511,7 +3511,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>8.93</v>
+        <v>-3.99</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3594,7 +3594,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3633,22 +3633,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54.4</v>
+        <v>54.25</v>
       </c>
       <c r="N33" t="n">
-        <v>7.51</v>
+        <v>7.21</v>
       </c>
       <c r="O33" t="n">
         <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>54.6</v>
+        <v>55.3</v>
       </c>
       <c r="Q33" t="n">
         <v>50.5</v>
       </c>
       <c r="R33" t="n">
-        <v>7.91</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
         <v>-0.2</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>7.51</v>
+        <v>7.21</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.65</v>
+        <v>8.59</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3746,7 +3746,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.53</v>
+        <v>0.82</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3781,14 +3781,25 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>46213</v>
+      </c>
+      <c r="J35" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>15.52</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.13</v>
+        <v>14.27</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-5.03</v>
       </c>
       <c r="O35" t="n">
         <v>7</v>
@@ -3797,13 +3808,13 @@
         <v>16.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>15.26</v>
+        <v>14.27</v>
       </c>
       <c r="R35" t="n">
         <v>5.68</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.55</v>
+        <v>-7.94</v>
       </c>
       <c r="T35" t="n">
         <v>14274.02</v>
@@ -3815,7 +3826,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.13</v>
+        <v>-5.03</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-3.06</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3854,22 +3868,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>222.1</v>
+        <v>224.8</v>
       </c>
       <c r="N36" t="n">
-        <v>-2.97</v>
+        <v>-1.79</v>
       </c>
       <c r="O36" t="n">
         <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>231</v>
+        <v>231.1</v>
       </c>
       <c r="Q36" t="n">
         <v>217.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="S36" t="n">
         <v>-4.81</v>
@@ -3884,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>-2.97</v>
+        <v>-1.79</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3934,7 +3948,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>18.12</v>
+        <v>19.27</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3946,13 +3960,13 @@
         <v>19.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>17.51</v>
+        <v>17.32</v>
       </c>
       <c r="R37" t="n">
         <v>2.99</v>
       </c>
       <c r="S37" t="n">
-        <v>-8.23</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -3967,7 +3981,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.06</v>
+        <v>6.29</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4006,10 +4020,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>341.75</v>
+        <v>344.5</v>
       </c>
       <c r="N38" t="n">
-        <v>-1.51</v>
+        <v>-0.72</v>
       </c>
       <c r="O38" t="n">
         <v>4</v>
@@ -4036,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>-1.51</v>
+        <v>-0.72</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4155,7 +4169,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>19.03</v>
+        <v>18.35</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4167,13 +4181,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>18.62</v>
+        <v>18.18</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-6.85</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4188,7 +4202,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>0.21</v>
+        <v>-3.37</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4227,10 +4241,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>355.75</v>
+        <v>341</v>
       </c>
       <c r="N41" t="n">
-        <v>11.87</v>
+        <v>7.23</v>
       </c>
       <c r="O41" t="n">
         <v>2</v>
@@ -4257,9 +4271,69 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>11.87</v>
+        <v>7.23</v>
       </c>
       <c r="Y41" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ISLEM-000041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CEOEM</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>46213</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="G42" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.07.2026 20:54:16</t>
+          <t>13.07.2026 19:21:37</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.4</v>
+        <v>22.52</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1170,13 +1170,13 @@
         <v>29.8</v>
       </c>
       <c r="Q2" s="16" t="n">
-        <v>22.54</v>
+        <v>22.5</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>2.76</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>-22.28</v>
+        <v>-22.41</v>
       </c>
       <c r="T2" s="8" t="n">
         <v>13744.64</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-15.4</v>
+        <v>-18.58</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>45.98</v>
+        <v>45.32</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-22.28</v>
+        <v>-23.39</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>186</v>
+        <v>184.4</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-2.57</v>
+        <v>-3.4</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14.42</v>
+        <v>14.22</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.88</v>
+        <v>7.02</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>80.2</v>
+        <v>78.5</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>2.56</v>
+        <v>0.38</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.52</v>
+        <v>23.06</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-7.84</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>40.52</v>
+        <v>39.34</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>40.36</v>
+        <v>39.26</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-17.19</v>
+        <v>-19.45</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-12.48</v>
+        <v>-15.03</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.54</v>
+        <v>37.7</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-12.41</v>
+        <v>-14.32</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.23</v>
+        <v>8.08</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>8.050000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-7.79</v>
+        <v>-7.9</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-0.72</v>
+        <v>-2.53</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>108.5</v>
+        <v>105.9</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-10.33</v>
+        <v>-12.48</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>179.9</v>
+        <v>184.5</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>191.7</v>
+        <v>193</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>49.18</v>
+        <v>50.19</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>47.34</v>
+        <v>51.11</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>22.12</v>
+        <v>22.24</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2135,13 +2135,13 @@
         <v>4</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>16.14</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>29.01</v>
+        <v>31.74</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>-12.14</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>26.76</v>
+        <v>27.45</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>21.57</v>
+        <v>29.4</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>137</v>
+        <v>130.5</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>10.48</v>
+        <v>5.24</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>13.57</v>
+        <v>8.33</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>83</v>
+        <v>82.2</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-13.99</v>
+        <v>-14.82</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.52</v>
+        <v>4.7</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-6.61</v>
+        <v>-2.89</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>18.35</v>
+        <v>18.1</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-2.34</v>
+        <v>-3.67</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>7.15</v>
+        <v>6.89</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>1.71</v>
+        <v>-1.99</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.81</v>
+        <v>4.49</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-1.64</v>
+        <v>-8.18</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2776,13 +2776,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-13.17</v>
+        <v>-14.63</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-9.09</v>
+        <v>-11.11</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,14 +2836,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>29.68</v>
+        <v>29.52</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>-1.07</v>
+        <v>-1.6</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-1.07</v>
+        <v>-1.6</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5107.5</v>
+        <v>5032.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2926,13 +2926,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>5050</v>
+        <v>5002.5</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.87</v>
+        <v>-6.76</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2947,7 +2947,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>0.21</v>
+        <v>-1.26</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>19.37</v>
+        <v>19.01</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3009,13 +3009,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.34</v>
+        <v>19</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.07</v>
+        <v>-5.75</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>101.3</v>
+        <v>100.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.27</v>
+        <v>1.77</v>
       </c>
       <c r="O26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.27</v>
+        <v>1.77</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.46</v>
+        <v>20.08</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3179,7 +3179,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>2.35</v>
+        <v>0.45</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3262,7 +3262,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>-5.34</v>
+        <v>-2.8</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3345,7 +3345,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3407,13 +3407,13 @@
         <v>10.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="R30" t="n">
         <v>-1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>-8.49</v>
+        <v>-14.62</v>
       </c>
       <c r="T30" t="n">
         <v>14274.02</v>
@@ -3428,7 +3428,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-3.67</v>
+        <v>-7.65</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>78.34999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3511,7 +3511,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-3.99</v>
+        <v>2.19</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3594,7 +3594,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3633,13 +3633,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54.25</v>
+        <v>51.75</v>
       </c>
       <c r="N33" t="n">
-        <v>7.21</v>
+        <v>2.27</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>7.21</v>
+        <v>2.27</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.59</v>
+        <v>8.84</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3746,7 +3746,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>0.82</v>
+        <v>3.76</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>14.27</v>
+        <v>14.05</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3808,13 +3808,13 @@
         <v>16.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>14.27</v>
+        <v>13.9</v>
       </c>
       <c r="R35" t="n">
         <v>5.68</v>
       </c>
       <c r="S35" t="n">
-        <v>-7.94</v>
+        <v>-10.32</v>
       </c>
       <c r="T35" t="n">
         <v>14274.02</v>
@@ -3829,7 +3829,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>-3.06</v>
+        <v>-4.55</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3868,13 +3868,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>224.8</v>
+        <v>220.4</v>
       </c>
       <c r="N36" t="n">
-        <v>-1.79</v>
+        <v>-3.71</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P36" t="n">
         <v>231.1</v>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>-1.79</v>
+        <v>-3.71</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>19.27</v>
+        <v>18.52</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3981,7 +3981,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>6.29</v>
+        <v>2.15</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4020,13 +4020,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>344.5</v>
+        <v>333.5</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.72</v>
+        <v>-3.89</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P38" t="n">
         <v>355.5</v>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.72</v>
+        <v>-3.89</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P39" t="n">
         <v>92.8</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>18.35</v>
+        <v>18.1</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4181,13 +4181,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>18.18</v>
+        <v>18.01</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4202,7 +4202,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-3.37</v>
+        <v>-4.69</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4241,25 +4241,25 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="N41" t="n">
-        <v>7.23</v>
+        <v>-3.46</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>361</v>
+        <v>361.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="R41" t="n">
-        <v>13.52</v>
+        <v>13.6</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>-3.46</v>
       </c>
       <c r="T41" t="n">
         <v>14274.02</v>
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>7.23</v>
+        <v>-3.46</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4310,30 +4310,159 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>28.06</v>
+        <v>30.2</v>
       </c>
       <c r="N42" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="R42" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="T42" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U42" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V42" t="n">
         <v>0</v>
       </c>
-      <c r="O42" t="n">
+      <c r="W42" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ISLEM-000042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FORTE</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>101</v>
+      </c>
+      <c r="G43" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>101</v>
+      </c>
+      <c r="N43" t="n">
         <v>0</v>
       </c>
-      <c r="P42" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="R42" t="n">
+      <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="n">
+      <c r="P43" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>101</v>
+      </c>
+      <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="T42" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y42" t="inlineStr">
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ISLEM-000043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GLBMD</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="G44" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.07.2026 19:21:37</t>
+          <t>14.07.2026 20:31:47</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>22.52</v>
+        <v>22.5</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1170,13 +1170,13 @@
         <v>29.8</v>
       </c>
       <c r="Q2" s="16" t="n">
-        <v>22.5</v>
+        <v>22.14</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>2.76</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>-22.41</v>
+        <v>-23.66</v>
       </c>
       <c r="T2" s="8" t="n">
         <v>13744.64</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-18.58</v>
+        <v>-18.66</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>45.32</v>
+        <v>45.6</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-23.39</v>
+        <v>-22.92</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>184.4</v>
+        <v>184</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.4</v>
+        <v>-3.61</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14.22</v>
+        <v>13.86</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.02</v>
+        <v>7.26</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0.38</v>
+        <v>0.64</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.06</v>
+        <v>23.84</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-9.640000000000001</v>
+        <v>-6.58</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>39.26</v>
+        <v>38.92</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-19.45</v>
+        <v>-20.15</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>37.7</v>
+        <v>38.44</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-14.32</v>
+        <v>-12.64</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.08</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-2.53</v>
+        <v>-1.93</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>105.9</v>
+        <v>108.8</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-12.48</v>
+        <v>-10.08</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>184.5</v>
+        <v>202.9</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>193</v>
+        <v>202.9</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>50.19</v>
+        <v>57.9</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>51.11</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>22.24</v>
+        <v>21.68</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>27.45</v>
+        <v>24.24</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>83.40000000000001</v>
+        <v>84.05</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>29.4</v>
+        <v>30.41</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>130.5</v>
+        <v>135</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>5.24</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>8.33</v>
+        <v>11.96</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-14.82</v>
+        <v>-14.4</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-2.89</v>
+        <v>-5.17</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>18.1</v>
+        <v>18.02</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-3.67</v>
+        <v>-4.1</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.89</v>
+        <v>6.65</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2614,13 +2614,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.82</v>
+        <v>6.64</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-7.84</v>
+        <v>-10.27</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-1.99</v>
+        <v>-5.41</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-8.18</v>
+        <v>-7.98</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2776,13 +2776,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-14.63</v>
+        <v>-16.59</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-11.11</v>
+        <v>-12.12</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,14 +2836,14 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>29.52</v>
+        <v>29.5</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>-1.6</v>
+        <v>-1.67</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>32.3</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-1.6</v>
+        <v>-1.67</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5032.5</v>
+        <v>5020</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2926,13 +2926,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>5002.5</v>
+        <v>4965</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.76</v>
+        <v>-7.46</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2947,7 +2947,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.26</v>
+        <v>-1.51</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>19.01</v>
+        <v>18.68</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3009,13 +3009,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>18.67</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.75</v>
+        <v>-7.39</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>100.8</v>
+        <v>100.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="O26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.08</v>
+        <v>20.02</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3179,7 +3179,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3324,13 +3324,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-6.26</v>
+        <v>-7.02</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3345,7 +3345,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.300000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3407,13 +3407,13 @@
         <v>10.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
         <v>-1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>-14.62</v>
+        <v>-15.09</v>
       </c>
       <c r="T30" t="n">
         <v>14274.02</v>
@@ -3428,7 +3428,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-7.65</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>83.40000000000001</v>
+        <v>84.05</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3511,7 +3511,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>2.19</v>
+        <v>2.99</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.84</v>
+        <v>3.73</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3594,7 +3594,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>-1.84</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3633,25 +3633,25 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>51.75</v>
+        <v>50.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.27</v>
+        <v>0.4</v>
       </c>
       <c r="O33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>50.5</v>
+        <v>50.45</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.27</v>
+        <v>0.4</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3746,7 +3746,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>3.76</v>
+        <v>4.46</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>14.05</v>
+        <v>15.45</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3829,7 +3829,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>-4.55</v>
+        <v>4.96</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3864,29 +3864,40 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J36" t="n">
+        <v>217.45</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L36" t="n">
         <v>220.4</v>
       </c>
-      <c r="N36" t="n">
-        <v>-3.71</v>
+      <c r="M36" t="n">
+        <v>-5</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P36" t="n">
         <v>231.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>217.9</v>
+        <v>217</v>
       </c>
       <c r="R36" t="n">
         <v>0.96</v>
       </c>
       <c r="S36" t="n">
-        <v>-4.81</v>
+        <v>-5.2</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
@@ -3898,7 +3909,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>-3.71</v>
+        <v>-5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.36</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3948,7 +3962,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>18.52</v>
+        <v>18.75</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3981,7 +3995,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>2.15</v>
+        <v>3.42</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4016,29 +4030,40 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J38" t="n">
+        <v>329.65</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>333.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-3.89</v>
+        <v>326</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-5</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>330.25</v>
+        <v>321.5</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-4.83</v>
+        <v>-7.35</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -4050,7 +4075,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.89</v>
+        <v>-5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-1.11</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4089,22 +4117,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>92.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="O39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P39" t="n">
-        <v>92.8</v>
+        <v>95.7</v>
       </c>
       <c r="Q39" t="n">
         <v>87.5</v>
       </c>
       <c r="R39" t="n">
-        <v>3.28</v>
+        <v>6.51</v>
       </c>
       <c r="S39" t="n">
         <v>-2.62</v>
@@ -4119,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -4169,7 +4197,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>18.1</v>
+        <v>18.02</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4202,7 +4230,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-4.69</v>
+        <v>-5.11</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4237,29 +4265,40 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J41" t="n">
+        <v>302.1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>307</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-3.46</v>
+        <v>276.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-5</v>
       </c>
       <c r="O41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P41" t="n">
         <v>361.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>307</v>
+        <v>276.5</v>
       </c>
       <c r="R41" t="n">
         <v>13.6</v>
       </c>
       <c r="S41" t="n">
-        <v>-3.46</v>
+        <v>-13.05</v>
       </c>
       <c r="T41" t="n">
         <v>14274.02</v>
@@ -4271,7 +4310,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>-3.46</v>
+        <v>-5</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-8.470000000000001</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4310,25 +4352,25 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>30.2</v>
+        <v>27.5</v>
       </c>
       <c r="N42" t="n">
-        <v>7.63</v>
+        <v>-2</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>30.44</v>
+        <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>27.26</v>
+        <v>27.18</v>
       </c>
       <c r="R42" t="n">
-        <v>8.48</v>
+        <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-2.85</v>
+        <v>-3.14</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4340,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>7.63</v>
+        <v>-2</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4379,28 +4421,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>101</v>
+        <v>107.1</v>
       </c>
       <c r="N43" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="T43" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U43" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V43" t="n">
         <v>0</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>101</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>14274.02</v>
+      <c r="W43" t="n">
+        <v>6.04</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4439,30 +4490,99 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>14.22</v>
+        <v>13.86</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>-2.53</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>14.22</v>
+        <v>13.71</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="T44" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U44" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="n">
-        <v>14274.02</v>
+      <c r="W44" t="n">
+        <v>-2.53</v>
       </c>
       <c r="Y44" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ISLEM-000044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MMCAS</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="G45" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.07.2026 20:31:47</t>
+          <t>16.07.2026 18:37:54</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>22.5</v>
+        <v>22.62</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1170,13 +1170,13 @@
         <v>29.8</v>
       </c>
       <c r="Q2" s="16" t="n">
-        <v>22.14</v>
+        <v>22.04</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>2.76</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>-23.66</v>
+        <v>-24</v>
       </c>
       <c r="T2" s="8" t="n">
         <v>13744.64</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-18.66</v>
+        <v>-18.22</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>45.6</v>
+        <v>46.48</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-22.92</v>
+        <v>-21.43</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>184</v>
+        <v>186.6</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.61</v>
+        <v>-2.25</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.86</v>
+        <v>13.9</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.26</v>
+        <v>6.85</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>78.7</v>
+        <v>77.3</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0.64</v>
+        <v>-1.15</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.84</v>
+        <v>24.4</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-6.58</v>
+        <v>-4.39</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>39.34</v>
+        <v>39.2</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-15.03</v>
+        <v>-15.33</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.44</v>
+        <v>38.26</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-12.64</v>
+        <v>-13.05</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-1.93</v>
+        <v>-1.69</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>108.8</v>
+        <v>110.1</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-10.08</v>
+        <v>-9.01</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>202.9</v>
+        <v>200.8</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>202.9</v>
+        <v>211.8</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>57.9</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>66.18000000000001</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>21.68</v>
+        <v>23.84</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>24.24</v>
+        <v>36.62</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>84.05</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>30.41</v>
+        <v>23.97</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,14 +2279,14 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>135</v>
+        <v>133.5</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>8.869999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>141.5</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>11.96</v>
+        <v>10.75</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>83.05</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-14.4</v>
+        <v>-13.94</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-5.17</v>
+        <v>-6.61</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>18.02</v>
+        <v>18.46</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-4.1</v>
+        <v>-1.76</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.65</v>
+        <v>6.76</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-5.41</v>
+        <v>-3.84</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.5</v>
+        <v>4.39</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-7.98</v>
+        <v>-10.22</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-12.12</v>
+        <v>-11.62</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,23 +2836,23 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>29.5</v>
+        <v>32.44</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>-1.67</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>32.3</v>
+        <v>32.44</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>29.04</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>7.67</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="S23" s="5" t="n">
         <v>-3.2</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-1.67</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2947,7 +2947,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.51</v>
+        <v>-1.31</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.68</v>
+        <v>18.9</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>100.4</v>
+        <v>99.55</v>
       </c>
       <c r="N26" t="n">
-        <v>1.36</v>
+        <v>0.5</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>0.5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.02</v>
+        <v>20.76</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3179,7 +3179,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>0.15</v>
+        <v>3.85</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3262,7 +3262,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>-2.8</v>
+        <v>-0.89</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3345,7 +3345,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.109999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3428,7 +3428,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.529999999999999</v>
+        <v>-6.85</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>84.05</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3511,7 +3511,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>2.99</v>
+        <v>-2.1</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3594,7 +3594,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-1.84</v>
+        <v>-1.05</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3633,13 +3633,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4</v>
+        <v>1.38</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.4</v>
+        <v>1.38</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.9</v>
+        <v>8.93</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3746,7 +3746,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>4.46</v>
+        <v>4.81</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>15.45</v>
+        <v>16.76</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3805,13 +3805,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>16.38</v>
+        <v>16.89</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>5.68</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3829,7 +3829,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>4.96</v>
+        <v>13.86</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>220.4</v>
+        <v>222.1</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3912,7 +3912,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>1.36</v>
+        <v>2.14</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>18.75</v>
+        <v>18.95</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3995,7 +3995,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>3.42</v>
+        <v>4.52</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4078,7 +4078,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-1.11</v>
+        <v>0.11</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4117,22 +4117,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>95.59999999999999</v>
+        <v>102.7</v>
       </c>
       <c r="N39" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P39" t="n">
-        <v>95.7</v>
+        <v>102.8</v>
       </c>
       <c r="Q39" t="n">
         <v>87.5</v>
       </c>
       <c r="R39" t="n">
-        <v>6.51</v>
+        <v>14.41</v>
       </c>
       <c r="S39" t="n">
         <v>-2.62</v>
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>18.02</v>
+        <v>18.46</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4230,7 +4230,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-5.11</v>
+        <v>-2.79</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>276.5</v>
+        <v>272.25</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4292,13 +4292,13 @@
         <v>361.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>276.5</v>
+        <v>265.5</v>
       </c>
       <c r="R41" t="n">
         <v>13.6</v>
       </c>
       <c r="S41" t="n">
-        <v>-13.05</v>
+        <v>-16.51</v>
       </c>
       <c r="T41" t="n">
         <v>14274.02</v>
@@ -4313,7 +4313,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>-8.470000000000001</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4348,29 +4348,40 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J42" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-2</v>
+        <v>26.44</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-4.99</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P42" t="n">
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>27.18</v>
+        <v>26.16</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-3.14</v>
+        <v>-6.77</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4382,7 +4393,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>-2</v>
+        <v>-4.99</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-0.83</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4421,13 +4435,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>107.1</v>
+        <v>105.5</v>
       </c>
       <c r="N43" t="n">
-        <v>6.04</v>
+        <v>4.46</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
         <v>108.1</v>
@@ -4451,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>6.04</v>
+        <v>4.46</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4490,13 +4504,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>13.86</v>
+        <v>13.9</v>
       </c>
       <c r="N44" t="n">
-        <v>-2.53</v>
+        <v>-2.25</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
         <v>14.22</v>
@@ -4520,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>-2.53</v>
+        <v>-2.25</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4559,22 +4573,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>60.55</v>
+        <v>65</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>60.55</v>
+        <v>65</v>
       </c>
       <c r="Q45" t="n">
         <v>60.55</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4582,7 +4596,136 @@
       <c r="T45" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U45" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>7.35</v>
+      </c>
       <c r="Y45" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ISLEM-000045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>90</v>
+      </c>
+      <c r="G46" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>90</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>90</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ISLEM-000046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ULUUN</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="G47" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.07.2026 18:37:54</t>
+          <t>17.07.2026 23:20:29</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>22.62</v>
+        <v>22.58</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-18.22</v>
+        <v>-18.37</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>46.48</v>
+        <v>44.96</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-21.43</v>
+        <v>-24</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>186.6</v>
+        <v>185</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-2.25</v>
+        <v>-3.09</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.9</v>
+        <v>13.76</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>77.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-1.15</v>
+        <v>2.17</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>24.4</v>
+        <v>24.36</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-4.39</v>
+        <v>-4.55</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>39.2</v>
+        <v>38.22</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>38.92</v>
+        <v>38.18</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-20.15</v>
+        <v>-21.67</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-15.33</v>
+        <v>-17.45</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.26</v>
+        <v>38.56</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-13.05</v>
+        <v>-12.36</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.15</v>
+        <v>8.17</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-1.69</v>
+        <v>-1.45</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>110.1</v>
+        <v>104.9</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-9.01</v>
+        <v>-13.31</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>200.8</v>
+        <v>215.5</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>211.8</v>
+        <v>220.8</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>64.81999999999999</v>
+        <v>71.83</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>64.45999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>23.84</v>
+        <v>24.94</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2135,13 +2135,13 @@
         <v>4</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>24.2</v>
+        <v>26.22</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>16.14</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>31.74</v>
+        <v>42.73</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>-12.14</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>36.62</v>
+        <v>42.92</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>23.97</v>
+        <v>12.49</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2279,23 +2279,23 @@
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="8" t="n">
-        <v>133.5</v>
+        <v>145.5</v>
       </c>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n">
-        <v>7.66</v>
+        <v>17.34</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>141.5</v>
+        <v>145.5</v>
       </c>
       <c r="Q16" s="8" t="n">
         <v>121.4</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>14.11</v>
+        <v>17.34</v>
       </c>
       <c r="S16" s="8" t="n">
         <v>-2.1</v>
@@ -2310,7 +2310,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>10.75</v>
+        <v>20.43</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>83.05</v>
+        <v>82.05</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2392,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-13.94</v>
+        <v>-14.97</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2473,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-6.61</v>
+        <v>-7.85</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>18.46</v>
+        <v>17.96</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2554,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-1.76</v>
+        <v>-4.42</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.76</v>
+        <v>6.51</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2614,13 +2614,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.64</v>
+        <v>6.49</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-10.27</v>
+        <v>-12.3</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2635,7 +2635,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-3.84</v>
+        <v>-7.4</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.39</v>
+        <v>4.57</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2716,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-10.22</v>
+        <v>-6.54</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2797,7 +2797,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-11.62</v>
+        <v>-10.1</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2836,23 +2836,23 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="n">
-        <v>32.44</v>
+        <v>34.24</v>
       </c>
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>14.13</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>32.44</v>
+        <v>34.98</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>29.04</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="S23" s="5" t="n">
         <v>-3.2</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>14.13</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5030</v>
+        <v>4955</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2926,13 +2926,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4965</v>
+        <v>4945</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.46</v>
+        <v>-7.83</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2947,7 +2947,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.31</v>
+        <v>-2.78</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.9</v>
+        <v>18.19</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3009,13 +3009,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>18.67</v>
+        <v>18.18</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.39</v>
+        <v>-9.82</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>99.55</v>
+        <v>98.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="O26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.76</v>
+        <v>20.8</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3179,7 +3179,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15.6</v>
+        <v>15.83</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3262,7 +3262,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.89</v>
+        <v>0.57</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3345,7 +3345,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.380000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3428,7 +3428,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-6.85</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>79.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3511,7 +3511,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-2.1</v>
+        <v>-11.16</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3594,7 +3594,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-1.05</v>
+        <v>-3.68</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3633,25 +3633,25 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>51.3</v>
+        <v>50.25</v>
       </c>
       <c r="N33" t="n">
-        <v>1.38</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>50.45</v>
+        <v>49.12</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.3</v>
+        <v>-2.92</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.38</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3746,7 +3746,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>4.81</v>
+        <v>4.93</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>16.76</v>
+        <v>18.3</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3805,13 +3805,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>16.89</v>
+        <v>18.3</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>8.970000000000001</v>
+        <v>18.06</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3829,7 +3829,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>13.86</v>
+        <v>24.32</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>222.1</v>
+        <v>221.8</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3912,7 +3912,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>18.95</v>
+        <v>19.63</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3971,13 +3971,13 @@
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>19.65</v>
+        <v>20</v>
       </c>
       <c r="Q37" t="n">
         <v>17.32</v>
       </c>
       <c r="R37" t="n">
-        <v>2.99</v>
+        <v>4.82</v>
       </c>
       <c r="S37" t="n">
         <v>-9.220000000000001</v>
@@ -3995,7 +3995,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>4.52</v>
+        <v>8.27</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>330</v>
+        <v>329.5</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4078,7 +4078,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4117,22 +4117,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>102.7</v>
+        <v>106</v>
       </c>
       <c r="N39" t="n">
-        <v>14.3</v>
+        <v>17.97</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P39" t="n">
-        <v>102.8</v>
+        <v>106.7</v>
       </c>
       <c r="Q39" t="n">
         <v>87.5</v>
       </c>
       <c r="R39" t="n">
-        <v>14.41</v>
+        <v>18.75</v>
       </c>
       <c r="S39" t="n">
         <v>-2.62</v>
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>14.3</v>
+        <v>17.97</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>18.46</v>
+        <v>17.96</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4209,13 +4209,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>18.01</v>
+        <v>17.82</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-9.9</v>
+        <v>-10.86</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4230,7 +4230,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-2.79</v>
+        <v>-5.42</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>272.25</v>
+        <v>282</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4292,13 +4292,13 @@
         <v>361.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>265.5</v>
+        <v>262.25</v>
       </c>
       <c r="R41" t="n">
         <v>13.6</v>
       </c>
       <c r="S41" t="n">
-        <v>-16.51</v>
+        <v>-17.53</v>
       </c>
       <c r="T41" t="n">
         <v>14274.02</v>
@@ -4313,7 +4313,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>-9.880000000000001</v>
+        <v>-6.65</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>26.44</v>
+        <v>25.1</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4375,13 +4375,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>26.16</v>
+        <v>25.1</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-6.77</v>
+        <v>-10.55</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4396,7 +4396,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-0.83</v>
+        <v>-5.85</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4435,13 +4435,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>105.5</v>
+        <v>104.7</v>
       </c>
       <c r="N43" t="n">
-        <v>4.46</v>
+        <v>3.66</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
         <v>108.1</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>4.46</v>
+        <v>3.66</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4500,29 +4500,40 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="n">
+        <v>46220</v>
+      </c>
+      <c r="J44" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-2.25</v>
+        <v>13.76</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-4.99</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-3.59</v>
+        <v>-5.06</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4534,7 +4545,10 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>-2.25</v>
+        <v>-4.99</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.85</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4573,22 +4587,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>7.35</v>
+        <v>8.34</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q45" t="n">
         <v>60.55</v>
       </c>
       <c r="R45" t="n">
-        <v>7.35</v>
+        <v>8.34</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4603,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>7.35</v>
+        <v>8.34</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4642,28 +4656,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>90</v>
+        <v>87.55</v>
       </c>
       <c r="N46" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="T46" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U46" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V46" t="n">
         <v>0</v>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>90</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>14274.02</v>
+      <c r="W46" t="n">
+        <v>-2.72</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4702,30 +4725,99 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="N47" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="T47" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U47" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V47" t="n">
         <v>0</v>
       </c>
-      <c r="O47" t="n">
+      <c r="W47" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ISLEM-000047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MOGAN</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N48" t="n">
         <v>0</v>
       </c>
-      <c r="P47" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="R47" t="n">
+      <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="n">
+      <c r="P48" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="T47" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y47" t="inlineStr">
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.07.2026 23:20:29</t>
+          <t>21.07.2026 09:07:57</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>22.58</v>
+        <v>23.8</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1170,13 +1170,13 @@
         <v>29.8</v>
       </c>
       <c r="Q2" s="16" t="n">
-        <v>22.04</v>
+        <v>22</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>2.76</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>-24</v>
+        <v>-24.14</v>
       </c>
       <c r="T2" s="8" t="n">
         <v>13744.64</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-18.37</v>
+        <v>-13.96</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>44.96</v>
+        <v>46</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-24</v>
+        <v>-22.24</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.76</v>
+        <v>13.5</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.5</v>
+        <v>5.93</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>78.05</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>2.17</v>
+        <v>-0.19</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>24.36</v>
+        <v>25</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-4.55</v>
+        <v>-2.04</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>38.22</v>
+        <v>37.5</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>38.18</v>
+        <v>37.42</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-21.67</v>
+        <v>-23.23</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-17.45</v>
+        <v>-19.01</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.56</v>
+        <v>36.5</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1814,13 +1814,13 @@
         <v>46.74</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>37.48</v>
+        <v>35.66</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.91</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>-19.08</v>
+        <v>-23.01</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>14493.09</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-12.36</v>
+        <v>-17.05</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.17</v>
+        <v>8.19</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-1.45</v>
+        <v>-1.21</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>104.9</v>
+        <v>105.3</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-13.31</v>
+        <v>-12.98</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>215.5</v>
+        <v>215.1</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>220.8</v>
+        <v>226</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>71.83</v>
+        <v>75.88</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>76.48999999999999</v>
+        <v>76.17</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24.94</v>
+        <v>25</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>42.92</v>
+        <v>43.27</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>72.5</v>
+        <v>69</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>12.49</v>
+        <v>7.06</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2272,21 +2272,29 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="9" t="n"/>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
+        </is>
+      </c>
       <c r="L16" s="8" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n">
-        <v>17.34</v>
-      </c>
+        <v>131.6</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P16" s="8" t="n">
         <v>145.5</v>
@@ -2310,7 +2318,7 @@
         <v>-3.09</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>20.43</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="9" t="n"/>
@@ -2358,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>82.05</v>
+        <v>83.3</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2392,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-14.97</v>
+        <v>-13.68</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2439,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2473,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-7.85</v>
+        <v>-6.82</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2520,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17.96</v>
+        <v>17.91</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2554,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-4.42</v>
+        <v>-4.68</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2601,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.51</v>
+        <v>6.82</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2614,13 +2622,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.49</v>
+        <v>6.47</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-12.3</v>
+        <v>-12.57</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2635,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-7.4</v>
+        <v>-2.99</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2682,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.57</v>
+        <v>4.51</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2716,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-6.54</v>
+        <v>-7.77</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2763,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2797,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-10.1</v>
+        <v>-11.11</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2829,30 +2837,38 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="6" t="n"/>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
+        </is>
+      </c>
       <c r="L23" s="5" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n">
-        <v>14.13</v>
-      </c>
+        <v>33.42</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>34.98</v>
+        <v>35.48</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>29.04</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>16.6</v>
+        <v>18.27</v>
       </c>
       <c r="S23" s="5" t="n">
         <v>-3.2</v>
@@ -2867,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>14.13</v>
+        <v>11.4</v>
       </c>
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="6" t="n"/>
@@ -2914,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4955</v>
+        <v>4920</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2926,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4945</v>
+        <v>4920</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.83</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2947,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.78</v>
+        <v>-3.47</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2997,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.19</v>
+        <v>18.34</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3009,13 +3025,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>18.18</v>
+        <v>18.08</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.82</v>
+        <v>-10.32</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3066,13 +3082,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>98.7</v>
+        <v>98.45</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
@@ -3096,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3146,7 +3162,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.8</v>
+        <v>21.16</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3155,13 +3171,13 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>21.26</v>
+        <v>21.42</v>
       </c>
       <c r="Q27" t="n">
         <v>19.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="S27" t="n">
         <v>-7.7</v>
@@ -3179,7 +3195,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>4.05</v>
+        <v>5.85</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3229,7 +3245,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15.83</v>
+        <v>15.99</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3262,7 +3278,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0.57</v>
+        <v>1.59</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3312,7 +3328,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.97</v>
+        <v>4.89</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3324,13 +3340,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-7.02</v>
+        <v>-7.97</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3345,7 +3361,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.8</v>
+        <v>-2.4</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3395,7 +3411,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.210000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3407,13 +3423,13 @@
         <v>10.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R30" t="n">
         <v>-1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>-15.09</v>
+        <v>-15.38</v>
       </c>
       <c r="T30" t="n">
         <v>14274.02</v>
@@ -3428,7 +3444,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-8.539999999999999</v>
+        <v>-10.92</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3478,7 +3494,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>72.5</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3490,13 +3506,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-19.09</v>
+        <v>-19.67</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3511,7 +3527,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-11.16</v>
+        <v>-15.45</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3561,7 +3577,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3573,13 +3589,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-8.5</v>
+        <v>-9.5</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3594,7 +3610,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-3.68</v>
+        <v>-4.21</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3633,13 +3649,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>50.25</v>
+        <v>49.96</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.26</v>
       </c>
       <c r="O33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
@@ -3663,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.26</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3713,7 +3729,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.94</v>
+        <v>8.69</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3746,7 +3762,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>4.93</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3796,7 +3812,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>18.3</v>
+        <v>18.85</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3805,13 +3821,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>18.3</v>
+        <v>19.19</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>18.06</v>
+        <v>23.81</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3829,7 +3845,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>24.32</v>
+        <v>28.06</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3879,7 +3895,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>221.8</v>
+        <v>220.2</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3912,7 +3928,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3962,7 +3978,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>19.63</v>
+        <v>17.91</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3995,7 +4011,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>8.27</v>
+        <v>-1.21</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4045,7 +4061,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>329.5</v>
+        <v>328</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4078,7 +4094,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.05</v>
+        <v>-0.5</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4123,16 +4139,16 @@
         <v>17.97</v>
       </c>
       <c r="O39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P39" t="n">
-        <v>106.7</v>
+        <v>109.2</v>
       </c>
       <c r="Q39" t="n">
         <v>87.5</v>
       </c>
       <c r="R39" t="n">
-        <v>18.75</v>
+        <v>21.54</v>
       </c>
       <c r="S39" t="n">
         <v>-2.62</v>
@@ -4197,7 +4213,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>17.96</v>
+        <v>17.91</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4230,7 +4246,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-5.42</v>
+        <v>-5.69</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4280,7 +4296,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4313,7 +4329,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>-6.65</v>
+        <v>2.62</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4363,7 +4379,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.1</v>
+        <v>24.4</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4375,13 +4391,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>25.1</v>
+        <v>24.32</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-10.55</v>
+        <v>-13.33</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4396,7 +4412,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-5.85</v>
+        <v>-8.48</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4435,22 +4451,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>104.7</v>
+        <v>109.5</v>
       </c>
       <c r="N43" t="n">
-        <v>3.66</v>
+        <v>8.42</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>108.1</v>
+        <v>111</v>
       </c>
       <c r="Q43" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="R43" t="n">
-        <v>7.03</v>
+        <v>9.9</v>
       </c>
       <c r="S43" t="n">
         <v>-1.39</v>
@@ -4465,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.66</v>
+        <v>8.42</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4515,7 +4531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>13.76</v>
+        <v>13.5</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4527,13 +4543,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.5</v>
+        <v>13.49</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-5.06</v>
+        <v>-5.13</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4548,7 +4564,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>1.85</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4587,22 +4603,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>65.59999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="N45" t="n">
-        <v>8.34</v>
+        <v>12.22</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P45" t="n">
-        <v>65.59999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="Q45" t="n">
         <v>60.55</v>
       </c>
       <c r="R45" t="n">
-        <v>8.34</v>
+        <v>12.22</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4617,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>8.34</v>
+        <v>12.22</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4656,25 +4672,25 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>87.55</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>-2.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>90.2</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>87.25</v>
+        <v>86.95</v>
       </c>
       <c r="R46" t="n">
-        <v>0.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S46" t="n">
-        <v>-3.06</v>
+        <v>-3.39</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4686,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>-2.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4721,29 +4737,40 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J47" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="N47" t="n">
-        <v>-0.2</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-4.99</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>9.859999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>9.65</v>
+        <v>9.23</v>
       </c>
       <c r="R47" t="n">
-        <v>0.51</v>
+        <v>1.63</v>
       </c>
       <c r="S47" t="n">
-        <v>-1.63</v>
+        <v>-5.91</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4755,7 +4782,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>-0.2</v>
+        <v>-4.99</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.64</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4794,30 +4824,99 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>18.3</v>
+        <v>18.85</v>
       </c>
       <c r="N48" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3</v>
+      </c>
+      <c r="P48" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="T48" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U48" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V48" t="n">
         <v>0</v>
       </c>
-      <c r="O48" t="n">
+      <c r="W48" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ISLEM-000048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>POLHO</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N49" t="n">
         <v>0</v>
       </c>
-      <c r="P48" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="R48" t="n">
+      <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="n">
+      <c r="P49" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="T48" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y48" t="inlineStr">
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.07.2026 09:07:57</t>
+          <t>22.07.2026 19:29:43</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y49"/>
+  <dimension ref="A1:Y50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.8</v>
+        <v>24.02</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-13.96</v>
+        <v>-13.16</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>46</v>
+        <v>46.26</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-22.24</v>
+        <v>-21.81</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.09</v>
+        <v>-2.04</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.5</v>
+        <v>13.09</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5.93</v>
+        <v>6.33</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>78.05</v>
+        <v>72.2</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-0.19</v>
+        <v>-7.67</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>25</v>
+        <v>24.26</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-2.04</v>
+        <v>-4.94</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>37.5</v>
+        <v>37.16</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>37.42</v>
+        <v>37.08</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-23.23</v>
+        <v>-23.92</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-19.01</v>
+        <v>-19.74</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>36.5</v>
+        <v>38.28</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-17.05</v>
+        <v>-13</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.19</v>
+        <v>8.01</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>8.039999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-7.9</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-1.21</v>
+        <v>-3.38</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>105.3</v>
+        <v>106.8</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-12.98</v>
+        <v>-11.74</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>215.1</v>
+        <v>221.3</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>76.17</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>43.27</v>
+        <v>40.4</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>69</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>7.06</v>
+        <v>21.26</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>131.6</v>
+        <v>131.5</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>83.3</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-13.68</v>
+        <v>-14.66</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-6.82</v>
+        <v>-7.85</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17.91</v>
+        <v>17.28</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17.49</v>
+        <v>17.2</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-11.58</v>
+        <v>-13.04</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-4.68</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.82</v>
+        <v>6.77</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-2.99</v>
+        <v>-3.7</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.51</v>
+        <v>4.38</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>4.1</v>
+        <v>3.93</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-20.39</v>
+        <v>-23.69</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-7.77</v>
+        <v>-10.43</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>33.42</v>
+        <v>32.82</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4920</v>
+        <v>4862.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4920</v>
+        <v>4862.5</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.289999999999999</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.47</v>
+        <v>-4.6</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.34</v>
+        <v>18.07</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3025,13 +3025,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>18.08</v>
+        <v>18.05</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.32</v>
+        <v>-10.47</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>98.45</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.61</v>
+        <v>-1.21</v>
       </c>
       <c r="O26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.61</v>
+        <v>-1.21</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.16</v>
+        <v>22.12</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3171,13 +3171,13 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>21.42</v>
+        <v>22.48</v>
       </c>
       <c r="Q27" t="n">
         <v>19.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.81</v>
+        <v>6.84</v>
       </c>
       <c r="S27" t="n">
         <v>-7.7</v>
@@ -3195,7 +3195,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>5.85</v>
+        <v>10.66</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3278,7 +3278,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>1.59</v>
+        <v>0.95</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.89</v>
+        <v>4.73</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3340,13 +3340,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.85</v>
+        <v>4.72</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-7.97</v>
+        <v>-10.44</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3361,7 +3361,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-2.4</v>
+        <v>-5.59</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.970000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3423,13 +3423,13 @@
         <v>10.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.970000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R30" t="n">
         <v>-1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>-15.38</v>
+        <v>-16.98</v>
       </c>
       <c r="T30" t="n">
         <v>14274.02</v>
@@ -3444,7 +3444,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.92</v>
+        <v>-11.62</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3527,7 +3527,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-15.45</v>
+        <v>-4.24</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3589,13 +3589,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>3.51</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-9.5</v>
+        <v>-12.25</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3610,7 +3610,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-4.21</v>
+        <v>-6.32</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3649,13 +3649,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>49.96</v>
+        <v>49.84</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.26</v>
+        <v>-1.5</v>
       </c>
       <c r="O33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.26</v>
+        <v>-1.5</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.69</v>
+        <v>8.85</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3762,7 +3762,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>2</v>
+        <v>3.87</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>18.85</v>
+        <v>18</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3821,13 +3821,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>19.19</v>
+        <v>19.65</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>23.81</v>
+        <v>26.77</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3845,7 +3845,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>28.06</v>
+        <v>22.28</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>220.2</v>
+        <v>222.5</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3928,7 +3928,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>17.91</v>
+        <v>14.51</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3990,13 +3990,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>17.32</v>
+        <v>14.51</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-9.220000000000001</v>
+        <v>-23.95</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4011,7 +4011,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-1.21</v>
+        <v>-19.97</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4073,13 +4073,13 @@
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>321.5</v>
+        <v>314.5</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-7.35</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -4094,7 +4094,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.5</v>
+        <v>-2.62</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4133,22 +4133,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="N39" t="n">
-        <v>17.97</v>
+        <v>29.1</v>
       </c>
       <c r="O39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P39" t="n">
-        <v>109.2</v>
+        <v>117.5</v>
       </c>
       <c r="Q39" t="n">
         <v>87.5</v>
       </c>
       <c r="R39" t="n">
-        <v>21.54</v>
+        <v>30.77</v>
       </c>
       <c r="S39" t="n">
         <v>-2.62</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>17.97</v>
+        <v>29.1</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>17.91</v>
+        <v>17.28</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4225,13 +4225,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>17.82</v>
+        <v>17.2</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-10.86</v>
+        <v>-13.96</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4246,7 +4246,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-5.69</v>
+        <v>-9</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>310</v>
+        <v>297.25</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4329,7 +4329,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>2.62</v>
+        <v>-1.61</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>24.4</v>
+        <v>23.92</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4391,13 +4391,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.32</v>
+        <v>23.76</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-13.33</v>
+        <v>-15.32</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4412,7 +4412,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-8.48</v>
+        <v>-10.28</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4451,13 +4451,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>109.5</v>
+        <v>104.3</v>
       </c>
       <c r="N43" t="n">
-        <v>8.42</v>
+        <v>3.27</v>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4481,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>8.42</v>
+        <v>3.27</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>13.5</v>
+        <v>13.09</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4543,13 +4543,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.49</v>
+        <v>12.84</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-5.13</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4564,7 +4564,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.11</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4603,22 +4603,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>67.95</v>
+        <v>73</v>
       </c>
       <c r="N45" t="n">
-        <v>12.22</v>
+        <v>20.56</v>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>67.95</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Q45" t="n">
         <v>60.55</v>
       </c>
       <c r="R45" t="n">
-        <v>12.22</v>
+        <v>22.87</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>12.22</v>
+        <v>20.56</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4672,22 +4672,22 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>90.84999999999999</v>
+        <v>92</v>
       </c>
       <c r="N46" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>90.84999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="Q46" t="n">
         <v>86.95</v>
       </c>
       <c r="R46" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.89</v>
       </c>
       <c r="S46" t="n">
         <v>-3.39</v>
@@ -4702,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.380000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4764,13 +4764,13 @@
         <v>9.970000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>9.23</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="R47" t="n">
         <v>1.63</v>
       </c>
       <c r="S47" t="n">
-        <v>-5.91</v>
+        <v>-9.68</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4785,7 +4785,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>0.64</v>
+        <v>3.86</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4824,22 +4824,22 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>18.85</v>
+        <v>18</v>
       </c>
       <c r="N48" t="n">
-        <v>3.01</v>
+        <v>-1.64</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P48" t="n">
-        <v>19.19</v>
+        <v>19.65</v>
       </c>
       <c r="Q48" t="n">
         <v>17.59</v>
       </c>
       <c r="R48" t="n">
-        <v>4.86</v>
+        <v>7.38</v>
       </c>
       <c r="S48" t="n">
         <v>-3.88</v>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3.01</v>
+        <v>-1.64</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4893,30 +4893,99 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>21.9</v>
+        <v>22.12</v>
       </c>
       <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="T49" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U49" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V49" t="n">
         <v>0</v>
       </c>
-      <c r="O49" t="n">
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ISLEM-000049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HDFGS</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N50" t="n">
         <v>0</v>
       </c>
-      <c r="P49" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R49" t="n">
+      <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="n">
+      <c r="P50" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="T49" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y49" t="inlineStr">
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.07.2026 19:29:43</t>
+          <t>23.07.2026 20:34:36</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>24.02</v>
+        <v>24.14</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-13.16</v>
+        <v>-12.73</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>46.26</v>
+        <v>47.08</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-21.81</v>
+        <v>-20.42</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>187</v>
+        <v>185.9</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-2.04</v>
+        <v>-2.62</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.09</v>
+        <v>12.98</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>72.2</v>
+        <v>71.55</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-7.67</v>
+        <v>-8.5</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>24.26</v>
+        <v>23.92</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-4.94</v>
+        <v>-6.27</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>37.16</v>
+        <v>36.44</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>37.08</v>
+        <v>36.44</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-23.92</v>
+        <v>-25.24</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-19.74</v>
+        <v>-21.3</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.28</v>
+        <v>39.48</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-13</v>
+        <v>-10.27</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>7.97</v>
+        <v>7.96</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-8.710000000000001</v>
+        <v>-8.82</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>106.8</v>
+        <v>109.3</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-11.74</v>
+        <v>-9.67</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>221.3</v>
+        <v>212.9</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>81.23999999999999</v>
+        <v>74.37</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>78.15000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>21.26</v>
+        <v>23.97</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>131.5</v>
+        <v>132.8</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>82.34999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-14.66</v>
+        <v>-14.72</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-7.85</v>
+        <v>-8.26</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17.28</v>
+        <v>17.14</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17.2</v>
+        <v>17.13</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-13.04</v>
+        <v>-13.4</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.77</v>
+        <v>6.66</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-3.7</v>
+        <v>-5.26</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.38</v>
+        <v>4.45</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-10.43</v>
+        <v>-9</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>32.82</v>
+        <v>30.54</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4862.5</v>
+        <v>4845</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4862.5</v>
+        <v>4840</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.369999999999999</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.6</v>
+        <v>-4.94</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.07</v>
+        <v>18.15</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>97.84999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.21</v>
+        <v>-1.56</v>
       </c>
       <c r="O26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.21</v>
+        <v>-1.56</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>22.12</v>
+        <v>21.54</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3195,7 +3195,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>10.66</v>
+        <v>7.75</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15.89</v>
+        <v>16.17</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3278,7 +3278,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0.95</v>
+        <v>2.73</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3340,13 +3340,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-10.44</v>
+        <v>-11.76</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3361,7 +3361,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-5.59</v>
+        <v>-6.79</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3423,13 +3423,13 @@
         <v>10.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R30" t="n">
         <v>-1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>-16.98</v>
+        <v>-17.92</v>
       </c>
       <c r="T30" t="n">
         <v>14274.02</v>
@@ -3444,7 +3444,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-11.62</v>
+        <v>-6.65</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>78.15000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3527,7 +3527,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-4.24</v>
+        <v>-2.1</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3589,13 +3589,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-12.25</v>
+        <v>-15</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3610,7 +3610,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-6.32</v>
+        <v>-10.26</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3649,13 +3649,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>49.84</v>
+        <v>50.55</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="O33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.85</v>
+        <v>8.77</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3762,7 +3762,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>3.87</v>
+        <v>2.93</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>18</v>
+        <v>17.82</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3845,7 +3845,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>22.28</v>
+        <v>21.06</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>222.5</v>
+        <v>219</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3928,7 +3928,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>2.32</v>
+        <v>0.71</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>14.51</v>
+        <v>13.06</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3990,13 +3990,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>14.51</v>
+        <v>13.06</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-23.95</v>
+        <v>-31.55</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4011,7 +4011,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-19.97</v>
+        <v>-27.96</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>321</v>
+        <v>312.75</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4073,13 +4073,13 @@
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>314.5</v>
+        <v>310.25</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-9.369999999999999</v>
+        <v>-10.59</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -4094,7 +4094,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-2.62</v>
+        <v>-5.13</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4129,17 +4129,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J39" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>116</v>
-      </c>
-      <c r="N39" t="n">
-        <v>29.1</v>
+        <v>104.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>16.19</v>
       </c>
       <c r="O39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P39" t="n">
         <v>117.5</v>
@@ -4163,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>29.1</v>
+        <v>16.19</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -4213,7 +4224,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>17.28</v>
+        <v>17.14</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4225,13 +4236,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>17.2</v>
+        <v>17.13</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-13.96</v>
+        <v>-14.31</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4246,7 +4257,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-9</v>
+        <v>-9.74</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4296,7 +4307,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>297.25</v>
+        <v>303.75</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4329,7 +4340,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.61</v>
+        <v>0.55</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4379,7 +4390,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>23.92</v>
+        <v>24.14</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4391,13 +4402,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.76</v>
+        <v>23.68</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-15.32</v>
+        <v>-15.61</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4412,7 +4423,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-10.28</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4451,13 +4462,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>104.3</v>
+        <v>103.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3.27</v>
+        <v>2.18</v>
       </c>
       <c r="O43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4481,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.27</v>
+        <v>2.18</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4531,7 +4542,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>13.09</v>
+        <v>12.98</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4543,13 +4554,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>12.84</v>
+        <v>12.61</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-9.699999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4564,7 +4575,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-3.11</v>
+        <v>-3.92</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4603,13 +4614,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>73</v>
+        <v>73.25</v>
       </c>
       <c r="N45" t="n">
-        <v>20.56</v>
+        <v>20.97</v>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P45" t="n">
         <v>74.40000000000001</v>
@@ -4633,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>20.56</v>
+        <v>20.97</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4672,13 +4683,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>92</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>2.22</v>
+        <v>1.22</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
@@ -4702,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.22</v>
+        <v>1.22</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4752,7 +4763,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.68</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4761,13 +4772,13 @@
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>9.970000000000001</v>
+        <v>10.34</v>
       </c>
       <c r="Q47" t="n">
         <v>8.859999999999999</v>
       </c>
       <c r="R47" t="n">
-        <v>1.63</v>
+        <v>5.4</v>
       </c>
       <c r="S47" t="n">
         <v>-9.68</v>
@@ -4785,7 +4796,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>3.86</v>
+        <v>4.94</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4824,25 +4835,25 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>18</v>
+        <v>17.82</v>
       </c>
       <c r="N48" t="n">
-        <v>-1.64</v>
+        <v>-2.62</v>
       </c>
       <c r="O48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P48" t="n">
         <v>19.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>17.59</v>
+        <v>17.49</v>
       </c>
       <c r="R48" t="n">
         <v>7.38</v>
       </c>
       <c r="S48" t="n">
-        <v>-3.88</v>
+        <v>-4.43</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4854,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>-1.64</v>
+        <v>-2.62</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4893,13 +4904,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.12</v>
+        <v>22.16</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
         <v>22.54</v>
@@ -4923,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -4958,32 +4969,55 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="N50" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S50" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="T50" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U50" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V50" t="n">
         <v>0</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>14274.02</v>
+      <c r="W50" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="X50" t="n">
+        <v>-0.35</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.07.2026 20:34:36</t>
+          <t>24.07.2026 20:09:51</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>24.14</v>
+        <v>24</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-12.73</v>
+        <v>-13.23</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>47.08</v>
+        <v>46</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-20.42</v>
+        <v>-22.24</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>185.9</v>
+        <v>186.3</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-2.62</v>
+        <v>-2.41</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.98</v>
+        <v>12.79</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-8.5</v>
+        <v>-10.49</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.92</v>
+        <v>23.9</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-6.27</v>
+        <v>-6.35</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>36.44</v>
+        <v>35.98</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>36.44</v>
+        <v>35.78</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-25.24</v>
+        <v>-26.59</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-21.3</v>
+        <v>-22.29</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>39.48</v>
+        <v>38.14</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-10.27</v>
+        <v>-13.32</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>8.01</v>
+        <v>7.66</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>7.96</v>
+        <v>7.65</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-8.82</v>
+        <v>-12.37</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-3.38</v>
+        <v>-7.6</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>109.3</v>
+        <v>107.3</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-9.67</v>
+        <v>-11.32</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>212.9</v>
+        <v>212.6</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>74.37</v>
+        <v>74.12</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>40.4</v>
+        <v>35.24</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>23.97</v>
+        <v>12.72</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>132.8</v>
+        <v>136</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>82.3</v>
+        <v>82</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-14.72</v>
+        <v>-15.03</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-14.34</v>
+        <v>-15.32</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-8.26</v>
+        <v>-10.74</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17.14</v>
+        <v>17.1</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17.13</v>
+        <v>16.98</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-13.4</v>
+        <v>-14.16</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.99</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.66</v>
+        <v>6.62</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-5.26</v>
+        <v>-5.83</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-9</v>
+        <v>-6.95</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-11.11</v>
+        <v>-13.13</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>30.54</v>
+        <v>30.62</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4845</v>
+        <v>4837.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4840</v>
+        <v>4782.5</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.789999999999999</v>
+        <v>-10.86</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.94</v>
+        <v>-5.09</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.15</v>
+        <v>17.75</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3025,13 +3025,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>18.05</v>
+        <v>17.62</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.47</v>
+        <v>-12.6</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3082,25 +3082,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>97.5</v>
+        <v>96.45</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.56</v>
+        <v>-2.62</v>
       </c>
       <c r="O26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>96.40000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.68</v>
+        <v>-2.83</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.56</v>
+        <v>-2.62</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.54</v>
+        <v>20.96</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3195,7 +3195,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>7.75</v>
+        <v>4.85</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.17</v>
+        <v>16.16</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3278,7 +3278,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3340,13 +3340,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-11.76</v>
+        <v>-12.33</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3361,7 +3361,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-6.79</v>
+        <v>-7.39</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3444,7 +3444,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-6.65</v>
+        <v>-2.68</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>79.90000000000001</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3527,7 +3527,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-2.1</v>
+        <v>-10.98</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3589,13 +3589,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-15</v>
+        <v>-17.5</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3610,7 +3610,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-10.26</v>
+        <v>-12.63</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3649,25 +3649,25 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>50.55</v>
+        <v>49.12</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.1</v>
+        <v>-2.92</v>
       </c>
       <c r="O33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>49.12</v>
+        <v>48.32</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-2.92</v>
+        <v>-4.51</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.1</v>
+        <v>-2.92</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.77</v>
+        <v>8.76</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3762,7 +3762,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>17.82</v>
+        <v>17.63</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3845,7 +3845,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>21.06</v>
+        <v>19.77</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3928,7 +3928,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.71</v>
+        <v>0.25</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>13.06</v>
+        <v>11.76</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3990,13 +3990,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>13.06</v>
+        <v>11.76</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-31.55</v>
+        <v>-38.36</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4011,7 +4011,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-27.96</v>
+        <v>-35.14</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>312.75</v>
+        <v>312</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4094,7 +4094,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-5.13</v>
+        <v>-5.35</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>104.4</v>
+        <v>105.8</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>17.14</v>
+        <v>17.1</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4236,13 +4236,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>17.13</v>
+        <v>16.98</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-14.31</v>
+        <v>-15.06</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4257,7 +4257,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-9.74</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>303.75</v>
+        <v>290</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4340,7 +4340,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>0.55</v>
+        <v>-4.01</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>24.14</v>
+        <v>23.88</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4423,7 +4423,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-9.449999999999999</v>
+        <v>-10.43</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>103.2</v>
+        <v>106.4</v>
       </c>
       <c r="N43" t="n">
-        <v>2.18</v>
+        <v>5.35</v>
       </c>
       <c r="O43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.18</v>
+        <v>5.35</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.98</v>
+        <v>12.79</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4554,13 +4554,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>12.61</v>
+        <v>12.5</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-11.32</v>
+        <v>-12.1</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4575,7 +4575,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-3.92</v>
+        <v>-5.33</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4614,13 +4614,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>73.25</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>20.97</v>
+        <v>19.08</v>
       </c>
       <c r="O45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P45" t="n">
         <v>74.40000000000001</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>20.97</v>
+        <v>19.08</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>91.09999999999999</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="O46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.779999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4796,7 +4796,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>4.94</v>
+        <v>-0.75</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4831,29 +4831,40 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J48" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>17.82</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-2.62</v>
+        <v>17.63</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-4.97</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
         <v>19.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>17.49</v>
+        <v>17.15</v>
       </c>
       <c r="R48" t="n">
         <v>7.38</v>
       </c>
       <c r="S48" t="n">
-        <v>-4.43</v>
+        <v>-6.28</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4865,7 +4876,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>-2.62</v>
+        <v>-4.97</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.38</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4904,25 +4918,25 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.16</v>
+        <v>21.42</v>
       </c>
       <c r="N49" t="n">
-        <v>1.19</v>
+        <v>-2.19</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
         <v>22.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>21.72</v>
+        <v>21.4</v>
       </c>
       <c r="R49" t="n">
         <v>2.92</v>
       </c>
       <c r="S49" t="n">
-        <v>-0.82</v>
+        <v>-2.28</v>
       </c>
       <c r="T49" t="n">
         <v>14274.02</v>
@@ -4934,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.19</v>
+        <v>-2.19</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -4984,7 +4998,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -4996,13 +5010,13 @@
         <v>3.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="R50" t="n">
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>-5.39</v>
+        <v>-8.08</v>
       </c>
       <c r="T50" t="n">
         <v>14274.02</v>
@@ -5017,9 +5031,129 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-0.35</v>
+        <v>-3.19</v>
       </c>
       <c r="Y50" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ISLEM-000050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IPEKE</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ISLEM-000051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PAGYO</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>163.88</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.07.2026 20:09:51</t>
+          <t>28.07.2026 08:28:22</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-13.23</v>
+        <v>-16.85</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>46</v>
+        <v>45.98</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-22.24</v>
+        <v>-22.28</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>186.3</v>
+        <v>186.7</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-2.41</v>
+        <v>-2.2</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.79</v>
+        <v>12.45</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>12.32</v>
+        <v>12.21</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-4.27</v>
+        <v>-5.13</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.47</v>
+        <v>6.25</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>70</v>
+        <v>71.5</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-10.49</v>
+        <v>-8.57</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-6.35</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>35.78</v>
+        <v>35.74</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-26.59</v>
+        <v>-26.67</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-22.29</v>
+        <v>-22.72</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>38.14</v>
+        <v>37.2</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-13.32</v>
+        <v>-15.45</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.66</v>
+        <v>7.29</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>7.65</v>
+        <v>7.29</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-12.37</v>
+        <v>-16.49</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-7.6</v>
+        <v>-12.06</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>107.3</v>
+        <v>110.5</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-11.32</v>
+        <v>-8.68</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>212.6</v>
+        <v>233.8</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>226</v>
+        <v>233.8</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>75.88</v>
+        <v>81.95</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>74.12</v>
+        <v>91.48</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>23.6</v>
+        <v>23.18</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>35.24</v>
+        <v>32.84</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>72.65000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>12.72</v>
+        <v>5.82</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>136</v>
+        <v>133.5</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>82</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-21.36</v>
+        <v>-21.46</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-15.03</v>
+        <v>-16.99</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-15.32</v>
+        <v>-17.09</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-10.74</v>
+        <v>-12.81</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17.1</v>
+        <v>16.85</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>16.98</v>
+        <v>16.85</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-14.16</v>
+        <v>-14.81</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-8.99</v>
+        <v>-10.32</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2622,13 +2622,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.47</v>
+        <v>6.42</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-12.57</v>
+        <v>-13.24</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-5.83</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.55</v>
+        <v>4.37</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-6.95</v>
+        <v>-10.63</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2784,13 +2784,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-16.59</v>
+        <v>-18.05</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-13.13</v>
+        <v>-14.14</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>30.62</v>
+        <v>30.04</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4837.5</v>
+        <v>4705</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4782.5</v>
+        <v>4700</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-10.86</v>
+        <v>-12.4</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.09</v>
+        <v>-7.69</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.75</v>
+        <v>17.66</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3025,13 +3025,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>17.62</v>
+        <v>17.54</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-12.6</v>
+        <v>-13</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3078,29 +3078,40 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>46230</v>
+      </c>
+      <c r="J26" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>96.45</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-2.62</v>
+        <v>93.75</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-5</v>
       </c>
       <c r="O26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P26" t="n">
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>96.25</v>
+        <v>93.7</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.83</v>
+        <v>-5.4</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3112,7 +3123,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.62</v>
+        <v>-5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.37</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3162,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.96</v>
+        <v>20.92</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3195,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3245,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.16</v>
+        <v>16.08</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3278,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>2.67</v>
+        <v>2.16</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3328,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3361,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-7.39</v>
+        <v>-7.19</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3411,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3444,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-2.68</v>
+        <v>-7.05</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3494,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>72.65000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3506,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>69</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-19.67</v>
+        <v>-20.66</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3527,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.98</v>
+        <v>-16.43</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3577,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3610,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-12.63</v>
+        <v>-12.37</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3645,29 +3659,40 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>46230</v>
+      </c>
+      <c r="J33" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-2.92</v>
+        <v>48.26</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-5</v>
       </c>
       <c r="O33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P33" t="n">
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>48.32</v>
+        <v>47.98</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-4.51</v>
+        <v>-5.18</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3679,7 +3704,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>-2.92</v>
+        <v>-5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.4</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3729,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.76</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3741,13 +3769,13 @@
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.4</v>
+        <v>8.26</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-6.35</v>
+        <v>-7.92</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3762,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>2.82</v>
+        <v>-1.88</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3812,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>17.63</v>
+        <v>17.21</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3845,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>19.77</v>
+        <v>16.92</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3895,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>218</v>
+        <v>218.1</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3907,13 +3935,13 @@
         <v>231.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>217</v>
+        <v>216.4</v>
       </c>
       <c r="R36" t="n">
         <v>0.96</v>
       </c>
       <c r="S36" t="n">
-        <v>-5.2</v>
+        <v>-5.46</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
@@ -3928,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3978,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>11.76</v>
+        <v>10.59</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -3990,13 +4018,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>11.76</v>
+        <v>10.59</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-38.36</v>
+        <v>-44.5</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4011,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-35.14</v>
+        <v>-41.59</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4061,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4094,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-5.35</v>
+        <v>-3.53</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4144,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>105.8</v>
+        <v>106.4</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4224,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>17.1</v>
+        <v>16.85</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4236,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>16.98</v>
+        <v>16.85</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-15.06</v>
+        <v>-15.71</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4257,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-9.949999999999999</v>
+        <v>-11.27</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4307,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4340,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>-4.01</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4390,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>23.88</v>
+        <v>23.7</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4402,13 +4430,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.68</v>
+        <v>23.64</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-15.61</v>
+        <v>-15.75</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4423,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-10.43</v>
+        <v>-11.1</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4462,13 +4490,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>106.4</v>
+        <v>106.5</v>
       </c>
       <c r="N43" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="O43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4492,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4542,7 +4570,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.79</v>
+        <v>12.45</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4554,13 +4582,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>12.5</v>
+        <v>12.21</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-12.1</v>
+        <v>-14.14</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4575,7 +4603,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-5.33</v>
+        <v>-7.85</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4614,22 +4642,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>72.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>19.08</v>
+        <v>27</v>
       </c>
       <c r="O45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P45" t="n">
-        <v>74.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="Q45" t="n">
         <v>60.55</v>
       </c>
       <c r="R45" t="n">
-        <v>22.87</v>
+        <v>30.47</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4644,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>19.08</v>
+        <v>27</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4683,13 +4711,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>91.15000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>1.28</v>
+        <v>-1</v>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
@@ -4713,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.28</v>
+        <v>-1</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4763,7 +4791,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.25</v>
+        <v>8.75</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4775,13 +4803,13 @@
         <v>10.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>8.859999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="R47" t="n">
         <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>-9.68</v>
+        <v>-11.21</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4796,7 +4824,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-0.75</v>
+        <v>-6.12</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4846,7 +4874,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>17.63</v>
+        <v>17.21</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4858,13 +4886,13 @@
         <v>19.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>17.15</v>
+        <v>17.02</v>
       </c>
       <c r="R48" t="n">
         <v>7.38</v>
       </c>
       <c r="S48" t="n">
-        <v>-6.28</v>
+        <v>-6.99</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4879,7 +4907,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>1.38</v>
+        <v>-1.04</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4914,29 +4942,40 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="n">
+        <v>46230</v>
+      </c>
+      <c r="J49" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-2.19</v>
+        <v>20.78</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-5.02</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P49" t="n">
         <v>22.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>21.4</v>
+        <v>20.74</v>
       </c>
       <c r="R49" t="n">
         <v>2.92</v>
       </c>
       <c r="S49" t="n">
-        <v>-2.28</v>
+        <v>-5.3</v>
       </c>
       <c r="T49" t="n">
         <v>14274.02</v>
@@ -4948,7 +4987,10 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>-2.19</v>
+        <v>-5.02</v>
+      </c>
+      <c r="X49" t="n">
+        <v>-0.1</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -4998,7 +5040,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5010,13 +5052,13 @@
         <v>3.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="R50" t="n">
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>-8.08</v>
+        <v>-11.11</v>
       </c>
       <c r="T50" t="n">
         <v>14274.02</v>
@@ -5031,7 +5073,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-3.19</v>
+        <v>-5.67</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5070,28 +5112,37 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>100.3</v>
+        <v>97.25</v>
       </c>
       <c r="N51" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S51" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="T51" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U51" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V51" t="n">
         <v>0</v>
       </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>14274.02</v>
+      <c r="W51" t="n">
+        <v>-3.04</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5130,30 +5181,99 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>172.5</v>
+        <v>168.1</v>
       </c>
       <c r="N52" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S52" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="T52" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U52" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V52" t="n">
         <v>0</v>
       </c>
-      <c r="O52" t="n">
+      <c r="W52" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ISLEM-000052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KRONT</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>GUCLU AL</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="N53" t="n">
         <v>0</v>
       </c>
-      <c r="P52" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="R52" t="n">
+      <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="n">
+      <c r="P53" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="T52" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y52" t="inlineStr">
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28.07.2026 08:28:22</t>
+          <t>28.07.2026 23:06:35</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-16.85</v>
+        <v>-17.21</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>45.98</v>
+        <v>43.26</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>44.3</v>
+        <v>43.26</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-28.85</v>
+        <v>-30.52</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-22.28</v>
+        <v>-26.88</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>186.7</v>
+        <v>183.5</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-2.2</v>
+        <v>-3.88</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.45</v>
+        <v>12.31</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>71.5</v>
+        <v>67</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1571,13 +1571,13 @@
         <v>85.95</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>68.55</v>
+        <v>66.3</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>4.43</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-16.71</v>
+        <v>-19.44</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>13743.5</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-8.57</v>
+        <v>-14.32</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.48</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>35.78</v>
+        <v>36.6</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>35.74</v>
+        <v>35.64</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-26.67</v>
+        <v>-26.88</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-22.72</v>
+        <v>-20.95</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>37.2</v>
+        <v>36.5</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-15.45</v>
+        <v>-17.05</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.29</v>
+        <v>6.99</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>7.29</v>
+        <v>6.95</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-16.49</v>
+        <v>-20.39</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-12.06</v>
+        <v>-15.68</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>110.5</v>
+        <v>107.3</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-8.68</v>
+        <v>-11.32</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>233.8</v>
+        <v>220</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2054,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>233.8</v>
+        <v>238.3</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>118.5</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>81.95</v>
+        <v>85.45</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>-7.78</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>91.48</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>23.18</v>
+        <v>25.02</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>32.84</v>
+        <v>43.38</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>68.2</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>5.82</v>
+        <v>4.97</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>80.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>79.8</v>
+        <v>78.55</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-21.46</v>
+        <v>-22.69</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-16.99</v>
+        <v>-17.51</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-17.09</v>
+        <v>-19.06</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-12.81</v>
+        <v>-14.46</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.85</v>
+        <v>16.8</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>16.85</v>
+        <v>16.77</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-14.81</v>
+        <v>-15.22</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-10.32</v>
+        <v>-10.59</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.44</v>
+        <v>6.35</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2622,13 +2622,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.42</v>
+        <v>6.13</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-13.24</v>
+        <v>-17.16</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.67</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.37</v>
+        <v>4.14</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-10.63</v>
+        <v>-15.34</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2784,13 +2784,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-18.05</v>
+        <v>-20.98</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-14.14</v>
+        <v>-15.66</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>30.04</v>
+        <v>27.9</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2865,13 +2865,13 @@
         <v>35.48</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>29.04</v>
+        <v>27.76</v>
       </c>
       <c r="R23" s="5" t="n">
         <v>18.27</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>-3.2</v>
+        <v>-7.47</v>
       </c>
       <c r="T23" s="5" t="n">
         <v>14274.02</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4705</v>
+        <v>4810</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4700</v>
+        <v>4675</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-12.4</v>
+        <v>-12.86</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.69</v>
+        <v>-5.63</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.66</v>
+        <v>17.36</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3025,13 +3025,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>17.54</v>
+        <v>17.36</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-13</v>
+        <v>-13.89</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>93.75</v>
+        <v>95.3</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3105,13 +3105,13 @@
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>93.7</v>
+        <v>93.5</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.4</v>
+        <v>-5.6</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.37</v>
+        <v>1.28</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.92</v>
+        <v>21.8</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>4.65</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.08</v>
+        <v>16.02</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.65</v>
+        <v>4.47</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3354,13 +3354,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.62</v>
+        <v>4.46</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-12.33</v>
+        <v>-15.37</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-7.19</v>
+        <v>-10.78</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.359999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-7.05</v>
+        <v>-9.93</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>68.2</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3520,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>68.15000000000001</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-20.66</v>
+        <v>-21.25</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-16.43</v>
+        <v>-17.11</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.33</v>
+        <v>3.19</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3603,13 +3603,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-17.5</v>
+        <v>-21</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-12.37</v>
+        <v>-16.05</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>48.26</v>
+        <v>46.46</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3686,13 +3686,13 @@
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>47.98</v>
+        <v>45.76</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-5.18</v>
+        <v>-9.57</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4</v>
+        <v>-3.35</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.359999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3769,13 +3769,13 @@
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.26</v>
+        <v>7.9</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-7.92</v>
+        <v>-11.93</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-1.88</v>
+        <v>-7.28</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>17.21</v>
+        <v>17.1</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>16.92</v>
+        <v>16.17</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>218.1</v>
+        <v>218.3</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>10.59</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4018,13 +4018,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>10.59</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-44.5</v>
+        <v>-50</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-41.59</v>
+        <v>-47.38</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-3.53</v>
+        <v>-3.23</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>106.4</v>
+        <v>106.9</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.85</v>
+        <v>16.8</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4264,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>16.85</v>
+        <v>16.77</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-15.71</v>
+        <v>-16.11</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-11.27</v>
+        <v>-11.53</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>273</v>
+        <v>300.25</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>-9.630000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>23.7</v>
+        <v>22.04</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4430,13 +4430,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.64</v>
+        <v>22.04</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-15.75</v>
+        <v>-21.45</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-11.1</v>
+        <v>-17.33</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>106.5</v>
+        <v>104.7</v>
       </c>
       <c r="N43" t="n">
-        <v>5.45</v>
+        <v>3.66</v>
       </c>
       <c r="O43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>5.45</v>
+        <v>3.66</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.45</v>
+        <v>12.31</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4603,7 +4603,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-7.85</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4638,17 +4638,28 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="n">
+        <v>46231</v>
+      </c>
+      <c r="J45" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="N45" t="n">
-        <v>27</v>
+        <v>70.59999999999999</v>
+      </c>
+      <c r="M45" t="n">
+        <v>16.6</v>
       </c>
       <c r="O45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P45" t="n">
         <v>79</v>
@@ -4672,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>27</v>
+        <v>16.6</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4711,13 +4722,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>89.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>-1</v>
+        <v>2.11</v>
       </c>
       <c r="O46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
@@ -4741,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>-1</v>
+        <v>2.11</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4791,7 +4802,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.75</v>
+        <v>8.41</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4803,13 +4814,13 @@
         <v>10.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>8.710000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="R47" t="n">
         <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>-11.21</v>
+        <v>-14.27</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4824,7 +4835,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-6.12</v>
+        <v>-9.76</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4874,7 +4885,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>17.21</v>
+        <v>17.1</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4886,13 +4897,13 @@
         <v>19.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>17.02</v>
+        <v>16.85</v>
       </c>
       <c r="R48" t="n">
         <v>7.38</v>
       </c>
       <c r="S48" t="n">
-        <v>-6.99</v>
+        <v>-7.92</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4907,7 +4918,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>-1.04</v>
+        <v>-1.67</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4957,7 +4968,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>20.78</v>
+        <v>20.64</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -4969,13 +4980,13 @@
         <v>22.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>20.74</v>
+        <v>20.54</v>
       </c>
       <c r="R49" t="n">
         <v>2.92</v>
       </c>
       <c r="S49" t="n">
-        <v>-5.3</v>
+        <v>-6.21</v>
       </c>
       <c r="T49" t="n">
         <v>14274.02</v>
@@ -4990,7 +5001,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>-0.1</v>
+        <v>-0.77</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5040,7 +5051,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5052,13 +5063,13 @@
         <v>3.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="R50" t="n">
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>-11.11</v>
+        <v>-13.47</v>
       </c>
       <c r="T50" t="n">
         <v>14274.02</v>
@@ -5073,7 +5084,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-5.67</v>
+        <v>-8.51</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5108,29 +5119,40 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>46231</v>
+      </c>
+      <c r="J51" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>97.25</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-3.04</v>
+        <v>95</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-5</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
         <v>103.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>97.25</v>
+        <v>93.95</v>
       </c>
       <c r="R51" t="n">
         <v>2.79</v>
       </c>
       <c r="S51" t="n">
-        <v>-3.04</v>
+        <v>-6.33</v>
       </c>
       <c r="T51" t="n">
         <v>14274.02</v>
@@ -5142,7 +5164,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.04</v>
+        <v>-5</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-0.29</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5181,13 +5206,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>168.1</v>
+        <v>172</v>
       </c>
       <c r="N52" t="n">
-        <v>-2.55</v>
+        <v>-0.29</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
         <v>175</v>
@@ -5211,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>-2.55</v>
+        <v>-0.29</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5246,32 +5271,55 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="n">
+        <v>46231</v>
+      </c>
+      <c r="J53" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="N53" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S53" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="T53" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U53" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V53" t="n">
         <v>0</v>
       </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>14274.02</v>
+      <c r="W53" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X53" t="n">
+        <v>-2.61</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28.07.2026 23:06:35</t>
+          <t>29.07.2026 21:45:39</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>22.9</v>
+        <v>23.56</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-17.21</v>
+        <v>-14.82</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>43.26</v>
+        <v>41.96</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>43.26</v>
+        <v>41.56</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-30.52</v>
+        <v>-33.25</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-26.88</v>
+        <v>-29.07</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>183.5</v>
+        <v>181.9</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-3.88</v>
+        <v>-4.71</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.31</v>
+        <v>12.18</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>12.21</v>
+        <v>11.94</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-5.13</v>
+        <v>-7.23</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>67</v>
+        <v>67.25</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1571,13 +1571,13 @@
         <v>85.95</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>4.43</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-19.44</v>
+        <v>-19.68</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>13743.5</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-14.32</v>
+        <v>-14</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.1</v>
+        <v>22.86</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-9.48</v>
+        <v>-10.42</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>36.6</v>
+        <v>36.04</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>35.64</v>
+        <v>35.32</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-26.88</v>
+        <v>-27.53</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-20.95</v>
+        <v>-22.16</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>36.5</v>
+        <v>36.28</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-17.05</v>
+        <v>-17.55</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>6.99</v>
+        <v>6.9</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>6.95</v>
+        <v>6.88</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-20.39</v>
+        <v>-21.19</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-15.68</v>
+        <v>-16.77</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>107.3</v>
+        <v>102.3</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-18.76</v>
+        <v>-19.94</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-11.32</v>
+        <v>-15.45</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>220</v>
+        <v>229.5</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>80.18000000000001</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>25.02</v>
+        <v>24.5</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>43.38</v>
+        <v>40.4</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>67.65000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>4.97</v>
+        <v>-4.58</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>79.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-17.51</v>
+        <v>-18.13</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-19.06</v>
+        <v>-21.41</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-14.46</v>
+        <v>-17.36</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.8</v>
+        <v>16.29</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>16.77</v>
+        <v>16.29</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-15.22</v>
+        <v>-17.64</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-10.59</v>
+        <v>-13.3</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-9.67</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.14</v>
+        <v>3.76</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.93</v>
+        <v>3.74</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-23.69</v>
+        <v>-27.38</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-15.34</v>
+        <v>-23.11</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2784,13 +2784,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-20.98</v>
+        <v>-22.93</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-15.66</v>
+        <v>-19.19</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>27.9</v>
+        <v>27.06</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2865,13 +2865,13 @@
         <v>35.48</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>27.76</v>
+        <v>26.96</v>
       </c>
       <c r="R23" s="5" t="n">
         <v>18.27</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>-7.47</v>
+        <v>-10.13</v>
       </c>
       <c r="T23" s="5" t="n">
         <v>14274.02</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4810</v>
+        <v>4720</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.63</v>
+        <v>-7.39</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.36</v>
+        <v>17.06</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3025,13 +3025,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>17.36</v>
+        <v>16.99</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-13.89</v>
+        <v>-15.72</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>95.3</v>
+        <v>94.3</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3105,13 +3105,13 @@
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>93.5</v>
+        <v>93.45</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.6</v>
+        <v>-5.65</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>1.28</v>
+        <v>0.21</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.8</v>
+        <v>21.48</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>9.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.02</v>
+        <v>16.75</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>1.78</v>
+        <v>6.42</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.47</v>
+        <v>4.32</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3354,13 +3354,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-15.37</v>
+        <v>-18.6</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-10.78</v>
+        <v>-13.77</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.07</v>
+        <v>9.02</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.93</v>
+        <v>-10.43</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>67.65000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3520,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>67.65000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-21.25</v>
+        <v>-29.1</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-17.11</v>
+        <v>-24.64</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3603,13 +3603,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-21</v>
+        <v>-23.25</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-16.05</v>
+        <v>-18.95</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>46.46</v>
+        <v>44.18</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3686,13 +3686,13 @@
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>45.76</v>
+        <v>43.94</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-9.57</v>
+        <v>-13.16</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>-3.35</v>
+        <v>-8.09</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.9</v>
+        <v>7.68</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3769,13 +3769,13 @@
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-11.93</v>
+        <v>-15.27</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-7.28</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>17.1</v>
+        <v>16.87</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>16.17</v>
+        <v>14.61</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>218.3</v>
+        <v>216.9</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.39</v>
+        <v>-0.25</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9.539999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4018,13 +4018,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>9.539999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-50</v>
+        <v>-54.98</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-47.38</v>
+        <v>-52.62</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>319</v>
+        <v>313.25</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-3.23</v>
+        <v>-4.97</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>106.9</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.8</v>
+        <v>16.29</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4264,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>16.77</v>
+        <v>16.29</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-16.11</v>
+        <v>-18.51</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-11.53</v>
+        <v>-14.22</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>300.25</v>
+        <v>330.25</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.61</v>
+        <v>9.32</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>22.04</v>
+        <v>21.8</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4430,13 +4430,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>22.04</v>
+        <v>21.72</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-21.45</v>
+        <v>-22.59</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-17.33</v>
+        <v>-18.23</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>104.7</v>
+        <v>101.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3.66</v>
+        <v>0.2</v>
       </c>
       <c r="O43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.66</v>
+        <v>0.2</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.31</v>
+        <v>12.18</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4582,13 +4582,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>12.21</v>
+        <v>11.94</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-14.14</v>
+        <v>-16.03</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4603,7 +4603,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-8.880000000000001</v>
+        <v>-9.84</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>70.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4665,13 +4665,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>60.55</v>
+        <v>62.1</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>91.90000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="O46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
@@ -4752,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.41</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4814,13 +4814,13 @@
         <v>10.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>8.41</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R47" t="n">
         <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>-14.27</v>
+        <v>-15.39</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4835,7 +4835,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-9.76</v>
+        <v>-10.94</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>17.1</v>
+        <v>16.87</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4897,13 +4897,13 @@
         <v>19.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>16.85</v>
+        <v>16.55</v>
       </c>
       <c r="R48" t="n">
         <v>7.38</v>
       </c>
       <c r="S48" t="n">
-        <v>-7.92</v>
+        <v>-9.56</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4918,7 +4918,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>-1.67</v>
+        <v>-2.99</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4980,13 +4980,13 @@
         <v>22.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>20.54</v>
+        <v>20.4</v>
       </c>
       <c r="R49" t="n">
         <v>2.92</v>
       </c>
       <c r="S49" t="n">
-        <v>-6.21</v>
+        <v>-6.85</v>
       </c>
       <c r="T49" t="n">
         <v>14274.02</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5063,13 +5063,13 @@
         <v>3.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="R50" t="n">
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>-13.47</v>
+        <v>-16.84</v>
       </c>
       <c r="T50" t="n">
         <v>14274.02</v>
@@ -5084,7 +5084,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-8.51</v>
+        <v>-10.99</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>95</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5146,13 +5146,13 @@
         <v>103.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>93.95</v>
+        <v>91.2</v>
       </c>
       <c r="R51" t="n">
         <v>2.79</v>
       </c>
       <c r="S51" t="n">
-        <v>-6.33</v>
+        <v>-9.07</v>
       </c>
       <c r="T51" t="n">
         <v>14274.02</v>
@@ -5167,7 +5167,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.29</v>
+        <v>-4.07</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5206,25 +5206,25 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.29</v>
+        <v>-4.35</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P52" t="n">
         <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>-3.48</v>
+        <v>-4.35</v>
       </c>
       <c r="T52" t="n">
         <v>14274.02</v>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.29</v>
+        <v>-4.35</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>22.02</v>
+        <v>22</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5298,13 +5298,13 @@
         <v>23.98</v>
       </c>
       <c r="Q53" t="n">
-        <v>22.02</v>
+        <v>21.4</v>
       </c>
       <c r="R53" t="n">
         <v>0.76</v>
       </c>
       <c r="S53" t="n">
-        <v>-7.48</v>
+        <v>-10.08</v>
       </c>
       <c r="T53" t="n">
         <v>14274.02</v>
@@ -5319,7 +5319,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>-2.61</v>
+        <v>-2.7</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29.07.2026 21:45:39</t>
+          <t>30.07.2026 22:04:46</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.56</v>
+        <v>23.58</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-14.82</v>
+        <v>-14.75</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>41.96</v>
+        <v>40.96</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>41.56</v>
+        <v>40.3</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-33.25</v>
+        <v>-35.27</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-29.07</v>
+        <v>-30.76</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>181.9</v>
+        <v>181.5</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-4.71</v>
+        <v>-4.92</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.18</v>
+        <v>11.98</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>11.94</v>
+        <v>11.91</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-7.23</v>
+        <v>-7.46</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.04</v>
+        <v>5.9</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>67.25</v>
+        <v>68.95</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-14</v>
+        <v>-11.83</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>22.86</v>
+        <v>22.7</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>22.76</v>
+        <v>22.66</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-15.26</v>
+        <v>-15.64</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-10.42</v>
+        <v>-11.05</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>36.04</v>
+        <v>35.74</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-22.16</v>
+        <v>-22.81</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>36.28</v>
+        <v>37.14</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1814,13 +1814,13 @@
         <v>46.74</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>35.66</v>
+        <v>35.56</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.91</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>-23.01</v>
+        <v>-23.23</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>14493.09</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-17.55</v>
+        <v>-15.59</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>6.9</v>
+        <v>6.92</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1895,13 +1895,13 @@
         <v>8.94</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>2.41</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-21.19</v>
+        <v>-22.11</v>
       </c>
       <c r="T11" s="5" t="n">
         <v>14493.09</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-16.77</v>
+        <v>-16.53</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>102.3</v>
+        <v>103</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>102</v>
+        <v>101.3</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-19.94</v>
+        <v>-20.49</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-15.45</v>
+        <v>-14.88</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>229.5</v>
+        <v>222.5</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>40.4</v>
+        <v>37.54</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>61.5</v>
+        <v>65.5</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-4.58</v>
+        <v>1.63</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>79</v>
+        <v>78.2</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>78.55</v>
+        <v>77.95</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-22.69</v>
+        <v>-23.28</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-18.13</v>
+        <v>-18.96</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-21.41</v>
+        <v>-22.59</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-17.36</v>
+        <v>-16.94</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.29</v>
+        <v>16.02</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>16.29</v>
+        <v>16.02</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-17.64</v>
+        <v>-19.01</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-13.3</v>
+        <v>-14.74</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.4</v>
+        <v>6.12</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2622,13 +2622,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-17.16</v>
+        <v>-17.3</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-8.960000000000001</v>
+        <v>-12.94</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.76</v>
+        <v>3.99</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-27.38</v>
+        <v>-29.13</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-23.11</v>
+        <v>-18.4</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-19.19</v>
+        <v>-20.2</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>27.06</v>
+        <v>26.98</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4720</v>
+        <v>4525</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4675</v>
+        <v>4417.5</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-12.86</v>
+        <v>-17.66</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.39</v>
+        <v>-11.22</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.06</v>
+        <v>16.99</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3025,13 +3025,13 @@
         <v>27.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>16.99</v>
+        <v>16.7</v>
       </c>
       <c r="R25" t="n">
         <v>36.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-15.72</v>
+        <v>-17.16</v>
       </c>
       <c r="T25" t="n">
         <v>14274.02</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>94.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3105,13 +3105,13 @@
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>93.45</v>
+        <v>92.5</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.65</v>
+        <v>-6.61</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>0.21</v>
+        <v>-1.06</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.48</v>
+        <v>22.08</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>7.45</v>
+        <v>10.46</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.75</v>
+        <v>17.02</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>6.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3354,13 +3354,13 @@
         <v>5.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="R29" t="n">
         <v>5.12</v>
       </c>
       <c r="S29" t="n">
-        <v>-18.6</v>
+        <v>-20.11</v>
       </c>
       <c r="T29" t="n">
         <v>14274.02</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-13.77</v>
+        <v>-14.77</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.02</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.43</v>
+        <v>-10.63</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>61.5</v>
+        <v>65.5</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-24.64</v>
+        <v>-19.74</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3603,13 +3603,13 @@
         <v>4.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="R32" t="n">
         <v>0.5</v>
       </c>
       <c r="S32" t="n">
-        <v>-23.25</v>
+        <v>-23.75</v>
       </c>
       <c r="T32" t="n">
         <v>14274.02</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-18.95</v>
+        <v>-19.47</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>44.18</v>
+        <v>46.18</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3686,13 +3686,13 @@
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>43.94</v>
+        <v>43.44</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-13.16</v>
+        <v>-14.15</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>-8.09</v>
+        <v>-3.93</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.68</v>
+        <v>7.51</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3769,13 +3769,13 @@
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-15.27</v>
+        <v>-16.39</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-9.859999999999999</v>
+        <v>-11.85</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>16.87</v>
+        <v>16.45</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>14.61</v>
+        <v>11.75</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>216.9</v>
+        <v>216.5</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3935,13 +3935,13 @@
         <v>231.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>216.4</v>
+        <v>215.6</v>
       </c>
       <c r="R36" t="n">
         <v>0.96</v>
       </c>
       <c r="S36" t="n">
-        <v>-5.46</v>
+        <v>-5.81</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.25</v>
+        <v>-0.44</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>8.59</v>
+        <v>7.74</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4018,13 +4018,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.59</v>
+        <v>7.74</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-54.98</v>
+        <v>-59.43</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-52.62</v>
+        <v>-57.31</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>313.25</v>
+        <v>308.25</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4101,13 +4101,13 @@
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>310.25</v>
+        <v>305.25</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-10.59</v>
+        <v>-12.03</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-4.97</v>
+        <v>-6.49</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>96.84999999999999</v>
+        <v>97</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.29</v>
+        <v>16.02</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4264,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>16.29</v>
+        <v>16.02</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-18.51</v>
+        <v>-19.86</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-14.22</v>
+        <v>-15.64</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>330.25</v>
+        <v>363.25</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4344,13 +4344,13 @@
         <v>6</v>
       </c>
       <c r="P41" t="n">
-        <v>361.25</v>
+        <v>363.25</v>
       </c>
       <c r="Q41" t="n">
         <v>262.25</v>
       </c>
       <c r="R41" t="n">
-        <v>13.6</v>
+        <v>14.23</v>
       </c>
       <c r="S41" t="n">
         <v>-17.53</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>9.32</v>
+        <v>20.24</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>21.8</v>
+        <v>21.78</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4430,13 +4430,13 @@
         <v>30.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.72</v>
+        <v>21.4</v>
       </c>
       <c r="R42" t="n">
         <v>9.41</v>
       </c>
       <c r="S42" t="n">
-        <v>-22.59</v>
+        <v>-23.73</v>
       </c>
       <c r="T42" t="n">
         <v>14274.02</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-18.23</v>
+        <v>-18.3</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>101.2</v>
+        <v>104.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0.2</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.2</v>
+        <v>3.17</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.18</v>
+        <v>11.98</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4582,13 +4582,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.94</v>
+        <v>11.91</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-16.03</v>
+        <v>-16.24</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4603,7 +4603,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-9.84</v>
+        <v>-11.32</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>65</v>
+        <v>64.5</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4665,13 +4665,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>62.1</v>
+        <v>61.15</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>2.56</v>
+        <v>0.99</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>91.45</v>
+        <v>90.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
@@ -4752,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4814,13 +4814,13 @@
         <v>10.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>8.300000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="R47" t="n">
         <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>-15.39</v>
+        <v>-15.8</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>16.87</v>
+        <v>16.45</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4897,13 +4897,13 @@
         <v>19.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>16.55</v>
+        <v>16.44</v>
       </c>
       <c r="R48" t="n">
         <v>7.38</v>
       </c>
       <c r="S48" t="n">
-        <v>-9.56</v>
+        <v>-10.16</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4918,7 +4918,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>-2.99</v>
+        <v>-5.41</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>20.64</v>
+        <v>20.8</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5001,7 +5001,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5063,13 +5063,13 @@
         <v>3.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="R50" t="n">
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>-16.84</v>
+        <v>-17.51</v>
       </c>
       <c r="T50" t="n">
         <v>14274.02</v>
@@ -5084,7 +5084,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-10.99</v>
+        <v>-9.57</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>91.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5146,13 +5146,13 @@
         <v>103.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>91.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="R51" t="n">
         <v>2.79</v>
       </c>
       <c r="S51" t="n">
-        <v>-9.07</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>14274.02</v>
@@ -5167,7 +5167,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>-4.07</v>
+        <v>-2.71</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5202,29 +5202,40 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="n">
+        <v>46233</v>
+      </c>
+      <c r="J52" t="n">
+        <v>163.88</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>165</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-4.35</v>
+        <v>162</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-5</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P52" t="n">
         <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>165</v>
+        <v>161.2</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>-4.35</v>
+        <v>-6.55</v>
       </c>
       <c r="T52" t="n">
         <v>14274.02</v>
@@ -5236,7 +5247,10 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>-4.35</v>
+        <v>-5</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-1.15</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5286,7 +5300,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5319,9 +5333,69 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>-2.7</v>
+        <v>1.72</v>
       </c>
       <c r="Y53" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ISLEM-000053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>DOBUR</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="G54" t="n">
+        <v>345.09</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:04:46</t>
+          <t>31.07.2026 23:19:07</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y54"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.58</v>
+        <v>23.2</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-14.75</v>
+        <v>-16.12</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>40.96</v>
+        <v>41.04</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-35.27</v>
+        <v>-35.59</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-30.76</v>
+        <v>-30.63</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>181.5</v>
+        <v>190.4</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-4.92</v>
+        <v>-0.26</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.98</v>
+        <v>12</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>11.91</v>
+        <v>11.9</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-7.46</v>
+        <v>-7.54</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5.9</v>
+        <v>5.63</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>68.95</v>
+        <v>66.95</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1571,13 +1571,13 @@
         <v>85.95</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>4.43</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-19.68</v>
+        <v>-20.53</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>13743.5</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-11.83</v>
+        <v>-14.39</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>22.66</v>
+        <v>22.46</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-15.64</v>
+        <v>-16.38</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-11.05</v>
+        <v>-9.09</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>35.74</v>
+        <v>37.44</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-22.81</v>
+        <v>-19.14</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>37.14</v>
+        <v>37.82</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-15.59</v>
+        <v>-14.05</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>6.92</v>
+        <v>7.17</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-16.53</v>
+        <v>-13.51</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>103</v>
+        <v>101.4</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>101.3</v>
+        <v>99.2</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-20.49</v>
+        <v>-22.14</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-14.88</v>
+        <v>-16.2</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>222.5</v>
+        <v>211</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>82.23</v>
+        <v>72.81</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24</v>
+        <v>24.56</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>37.54</v>
+        <v>40.74</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>65.5</v>
+        <v>66</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>133.5</v>
+        <v>134.5</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>77.95</v>
+        <v>77.2</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-23.28</v>
+        <v>-24.02</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-18.96</v>
+        <v>-19.07</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-16.94</v>
+        <v>-17.15</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.02</v>
+        <v>16</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>16.02</v>
+        <v>15.86</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-19.01</v>
+        <v>-19.82</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-14.74</v>
+        <v>-14.85</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.12</v>
+        <v>6.24</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2622,13 +2622,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-17.3</v>
+        <v>-18.92</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-12.94</v>
+        <v>-11.24</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.99</v>
+        <v>3.78</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-29.13</v>
+        <v>-30.1</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-18.4</v>
+        <v>-22.7</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2784,13 +2784,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-22.93</v>
+        <v>-25.85</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-20.2</v>
+        <v>-20.71</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>26.98</v>
+        <v>28.72</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4525</v>
+        <v>4550</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-11.22</v>
+        <v>-10.73</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>16.99</v>
+        <v>17.12</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>93.09999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3105,13 +3105,13 @@
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>92.5</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.61</v>
+        <v>-6.97</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.06</v>
+        <v>-0.37</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>22.08</v>
+        <v>21.88</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>10.46</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>17.02</v>
+        <v>16.58</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>8.130000000000001</v>
+        <v>5.34</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.27</v>
+        <v>4.47</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-14.77</v>
+        <v>-10.78</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>9.02</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.63</v>
+        <v>-10.43</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>65.5</v>
+        <v>66</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-19.74</v>
+        <v>-19.13</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-19.47</v>
+        <v>-16.84</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>46.18</v>
+        <v>44.16</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3686,13 +3686,13 @@
         <v>55.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>43.44</v>
+        <v>42.4</v>
       </c>
       <c r="R33" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>-14.15</v>
+        <v>-16.21</v>
       </c>
       <c r="T33" t="n">
         <v>14274.02</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>-3.93</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.51</v>
+        <v>7.46</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3769,13 +3769,13 @@
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-16.39</v>
+        <v>-18.73</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-11.85</v>
+        <v>-12.44</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>16.45</v>
+        <v>16.98</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>11.75</v>
+        <v>15.35</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>216.5</v>
+        <v>216.7</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3935,13 +3935,13 @@
         <v>231.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>215.6</v>
+        <v>214.1</v>
       </c>
       <c r="R36" t="n">
         <v>0.96</v>
       </c>
       <c r="S36" t="n">
-        <v>-5.81</v>
+        <v>-6.47</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.44</v>
+        <v>-0.34</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.74</v>
+        <v>6.97</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4018,13 +4018,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.74</v>
+        <v>6.97</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-59.43</v>
+        <v>-63.47</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-57.31</v>
+        <v>-61.56</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>308.25</v>
+        <v>314</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-6.49</v>
+        <v>-4.75</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>97</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.02</v>
+        <v>16</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4264,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>16.02</v>
+        <v>15.86</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-19.86</v>
+        <v>-20.66</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-15.64</v>
+        <v>-15.75</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>363.25</v>
+        <v>364.5</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4344,13 +4344,13 @@
         <v>6</v>
       </c>
       <c r="P41" t="n">
-        <v>363.25</v>
+        <v>383</v>
       </c>
       <c r="Q41" t="n">
         <v>262.25</v>
       </c>
       <c r="R41" t="n">
-        <v>14.23</v>
+        <v>20.44</v>
       </c>
       <c r="S41" t="n">
         <v>-17.53</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>20.24</v>
+        <v>20.66</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>21.78</v>
+        <v>22.04</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-18.3</v>
+        <v>-17.33</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>104.2</v>
+        <v>108.6</v>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>7.52</v>
       </c>
       <c r="O43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P43" t="n">
         <v>111</v>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.17</v>
+        <v>7.52</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.98</v>
+        <v>12</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4582,13 +4582,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.91</v>
+        <v>11.9</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-16.24</v>
+        <v>-16.32</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4603,7 +4603,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-11.32</v>
+        <v>-11.18</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4665,13 +4665,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>61.15</v>
+        <v>61</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0.99</v>
+        <v>0.74</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>90.5</v>
+        <v>91.05</v>
       </c>
       <c r="N46" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="O46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
@@ -4752,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.300000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4814,13 +4814,13 @@
         <v>10.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>8.26</v>
+        <v>7.97</v>
       </c>
       <c r="R47" t="n">
         <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>-15.8</v>
+        <v>-18.76</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4835,7 +4835,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-10.94</v>
+        <v>-13.52</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>16.45</v>
+        <v>16.98</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4897,13 +4897,13 @@
         <v>19.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>16.44</v>
+        <v>16.16</v>
       </c>
       <c r="R48" t="n">
         <v>7.38</v>
       </c>
       <c r="S48" t="n">
-        <v>-10.16</v>
+        <v>-11.69</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4918,7 +4918,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>-5.41</v>
+        <v>-2.36</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5001,7 +5001,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5084,7 +5084,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.57</v>
+        <v>-7.45</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>92.7</v>
+        <v>90.95</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5146,13 +5146,13 @@
         <v>103.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>90.40000000000001</v>
+        <v>87.45</v>
       </c>
       <c r="R51" t="n">
         <v>2.79</v>
       </c>
       <c r="S51" t="n">
-        <v>-9.869999999999999</v>
+        <v>-12.81</v>
       </c>
       <c r="T51" t="n">
         <v>14274.02</v>
@@ -5167,7 +5167,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>-2.71</v>
+        <v>-4.54</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>162</v>
+        <v>166.4</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5250,7 +5250,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-1.15</v>
+        <v>1.54</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>23</v>
+        <v>23.24</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5333,7 +5333,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>1.72</v>
+        <v>2.79</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5368,34 +5368,117 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="n">
+        <v>46234</v>
+      </c>
+      <c r="J54" t="n">
+        <v>345.09</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="R54" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="S54" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="T54" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U54" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X54" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ISLEM-000054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SELGD</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>147.53</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>AÇIK</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>363.25</v>
-      </c>
-      <c r="N54" t="n">
+      <c r="L55" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="N55" t="n">
         <v>0</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="P54" t="n">
-        <v>363.25</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>363.25</v>
-      </c>
-      <c r="R54" t="n">
+      <c r="P55" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S55" t="n">
         <v>0</v>
       </c>
-      <c r="T54" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y54" t="inlineStr">
+      <c r="T55" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.07.2026 23:19:07</t>
+          <t>08.08.2026 11:05:18</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y55"/>
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.2</v>
+        <v>23.42</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-16.12</v>
+        <v>-15.33</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>41.04</v>
+        <v>42.08</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-30.63</v>
+        <v>-28.87</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>190.4</v>
+        <v>194.3</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-0.26</v>
+        <v>1.78</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-7.54</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5.63</v>
+        <v>7.37</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>66.95</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1571,13 +1571,13 @@
         <v>85.95</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>4.43</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-20.53</v>
+        <v>-20.84</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>13743.5</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-14.39</v>
+        <v>-12.53</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-9.09</v>
+        <v>-10.66</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>37.44</v>
+        <v>37.02</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-19.14</v>
+        <v>-20.04</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>37.82</v>
+        <v>15.91</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1811,16 +1811,16 @@
         <v>1</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>46.74</v>
+        <v>18.08</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>35.56</v>
+        <v>13.75</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>0.91</v>
+        <v>-60.98</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>-23.23</v>
+        <v>-70.31</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>14493.09</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-14.05</v>
+        <v>-63.84</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>101.4</v>
+        <v>99.05</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>99.2</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-22.14</v>
+        <v>-25.71</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-16.2</v>
+        <v>-18.14</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>72.81</v>
+        <v>53.97</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24.56</v>
+        <v>24.98</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2135,13 +2135,13 @@
         <v>4</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>26.22</v>
+        <v>27.82</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>16.14</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>42.73</v>
+        <v>51.44</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>-12.14</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>40.74</v>
+        <v>43.15</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>66</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>2.4</v>
+        <v>11.48</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>134.5</v>
+        <v>126.1</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>78.09999999999999</v>
+        <v>80.05</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-19.07</v>
+        <v>-17.05</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>3.94</v>
+        <v>3.76</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-22.59</v>
+        <v>-26.13</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-17.15</v>
+        <v>-17.56</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16</v>
+        <v>16.15</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-14.85</v>
+        <v>-14.05</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.24</v>
+        <v>6.35</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-11.24</v>
+        <v>-9.67</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.6</v>
+        <v>3.43</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-30.1</v>
+        <v>-33.4</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-22.7</v>
+        <v>-27.61</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-20.71</v>
+        <v>-20.2</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>28.72</v>
+        <v>30.66</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4550</v>
+        <v>4415</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4417.5</v>
+        <v>4182.5</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-17.66</v>
+        <v>-22.04</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.73</v>
+        <v>-13.38</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.12</v>
+        <v>19.65</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>93.75</v>
+        <v>91.45</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3105,13 +3105,13 @@
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>92.15000000000001</v>
+        <v>90.75</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.97</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.37</v>
+        <v>-2.82</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.88</v>
+        <v>21.58</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3185,13 +3185,13 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>22.48</v>
+        <v>22.52</v>
       </c>
       <c r="Q27" t="n">
         <v>19.42</v>
       </c>
       <c r="R27" t="n">
-        <v>6.84</v>
+        <v>7.03</v>
       </c>
       <c r="S27" t="n">
         <v>-7.7</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>9.449999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.58</v>
+        <v>18.46</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>5.34</v>
+        <v>17.28</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.47</v>
+        <v>4.32</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-10.78</v>
+        <v>-13.77</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.02</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.43</v>
+        <v>-10.63</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>66</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-19.13</v>
+        <v>-11.96</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-16.84</v>
+        <v>-17.11</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>44.16</v>
+        <v>52.15</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>-8.130000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.46</v>
+        <v>7.6</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3769,13 +3769,13 @@
         <v>9.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.29</v>
+        <v>7.15</v>
       </c>
       <c r="R34" t="n">
         <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-18.73</v>
+        <v>-20.29</v>
       </c>
       <c r="T34" t="n">
         <v>14274.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-12.44</v>
+        <v>-10.8</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>16.98</v>
+        <v>20.84</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3849,13 +3849,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>19.65</v>
+        <v>21.62</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>26.77</v>
+        <v>39.48</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>15.35</v>
+        <v>41.58</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>216.7</v>
+        <v>221.3</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.34</v>
+        <v>1.77</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.97</v>
+        <v>6.09</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4018,13 +4018,13 @@
         <v>20</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.97</v>
+        <v>5.81</v>
       </c>
       <c r="R37" t="n">
         <v>4.82</v>
       </c>
       <c r="S37" t="n">
-        <v>-63.47</v>
+        <v>-69.55</v>
       </c>
       <c r="T37" t="n">
         <v>14274.02</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-61.56</v>
+        <v>-66.41</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>314</v>
+        <v>306.25</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4101,13 +4101,13 @@
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>305.25</v>
+        <v>303.25</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-12.03</v>
+        <v>-12.61</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-4.75</v>
+        <v>-7.1</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>94.15000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16</v>
+        <v>16.15</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-15.75</v>
+        <v>-14.96</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>364.5</v>
+        <v>363</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4344,13 +4344,13 @@
         <v>6</v>
       </c>
       <c r="P41" t="n">
-        <v>383</v>
+        <v>390.5</v>
       </c>
       <c r="Q41" t="n">
         <v>262.25</v>
       </c>
       <c r="R41" t="n">
-        <v>20.44</v>
+        <v>22.8</v>
       </c>
       <c r="S41" t="n">
         <v>-17.53</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>20.66</v>
+        <v>20.16</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>22.04</v>
+        <v>22.82</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-17.33</v>
+        <v>-14.4</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4486,26 +4486,37 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>46241</v>
+      </c>
+      <c r="J43" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="N43" t="n">
-        <v>7.52</v>
+        <v>113.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>12.18</v>
       </c>
       <c r="O43" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="P43" t="n">
-        <v>111</v>
+        <v>127.5</v>
       </c>
       <c r="Q43" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="R43" t="n">
-        <v>9.9</v>
+        <v>26.24</v>
       </c>
       <c r="S43" t="n">
         <v>-1.39</v>
@@ -4520,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>7.52</v>
+        <v>12.18</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -4570,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4582,13 +4593,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-16.32</v>
+        <v>-18.42</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4603,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-11.18</v>
+        <v>-13.4</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4653,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>61.1</v>
+        <v>55</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4665,13 +4676,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0.74</v>
+        <v>-9.17</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4722,25 +4733,25 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>91.05</v>
+        <v>89</v>
       </c>
       <c r="N46" t="n">
-        <v>1.17</v>
+        <v>-1.11</v>
       </c>
       <c r="O46" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>86.95</v>
+        <v>86</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-3.39</v>
+        <v>-4.44</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4752,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.17</v>
+        <v>-1.11</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4802,7 +4813,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4814,13 +4825,13 @@
         <v>10.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.97</v>
+        <v>7.79</v>
       </c>
       <c r="R47" t="n">
         <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>-18.76</v>
+        <v>-20.59</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4835,7 +4846,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-13.52</v>
+        <v>-12.66</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4885,7 +4896,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>16.98</v>
+        <v>20.84</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4894,13 +4905,13 @@
         <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>19.65</v>
+        <v>21.62</v>
       </c>
       <c r="Q48" t="n">
         <v>16.16</v>
       </c>
       <c r="R48" t="n">
-        <v>7.38</v>
+        <v>18.14</v>
       </c>
       <c r="S48" t="n">
         <v>-11.69</v>
@@ -4918,7 +4929,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>-2.36</v>
+        <v>19.84</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4968,7 +4979,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>21.1</v>
+        <v>21.04</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5001,7 +5012,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5051,7 +5062,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5084,7 +5095,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-7.45</v>
+        <v>-6.38</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5134,7 +5145,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>90.95</v>
+        <v>103.9</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5143,13 +5154,13 @@
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>103.1</v>
+        <v>104.9</v>
       </c>
       <c r="Q51" t="n">
         <v>87.45</v>
       </c>
       <c r="R51" t="n">
-        <v>2.79</v>
+        <v>4.59</v>
       </c>
       <c r="S51" t="n">
         <v>-12.81</v>
@@ -5167,7 +5178,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>-4.54</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5217,7 +5228,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>166.4</v>
+        <v>163.2</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5229,13 +5240,13 @@
         <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>161.2</v>
+        <v>154.1</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>-6.55</v>
+        <v>-10.67</v>
       </c>
       <c r="T52" t="n">
         <v>14274.02</v>
@@ -5250,7 +5261,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>1.54</v>
+        <v>-0.41</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5300,7 +5311,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>23.24</v>
+        <v>25.2</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5309,13 +5320,13 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>23.98</v>
+        <v>25.48</v>
       </c>
       <c r="Q53" t="n">
         <v>21.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0.76</v>
+        <v>7.06</v>
       </c>
       <c r="S53" t="n">
         <v>-10.08</v>
@@ -5333,7 +5344,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>2.79</v>
+        <v>11.46</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5383,7 +5394,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>364.5</v>
+        <v>363</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5392,13 +5403,13 @@
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>383</v>
+        <v>390.5</v>
       </c>
       <c r="Q54" t="n">
         <v>335.25</v>
       </c>
       <c r="R54" t="n">
-        <v>5.44</v>
+        <v>7.5</v>
       </c>
       <c r="S54" t="n">
         <v>-7.71</v>
@@ -5416,7 +5427,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>5.62</v>
+        <v>5.19</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5455,30 +5466,219 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>155.3</v>
+        <v>148.5</v>
       </c>
       <c r="N55" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="O55" t="n">
+        <v>7</v>
+      </c>
+      <c r="P55" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="T55" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U55" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V55" t="n">
         <v>0</v>
       </c>
-      <c r="O55" t="n">
+      <c r="W55" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ISLEM-000055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AYGAZ</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>270.27</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="N56" t="n">
         <v>0</v>
       </c>
-      <c r="P55" t="n">
-        <v>155.3</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>155.3</v>
-      </c>
-      <c r="R55" t="n">
+      <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="n">
+      <c r="P56" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="T55" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y55" t="inlineStr">
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ISLEM-000056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TRCAS</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="G57" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ISLEM-000057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TUPRS</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>307.32</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08.08.2026 11:05:18</t>
+          <t>11.08.2026 22:00:16</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y58"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>23.42</v>
+        <v>24.6</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-15.33</v>
+        <v>-11.06</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>42.08</v>
+        <v>41.14</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-28.87</v>
+        <v>-30.46</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>194.3</v>
+        <v>193.9</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.37</v>
+        <v>7.1</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-12.53</v>
+        <v>-11.76</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-10.66</v>
+        <v>-11.44</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>37.02</v>
+        <v>32.44</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1733,13 +1733,13 @@
         <v>52.2</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>35.32</v>
+        <v>32.14</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-27.53</v>
+        <v>-34.06</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>14446.42</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-20.04</v>
+        <v>-29.94</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>15.91</v>
+        <v>15.5</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-63.84</v>
+        <v>-64.77</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.17</v>
+        <v>7.1</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-13.51</v>
+        <v>-14.35</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>99.05</v>
+        <v>97.25</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-18.14</v>
+        <v>-19.63</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>188</v>
+        <v>180.5</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>53.97</v>
+        <v>47.83</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24.98</v>
+        <v>24.5</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>43.15</v>
+        <v>40.4</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2219,13 +2219,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>59.25</v>
+        <v>58.25</v>
       </c>
       <c r="R15" s="5" t="n">
         <v>31.02</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>-12.68</v>
+        <v>-14.15</v>
       </c>
       <c r="T15" s="5" t="n">
         <v>14734.5</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>11.48</v>
+        <v>4.97</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>126.1</v>
+        <v>123.4</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2300,13 +2300,13 @@
         <v>145.5</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>121.4</v>
+        <v>120.4</v>
       </c>
       <c r="R16" s="8" t="n">
         <v>17.34</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>-2.1</v>
+        <v>-2.9</v>
       </c>
       <c r="T16" s="8" t="n">
         <v>14729.65</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>80.05</v>
+        <v>79.2</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-17.05</v>
+        <v>-17.93</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.99</v>
+        <v>3.87</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-17.56</v>
+        <v>-20.04</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.15</v>
+        <v>15.99</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>15.86</v>
+        <v>15.78</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-19.82</v>
+        <v>-20.22</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-14.05</v>
+        <v>-14.9</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-9.67</v>
+        <v>-5.12</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-33.4</v>
+        <v>-33.98</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-27.61</v>
+        <v>-30.47</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>30.66</v>
+        <v>31.02</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4415</v>
+        <v>4305</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-13.38</v>
+        <v>-15.53</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>19.65</v>
+        <v>18.71</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>91.45</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3105,13 +3105,13 @@
         <v>103.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>90.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R26" t="n">
         <v>4.19</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.380000000000001</v>
+        <v>-10.05</v>
       </c>
       <c r="T26" t="n">
         <v>14274.02</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.82</v>
+        <v>-2.6</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.58</v>
+        <v>21.02</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>7.95</v>
+        <v>5.15</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>18.46</v>
+        <v>18.49</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3268,13 +3268,13 @@
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>19.21</v>
+        <v>19.4</v>
       </c>
       <c r="Q28" t="n">
         <v>14.35</v>
       </c>
       <c r="R28" t="n">
-        <v>15.93</v>
+        <v>17.08</v>
       </c>
       <c r="S28" t="n">
         <v>-13.4</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>17.28</v>
+        <v>17.47</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.32</v>
+        <v>4.25</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-13.77</v>
+        <v>-15.17</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.63</v>
+        <v>-11.62</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>71.84999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3520,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>60.9</v>
+        <v>58.25</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-29.1</v>
+        <v>-32.19</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-11.96</v>
+        <v>-17.11</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-17.11</v>
+        <v>-16.58</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>52.15</v>
+        <v>48.88</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>8.49</v>
+        <v>1.69</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-10.8</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.84</v>
+        <v>20.8</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3849,13 +3849,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>21.62</v>
+        <v>21.68</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>39.48</v>
+        <v>39.87</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>41.58</v>
+        <v>41.3</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>221.3</v>
+        <v>220.2</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>1.77</v>
+        <v>1.26</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.09</v>
+        <v>6.02</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-66.41</v>
+        <v>-66.8</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>306.25</v>
+        <v>301</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4101,13 +4101,13 @@
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>303.25</v>
+        <v>295.25</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-12.61</v>
+        <v>-14.91</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-7.1</v>
+        <v>-8.69</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>91.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4184,13 +4184,13 @@
         <v>117.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R39" t="n">
         <v>30.77</v>
       </c>
       <c r="S39" t="n">
-        <v>-2.62</v>
+        <v>-13.08</v>
       </c>
       <c r="T39" t="n">
         <v>14274.02</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.15</v>
+        <v>15.99</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4264,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>15.86</v>
+        <v>15.78</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-20.66</v>
+        <v>-21.06</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-14.96</v>
+        <v>-15.8</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>363</v>
+        <v>343.5</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>20.16</v>
+        <v>13.7</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>22.82</v>
+        <v>23.54</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-14.4</v>
+        <v>-11.7</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>113.3</v>
+        <v>137</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4510,13 +4510,13 @@
         <v>25</v>
       </c>
       <c r="P43" t="n">
-        <v>127.5</v>
+        <v>137</v>
       </c>
       <c r="Q43" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="R43" t="n">
-        <v>26.24</v>
+        <v>35.64</v>
       </c>
       <c r="S43" t="n">
         <v>-1.39</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-13.4</v>
+        <v>-6</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4676,13 +4676,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>55</v>
+        <v>53.2</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>-9.17</v>
+        <v>-12.14</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4729,29 +4729,40 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="n">
+        <v>46245</v>
+      </c>
+      <c r="J46" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>89</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-1.11</v>
+        <v>86.65000000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-5</v>
       </c>
       <c r="O46" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P46" t="n">
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>86</v>
+        <v>85.05</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-4.44</v>
+        <v>-5.5</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4763,7 +4774,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>-1.11</v>
+        <v>-5</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.35</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4813,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.140000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4825,13 +4839,13 @@
         <v>10.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.79</v>
+        <v>7.69</v>
       </c>
       <c r="R47" t="n">
         <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>-20.59</v>
+        <v>-21.61</v>
       </c>
       <c r="T47" t="n">
         <v>14274.02</v>
@@ -4846,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-12.66</v>
+        <v>-17.49</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4896,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.84</v>
+        <v>20.8</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4905,13 +4919,13 @@
         <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>21.62</v>
+        <v>21.68</v>
       </c>
       <c r="Q48" t="n">
         <v>16.16</v>
       </c>
       <c r="R48" t="n">
-        <v>18.14</v>
+        <v>18.47</v>
       </c>
       <c r="S48" t="n">
         <v>-11.69</v>
@@ -4929,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>19.84</v>
+        <v>19.61</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4979,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>21.04</v>
+        <v>22</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -4988,13 +5002,13 @@
         <v>7</v>
       </c>
       <c r="P49" t="n">
-        <v>22.54</v>
+        <v>22.58</v>
       </c>
       <c r="Q49" t="n">
         <v>20.4</v>
       </c>
       <c r="R49" t="n">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="S49" t="n">
         <v>-6.85</v>
@@ -5012,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>1.15</v>
+        <v>5.77</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5062,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5095,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-6.38</v>
+        <v>-9.93</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5145,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>103.9</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5154,13 +5168,13 @@
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>104.9</v>
+        <v>106.2</v>
       </c>
       <c r="Q51" t="n">
         <v>87.45</v>
       </c>
       <c r="R51" t="n">
-        <v>4.59</v>
+        <v>5.88</v>
       </c>
       <c r="S51" t="n">
         <v>-12.81</v>
@@ -5178,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>9.050000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5228,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>163.2</v>
+        <v>157.3</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5261,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-0.41</v>
+        <v>-4.02</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5311,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>25.2</v>
+        <v>26</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5320,13 +5334,13 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>25.48</v>
+        <v>26.46</v>
       </c>
       <c r="Q53" t="n">
         <v>21.4</v>
       </c>
       <c r="R53" t="n">
-        <v>7.06</v>
+        <v>11.18</v>
       </c>
       <c r="S53" t="n">
         <v>-10.08</v>
@@ -5344,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>11.46</v>
+        <v>14.99</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5394,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>363</v>
+        <v>343.5</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5427,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>5.19</v>
+        <v>-0.46</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5462,29 +5476,40 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="n">
+        <v>46244</v>
+      </c>
+      <c r="J55" t="n">
+        <v>147.53</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>148.5</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-4.38</v>
+        <v>161.6</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-5</v>
       </c>
       <c r="O55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P55" t="n">
         <v>159.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>148.5</v>
+        <v>142.6</v>
       </c>
       <c r="R55" t="n">
         <v>2.77</v>
       </c>
       <c r="S55" t="n">
-        <v>-4.38</v>
+        <v>-8.18</v>
       </c>
       <c r="T55" t="n">
         <v>14274.02</v>
@@ -5496,7 +5521,10 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>-4.38</v>
+        <v>-5</v>
+      </c>
+      <c r="X55" t="n">
+        <v>9.539999999999999</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5535,28 +5563,37 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>284.5</v>
+        <v>286.5</v>
       </c>
       <c r="N56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4</v>
+      </c>
+      <c r="P56" t="n">
+        <v>298.75</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>284.25</v>
+      </c>
+      <c r="R56" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="S56" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="T56" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U56" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V56" t="n">
         <v>0</v>
       </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>284.5</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>284.5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>14274.02</v>
+      <c r="W56" t="n">
+        <v>0.7</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5595,28 +5632,37 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>44.88</v>
+        <v>44.82</v>
       </c>
       <c r="N57" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="T57" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U57" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V57" t="n">
         <v>0</v>
       </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>14274.02</v>
+      <c r="W57" t="n">
+        <v>-0.13</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5655,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>323.5</v>
+        <v>336.5</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>323.5</v>
+        <v>344.75</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5678,7 +5724,256 @@
       <c r="T58" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U58" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>4.02</v>
+      </c>
       <c r="Y58" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ISLEM-000058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AKCNS</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>234.56</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ISLEM-000059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ISLEM-000060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="G61" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ISLEM-000061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SELGD</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>153.52</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.08.2026 22:00:16</t>
+          <t>12.08.2026 21:42:24</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y62"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-11.06</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>41.14</v>
+        <v>40.8</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-30.46</v>
+        <v>-31.03</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>193.9</v>
+        <v>194.4</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.7</v>
+        <v>13.08</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.1</v>
+        <v>7.15</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>69</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-11.76</v>
+        <v>-2.94</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-11.44</v>
+        <v>-11.05</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>32.44</v>
+        <v>34.48</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-29.94</v>
+        <v>-25.53</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>15.5</v>
+        <v>15.79</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-64.77</v>
+        <v>-64.11</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-14.35</v>
+        <v>-13.87</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>97.25</v>
+        <v>95.2</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-19.63</v>
+        <v>-21.32</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>180.5</v>
+        <v>185.1</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>47.83</v>
+        <v>51.6</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24.5</v>
+        <v>23.32</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>40.4</v>
+        <v>33.64</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>67.65000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>4.97</v>
+        <v>-0.78</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>123.4</v>
+        <v>131</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>79.2</v>
+        <v>78.3</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-17.93</v>
+        <v>-18.86</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-20.04</v>
+        <v>-21.07</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>15.99</v>
+        <v>16.03</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-14.9</v>
+        <v>-14.69</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.67</v>
+        <v>6.44</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-5.12</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-33.98</v>
+        <v>-37.09</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-30.47</v>
+        <v>-32.92</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-20.2</v>
+        <v>-20.71</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>31.02</v>
+        <v>31.1</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4305</v>
+        <v>4330</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-15.53</v>
+        <v>-15.04</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.71</v>
+        <v>19.54</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>91.65000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.6</v>
+        <v>-1.81</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>21.02</v>
+        <v>19.52</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3188,13 +3188,13 @@
         <v>22.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.42</v>
+        <v>19.03</v>
       </c>
       <c r="R27" t="n">
         <v>7.03</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.7</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>5.15</v>
+        <v>-2.35</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>18.49</v>
+        <v>17.68</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>17.47</v>
+        <v>12.33</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-15.17</v>
+        <v>-14.77</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.9</v>
+        <v>9.02</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-11.62</v>
+        <v>-10.43</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>67.65000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-17.11</v>
+        <v>-21.64</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>48.88</v>
+        <v>47.7</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>1.69</v>
+        <v>-0.77</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7.8</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-8.449999999999999</v>
+        <v>-2.82</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.8</v>
+        <v>20.44</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>41.3</v>
+        <v>38.86</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>220.2</v>
+        <v>218.9</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>1.26</v>
+        <v>0.67</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.02</v>
+        <v>6.06</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-66.8</v>
+        <v>-66.56999999999999</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>301</v>
+        <v>308.75</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.69</v>
+        <v>-6.34</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>78.8</v>
+        <v>82.3</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15.99</v>
+        <v>16.03</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-15.8</v>
+        <v>-15.59</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>343.5</v>
+        <v>345</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>23.54</v>
+        <v>24.18</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-11.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>137</v>
+        <v>128.9</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4510,13 +4510,13 @@
         <v>25</v>
       </c>
       <c r="P43" t="n">
-        <v>137</v>
+        <v>146.1</v>
       </c>
       <c r="Q43" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="R43" t="n">
-        <v>35.64</v>
+        <v>44.65</v>
       </c>
       <c r="S43" t="n">
         <v>-1.39</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.7</v>
+        <v>13.08</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-6</v>
+        <v>-3.18</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>54</v>
+        <v>52.7</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4676,13 +4676,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>53.2</v>
+        <v>51.3</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>-12.14</v>
+        <v>-15.28</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>86.65000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4756,13 +4756,13 @@
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>85.05</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-5.5</v>
+        <v>-7.61</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>1.35</v>
+        <v>-2.63</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>7.69</v>
+        <v>8.06</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-17.49</v>
+        <v>-13.52</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.8</v>
+        <v>20.44</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>19.61</v>
+        <v>17.54</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>5.77</v>
+        <v>6.73</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.93</v>
+        <v>-11.35</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>95.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>157.3</v>
+        <v>159</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-4.02</v>
+        <v>-2.98</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5334,13 +5334,13 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>26.46</v>
+        <v>27.44</v>
       </c>
       <c r="Q53" t="n">
         <v>21.4</v>
       </c>
       <c r="R53" t="n">
-        <v>11.18</v>
+        <v>15.29</v>
       </c>
       <c r="S53" t="n">
         <v>-10.08</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>14.99</v>
+        <v>15.44</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>343.5</v>
+        <v>345</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.46</v>
+        <v>-0.03</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>161.6</v>
+        <v>149.5</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5500,13 +5500,13 @@
         <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>159.6</v>
+        <v>167.2</v>
       </c>
       <c r="Q55" t="n">
         <v>142.6</v>
       </c>
       <c r="R55" t="n">
-        <v>2.77</v>
+        <v>7.66</v>
       </c>
       <c r="S55" t="n">
         <v>-8.18</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>9.539999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5563,25 +5563,25 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>286.5</v>
+        <v>294.75</v>
       </c>
       <c r="N56" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P56" t="n">
         <v>298.75</v>
       </c>
       <c r="Q56" t="n">
-        <v>284.25</v>
+        <v>283.75</v>
       </c>
       <c r="R56" t="n">
         <v>5.01</v>
       </c>
       <c r="S56" t="n">
-        <v>-0.09</v>
+        <v>-0.26</v>
       </c>
       <c r="T56" t="n">
         <v>14274.02</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>44.82</v>
+        <v>44.72</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
         <v>46.38</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>-0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>336.5</v>
+        <v>351.25</v>
       </c>
       <c r="N58" t="n">
-        <v>4.02</v>
+        <v>8.58</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>344.75</v>
+        <v>353.5</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>6.57</v>
+        <v>9.27</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>4.02</v>
+        <v>8.58</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,28 +5770,37 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>246.9</v>
+        <v>246.8</v>
       </c>
       <c r="N59" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S59" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="T59" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U59" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V59" t="n">
         <v>0</v>
       </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>246.9</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>246.9</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>14274.02</v>
+      <c r="W59" t="n">
+        <v>-0.04</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5830,28 +5839,37 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>104.7</v>
+        <v>101.5</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-3.06</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
         <v>104.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>104.7</v>
+        <v>101.1</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="T60" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U60" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V60" t="n">
         <v>0</v>
       </c>
-      <c r="T60" t="n">
-        <v>14274.02</v>
+      <c r="W60" t="n">
+        <v>-3.06</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5890,28 +5908,37 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>20.84</v>
+        <v>21.52</v>
       </c>
       <c r="N61" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="R61" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="S61" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U61" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V61" t="n">
         <v>0</v>
       </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>14274.02</v>
+      <c r="W61" t="n">
+        <v>3.26</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -5946,34 +5973,177 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>46246</v>
+      </c>
+      <c r="J62" t="n">
+        <v>153.52</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="T62" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U62" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ISLEM-000062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="G63" t="n">
+        <v>128.06</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>AÇIK</t>
         </is>
       </c>
-      <c r="L62" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="N62" t="n">
+      <c r="L63" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="N63" t="n">
         <v>0</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="P62" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="R62" t="n">
+      <c r="P63" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="n">
+      <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T62" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y62" t="inlineStr">
+      <c r="T63" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ISLEM-000063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KGYO</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="G64" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ÖZET" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="VERİLER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BIST" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÖZET" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VERİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BIST" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.08.2026 21:42:24</t>
+          <t>13.08.2026 20:04:05</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-8.529999999999999</v>
+        <v>-8.17</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>40.8</v>
+        <v>40.54</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>40.1</v>
+        <v>39.84</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-35.59</v>
+        <v>-36.01</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-31.03</v>
+        <v>-31.47</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>194.4</v>
+        <v>174.5</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1332,13 +1332,13 @@
         <v>209.1</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>178.7</v>
+        <v>174.3</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>4.08</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-11.05</v>
+        <v>-13.24</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>13744.64</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>1.83</v>
+        <v>-8.59</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>13.08</v>
+        <v>12.38</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.15</v>
+        <v>7.32</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>83.45</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>-2.94</v>
+        <v>6.71</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>22.7</v>
+        <v>20.44</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>22.46</v>
+        <v>20.44</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-16.38</v>
+        <v>-23.9</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-11.05</v>
+        <v>-19.91</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>34.48</v>
+        <v>34.64</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-25.53</v>
+        <v>-25.18</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>15.79</v>
+        <v>15.9</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-64.11</v>
+        <v>-63.86</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.14</v>
+        <v>7.24</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-13.87</v>
+        <v>-12.67</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>95.2</v>
+        <v>100.7</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-21.32</v>
+        <v>-16.78</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>185.1</v>
+        <v>189.1</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>51.6</v>
+        <v>54.87</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>23.32</v>
+        <v>23.5</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>33.64</v>
+        <v>34.67</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>63.95</v>
+        <v>60.25</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-0.78</v>
+        <v>-6.52</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>78.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-18.86</v>
+        <v>-14.92</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-21.07</v>
+        <v>-20.87</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.03</v>
+        <v>15.88</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-14.69</v>
+        <v>-15.49</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.68</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-37.09</v>
+        <v>-37.67</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>31.1</v>
+        <v>32.38</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4330</v>
+        <v>4762.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-15.04</v>
+        <v>-6.56</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>19.54</v>
+        <v>18.96</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>92.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.81</v>
+        <v>-2.23</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>19.52</v>
+        <v>19.25</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3188,13 +3188,13 @@
         <v>22.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.03</v>
+        <v>18.74</v>
       </c>
       <c r="R27" t="n">
         <v>7.03</v>
       </c>
       <c r="S27" t="n">
-        <v>-9.550000000000001</v>
+        <v>-10.93</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.35</v>
+        <v>-3.7</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>17.68</v>
+        <v>17</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>12.33</v>
+        <v>8.01</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-14.77</v>
+        <v>-13.77</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.02</v>
+        <v>8.91</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.43</v>
+        <v>-11.52</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>63.95</v>
+        <v>60.25</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-21.64</v>
+        <v>-26.17</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-16.58</v>
+        <v>-14.74</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>47.7</v>
+        <v>48.1</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.77</v>
+        <v>0.06</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.279999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>-2.82</v>
+        <v>0.47</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.44</v>
+        <v>19.98</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>38.86</v>
+        <v>35.73</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>218.9</v>
+        <v>217.1</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.67</v>
+        <v>-0.16</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-66.56999999999999</v>
+        <v>-66.73999999999999</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>308.75</v>
+        <v>308</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-6.34</v>
+        <v>-6.57</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>82.3</v>
+        <v>83.8</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.03</v>
+        <v>15.88</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-15.59</v>
+        <v>-16.38</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>345</v>
+        <v>341.5</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>14.2</v>
+        <v>13.04</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>24.18</v>
+        <v>23.96</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10.13</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>128.9</v>
+        <v>137.4</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>13.08</v>
+        <v>12.38</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-3.18</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>52.7</v>
+        <v>54.9</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>83.25</v>
+        <v>84.95</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4756,13 +4756,13 @@
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>83.15000000000001</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-7.61</v>
+        <v>-8.17</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-2.63</v>
+        <v>-0.64</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.06</v>
+        <v>8.1</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-13.52</v>
+        <v>-13.09</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.44</v>
+        <v>19.98</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>17.54</v>
+        <v>14.89</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.2</v>
+        <v>22.32</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5002,13 +5002,13 @@
         <v>7</v>
       </c>
       <c r="P49" t="n">
-        <v>22.58</v>
+        <v>22.7</v>
       </c>
       <c r="Q49" t="n">
         <v>20.4</v>
       </c>
       <c r="R49" t="n">
-        <v>3.11</v>
+        <v>3.65</v>
       </c>
       <c r="S49" t="n">
         <v>-6.85</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>6.73</v>
+        <v>7.31</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-11.35</v>
+        <v>-11.7</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.08</v>
+        <v>1.81</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>159</v>
+        <v>153.1</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5254,13 +5254,13 @@
         <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>154.1</v>
+        <v>153.1</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>-10.67</v>
+        <v>-11.25</v>
       </c>
       <c r="T52" t="n">
         <v>14274.02</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-2.98</v>
+        <v>-6.58</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>26.1</v>
+        <v>28</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5334,13 +5334,13 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>27.44</v>
+        <v>28.1</v>
       </c>
       <c r="Q53" t="n">
         <v>21.4</v>
       </c>
       <c r="R53" t="n">
-        <v>15.29</v>
+        <v>18.07</v>
       </c>
       <c r="S53" t="n">
         <v>-10.08</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>15.44</v>
+        <v>23.84</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>345</v>
+        <v>341.5</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.03</v>
+        <v>-1.04</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>149.5</v>
+        <v>147.4</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>1.34</v>
+        <v>-0.09</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5563,22 +5563,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>294.75</v>
+        <v>291.25</v>
       </c>
       <c r="N56" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="O56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P56" t="n">
-        <v>298.75</v>
+        <v>303.75</v>
       </c>
       <c r="Q56" t="n">
         <v>283.75</v>
       </c>
       <c r="R56" t="n">
-        <v>5.01</v>
+        <v>6.77</v>
       </c>
       <c r="S56" t="n">
         <v>-0.26</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,25 +5632,25 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>44.72</v>
+        <v>44.34</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.36</v>
+        <v>-1.2</v>
       </c>
       <c r="O57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P57" t="n">
         <v>46.38</v>
       </c>
       <c r="Q57" t="n">
-        <v>44.6</v>
+        <v>43.64</v>
       </c>
       <c r="R57" t="n">
         <v>3.34</v>
       </c>
       <c r="S57" t="n">
-        <v>-0.62</v>
+        <v>-2.76</v>
       </c>
       <c r="T57" t="n">
         <v>14274.02</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>-0.36</v>
+        <v>-1.2</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>351.25</v>
+        <v>346</v>
       </c>
       <c r="N58" t="n">
-        <v>8.58</v>
+        <v>6.96</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>353.5</v>
+        <v>357</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>9.27</v>
+        <v>10.36</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>8.58</v>
+        <v>6.96</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>246.8</v>
+        <v>245.6</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.04</v>
+        <v>-0.53</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
         <v>249</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-0.04</v>
+        <v>-0.53</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5839,25 +5839,25 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="N60" t="n">
-        <v>-3.06</v>
+        <v>-2.1</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P60" t="n">
         <v>104.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>-3.44</v>
+        <v>-3.63</v>
       </c>
       <c r="T60" t="n">
         <v>14274.02</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>-3.06</v>
+        <v>-2.1</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>3.26</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P61" t="n">
         <v>21.66</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>149.5</v>
+        <v>147.4</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6000,13 +6000,13 @@
         <v>163</v>
       </c>
       <c r="Q62" t="n">
-        <v>149.5</v>
+        <v>146.5</v>
       </c>
       <c r="R62" t="n">
         <v>0.87</v>
       </c>
       <c r="S62" t="n">
-        <v>-7.49</v>
+        <v>-9.34</v>
       </c>
       <c r="T62" t="n">
         <v>14274.02</v>
@@ -6021,7 +6021,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.62</v>
+        <v>-3.99</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6060,28 +6060,37 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>134.8</v>
+        <v>137.9</v>
       </c>
       <c r="N63" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T63" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U63" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V63" t="n">
         <v>0</v>
       </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>134.8</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>134.8</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>14274.02</v>
+      <c r="W63" t="n">
+        <v>2.3</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6120,28 +6129,37 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>11.28</v>
+        <v>12.4</v>
       </c>
       <c r="N64" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="R64" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="S64" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="T64" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U64" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V64" t="n">
         <v>0</v>
       </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>14274.02</v>
+      <c r="W64" t="n">
+        <v>9.93</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.08.2026 20:04:05</t>
+          <t>17.08.2026 19:25:32</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.4</v>
+        <v>25.06</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-8.17</v>
+        <v>-9.4</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>40.54</v>
+        <v>40.9</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-31.47</v>
+        <v>-30.87</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>174.5</v>
+        <v>173.2</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1332,13 +1332,13 @@
         <v>209.1</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>174.3</v>
+        <v>170.9</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>4.08</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-13.24</v>
+        <v>-14.93</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>13744.64</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-8.59</v>
+        <v>-9.27</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.38</v>
+        <v>12.72</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7.32</v>
+        <v>6.91</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>83.45</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1568,13 +1568,13 @@
         <v>5</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>85.95</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>65.15000000000001</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>4.43</v>
+        <v>20.17</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>-20.84</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>6.71</v>
+        <v>21.29</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>20.44</v>
+        <v>19.5</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>20.44</v>
+        <v>18.4</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-23.9</v>
+        <v>-31.5</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-19.91</v>
+        <v>-23.59</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>34.64</v>
+        <v>33.78</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-25.18</v>
+        <v>-27.04</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>15.9</v>
+        <v>16.81</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-63.86</v>
+        <v>-61.8</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.24</v>
+        <v>7.37</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-12.67</v>
+        <v>-11.1</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>100.7</v>
+        <v>114</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-16.78</v>
+        <v>-5.79</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>189.1</v>
+        <v>188.3</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>54.87</v>
+        <v>54.22</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>23.5</v>
+        <v>26.04</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>34.67</v>
+        <v>49.23</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>60.25</v>
+        <v>58.85</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2219,13 +2219,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>58.25</v>
+        <v>57.5</v>
       </c>
       <c r="R15" s="5" t="n">
         <v>31.02</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>-14.15</v>
+        <v>-15.25</v>
       </c>
       <c r="T15" s="5" t="n">
         <v>14734.5</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-6.52</v>
+        <v>-8.69</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>131</v>
+        <v>129.1</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-14.92</v>
+        <v>-18.29</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-20.87</v>
+        <v>-20.66</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>15.88</v>
+        <v>16.18</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-15.49</v>
+        <v>-13.89</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.42</v>
+        <v>6.38</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-8.68</v>
+        <v>-9.25</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-37.67</v>
+        <v>-39.42</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-32.92</v>
+        <v>-35.58</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-20.71</v>
+        <v>-19.19</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>32.38</v>
+        <v>33.62</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4762.5</v>
+        <v>4590</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.56</v>
+        <v>-9.94</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.96</v>
+        <v>18.1</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>92</v>
+        <v>91.95</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.23</v>
+        <v>-2.28</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>19.25</v>
+        <v>18.95</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.7</v>
+        <v>-5.2</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>17</v>
+        <v>16.67</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>8.01</v>
+        <v>5.91</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.32</v>
+        <v>4.48</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-13.77</v>
+        <v>-10.58</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-11.52</v>
+        <v>-10.63</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>60.25</v>
+        <v>58.85</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3520,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>58.25</v>
+        <v>57.5</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-32.19</v>
+        <v>-33.06</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-26.17</v>
+        <v>-27.89</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-14.74</v>
+        <v>-15.53</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>48.1</v>
+        <v>49.1</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>0.06</v>
+        <v>2.14</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.56</v>
+        <v>8.83</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>0.47</v>
+        <v>3.64</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>19.98</v>
+        <v>20.54</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>35.73</v>
+        <v>39.54</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>217.1</v>
+        <v>218</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.16</v>
+        <v>0.25</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.03</v>
+        <v>6.26</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-66.73999999999999</v>
+        <v>-65.47</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-6.57</v>
+        <v>-8.69</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>83.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15.88</v>
+        <v>16.18</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-16.38</v>
+        <v>-14.8</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>341.5</v>
+        <v>346</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>13.04</v>
+        <v>14.53</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>23.96</v>
+        <v>25.12</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-10.13</v>
+        <v>-5.78</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>137.4</v>
+        <v>143</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.38</v>
+        <v>12.72</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-8.359999999999999</v>
+        <v>-5.85</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>54.9</v>
+        <v>57.25</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>84.95</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4756,13 +4756,13 @@
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>82.65000000000001</v>
+        <v>80</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-8.17</v>
+        <v>-11.11</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-0.64</v>
+        <v>-6.02</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.1</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-13.09</v>
+        <v>-9.98</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>19.98</v>
+        <v>20.54</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>14.89</v>
+        <v>18.11</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.32</v>
+        <v>23.02</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5002,13 +5002,13 @@
         <v>7</v>
       </c>
       <c r="P49" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q49" t="n">
         <v>20.4</v>
       </c>
       <c r="R49" t="n">
-        <v>3.65</v>
+        <v>6.39</v>
       </c>
       <c r="S49" t="n">
         <v>-6.85</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>7.31</v>
+        <v>10.67</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-11.7</v>
+        <v>-10.64</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>97</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>1.81</v>
+        <v>-0.98</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>153.1</v>
+        <v>154.6</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5254,13 +5254,13 @@
         <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>153.1</v>
+        <v>148.8</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>-11.25</v>
+        <v>-13.74</v>
       </c>
       <c r="T52" t="n">
         <v>14274.02</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-6.58</v>
+        <v>-5.66</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>28</v>
+        <v>27.62</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5334,13 +5334,13 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>28.1</v>
+        <v>29.28</v>
       </c>
       <c r="Q53" t="n">
         <v>21.4</v>
       </c>
       <c r="R53" t="n">
-        <v>18.07</v>
+        <v>23.03</v>
       </c>
       <c r="S53" t="n">
         <v>-10.08</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>23.84</v>
+        <v>22.16</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>341.5</v>
+        <v>346</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5420,13 +5420,13 @@
         <v>390.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>335.25</v>
+        <v>311.75</v>
       </c>
       <c r="R54" t="n">
         <v>7.5</v>
       </c>
       <c r="S54" t="n">
-        <v>-7.71</v>
+        <v>-14.18</v>
       </c>
       <c r="T54" t="n">
         <v>14274.02</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>-1.04</v>
+        <v>0.26</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>147.4</v>
+        <v>149.3</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>-0.09</v>
+        <v>1.2</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5563,22 +5563,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>291.25</v>
+        <v>313</v>
       </c>
       <c r="N56" t="n">
-        <v>2.37</v>
+        <v>10.02</v>
       </c>
       <c r="O56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P56" t="n">
-        <v>303.75</v>
+        <v>317</v>
       </c>
       <c r="Q56" t="n">
         <v>283.75</v>
       </c>
       <c r="R56" t="n">
-        <v>6.77</v>
+        <v>11.42</v>
       </c>
       <c r="S56" t="n">
         <v>-0.26</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>2.37</v>
+        <v>10.02</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,22 +5632,22 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>44.34</v>
+        <v>46.34</v>
       </c>
       <c r="N57" t="n">
-        <v>-1.2</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>46.38</v>
+        <v>46.88</v>
       </c>
       <c r="Q57" t="n">
         <v>43.64</v>
       </c>
       <c r="R57" t="n">
-        <v>3.34</v>
+        <v>4.46</v>
       </c>
       <c r="S57" t="n">
         <v>-2.76</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>346</v>
+        <v>368.75</v>
       </c>
       <c r="N58" t="n">
-        <v>6.96</v>
+        <v>13.99</v>
       </c>
       <c r="O58" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P58" t="n">
-        <v>357</v>
+        <v>373.5</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>10.36</v>
+        <v>15.46</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>6.96</v>
+        <v>13.99</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,25 +5770,25 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>245.6</v>
+        <v>240.5</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.53</v>
+        <v>-2.59</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P59" t="n">
         <v>249</v>
       </c>
       <c r="Q59" t="n">
-        <v>242.1</v>
+        <v>238.7</v>
       </c>
       <c r="R59" t="n">
         <v>0.85</v>
       </c>
       <c r="S59" t="n">
-        <v>-1.94</v>
+        <v>-3.32</v>
       </c>
       <c r="T59" t="n">
         <v>14274.02</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-0.53</v>
+        <v>-2.59</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5839,22 +5839,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>102.5</v>
+        <v>103.8</v>
       </c>
       <c r="N60" t="n">
-        <v>-2.1</v>
+        <v>-0.86</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P60" t="n">
-        <v>104.7</v>
+        <v>105</v>
       </c>
       <c r="Q60" t="n">
         <v>100.9</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="S60" t="n">
         <v>-3.63</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>-2.1</v>
+        <v>-0.86</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5908,22 +5908,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>21.52</v>
+        <v>22.02</v>
       </c>
       <c r="N61" t="n">
-        <v>3.26</v>
+        <v>5.66</v>
       </c>
       <c r="O61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P61" t="n">
-        <v>21.66</v>
+        <v>22.1</v>
       </c>
       <c r="Q61" t="n">
         <v>20.82</v>
       </c>
       <c r="R61" t="n">
-        <v>3.93</v>
+        <v>6.05</v>
       </c>
       <c r="S61" t="n">
         <v>-0.1</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>3.26</v>
+        <v>5.66</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>147.4</v>
+        <v>149.3</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6021,7 +6021,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.99</v>
+        <v>-2.75</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6060,22 +6060,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>137.9</v>
+        <v>139.5</v>
       </c>
       <c r="N63" t="n">
-        <v>2.3</v>
+        <v>3.49</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>140.8</v>
+        <v>143.5</v>
       </c>
       <c r="Q63" t="n">
         <v>132.1</v>
       </c>
       <c r="R63" t="n">
-        <v>4.45</v>
+        <v>6.45</v>
       </c>
       <c r="S63" t="n">
         <v>-2</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>2.3</v>
+        <v>3.49</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6129,22 +6129,22 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>12.4</v>
+        <v>13.65</v>
       </c>
       <c r="N64" t="n">
-        <v>9.93</v>
+        <v>21.01</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>12.4</v>
+        <v>13.91</v>
       </c>
       <c r="Q64" t="n">
         <v>11.17</v>
       </c>
       <c r="R64" t="n">
-        <v>9.93</v>
+        <v>23.32</v>
       </c>
       <c r="S64" t="n">
         <v>-0.98</v>
@@ -6159,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>9.93</v>
+        <v>21.01</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.08.2026 19:25:32</t>
+          <t>19.08.2026 23:50:55</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.06</v>
+        <v>25.4</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-9.4</v>
+        <v>-8.17</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>40.9</v>
+        <v>39.52</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>39.84</v>
+        <v>39.38</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-36.01</v>
+        <v>-36.75</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-30.87</v>
+        <v>-33.2</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>173.2</v>
+        <v>169.2</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1332,13 +1332,13 @@
         <v>209.1</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>170.9</v>
+        <v>167.6</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>4.08</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-14.93</v>
+        <v>-16.58</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>13744.64</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-9.27</v>
+        <v>-11.37</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.72</v>
+        <v>12.15</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.91</v>
+        <v>6.89</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>94.84999999999999</v>
+        <v>92</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>21.29</v>
+        <v>17.65</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-23.59</v>
+        <v>-21.63</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>33.78</v>
+        <v>34.34</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-27.04</v>
+        <v>-25.83</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>16.81</v>
+        <v>16.46</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-61.8</v>
+        <v>-62.59</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.37</v>
+        <v>7.08</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-11.1</v>
+        <v>-14.6</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>114</v>
+        <v>22.64</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1976,13 +1976,13 @@
         <v>134.1</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>94.65000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>5.26</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-25.71</v>
+        <v>-83.2</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-5.79</v>
+        <v>-81.29000000000001</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>188.3</v>
+        <v>178</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>54.22</v>
+        <v>45.78</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>26.04</v>
+        <v>26.08</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>49.23</v>
+        <v>49.46</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>58.85</v>
+        <v>53</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2219,13 +2219,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>57.5</v>
+        <v>52.95</v>
       </c>
       <c r="R15" s="5" t="n">
         <v>31.02</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>-15.25</v>
+        <v>-21.96</v>
       </c>
       <c r="T15" s="5" t="n">
         <v>14734.5</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-8.69</v>
+        <v>-17.77</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>129.1</v>
+        <v>140.1</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>78.84999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-18.29</v>
+        <v>-18.96</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>3.76</v>
+        <v>3.67</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-26.13</v>
+        <v>-27.9</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-20.66</v>
+        <v>-23.97</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.18</v>
+        <v>15.67</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>15.78</v>
+        <v>15.48</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-20.22</v>
+        <v>-21.74</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-13.89</v>
+        <v>-16.6</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.38</v>
+        <v>6.53</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-9.25</v>
+        <v>-7.11</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-39.42</v>
+        <v>-42.14</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-35.58</v>
+        <v>-37.63</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-19.19</v>
+        <v>-20.2</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>33.62</v>
+        <v>33.78</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4590</v>
+        <v>4505</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.94</v>
+        <v>-11.61</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.1</v>
+        <v>17.95</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>91.95</v>
+        <v>94.45</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.28</v>
+        <v>0.37</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>18.95</v>
+        <v>19.41</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-5.2</v>
+        <v>-2.9</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>5.91</v>
+        <v>5.65</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-10.58</v>
+        <v>-9.98</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.63</v>
+        <v>-11.02</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>58.85</v>
+        <v>53</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3520,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>57.5</v>
+        <v>52.95</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-33.06</v>
+        <v>-38.36</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-27.89</v>
+        <v>-35.06</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-15.53</v>
+        <v>-16.05</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>49.1</v>
+        <v>50.5</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>2.14</v>
+        <v>5.06</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.83</v>
+        <v>8.84</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>3.64</v>
+        <v>3.76</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.54</v>
+        <v>20.34</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3849,13 +3849,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>21.68</v>
+        <v>21.72</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>39.87</v>
+        <v>40.13</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>39.54</v>
+        <v>38.18</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>218</v>
+        <v>215.8</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.25</v>
+        <v>-0.76</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.26</v>
+        <v>6.18</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-65.47</v>
+        <v>-65.91</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>301</v>
+        <v>301.25</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.69</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>84.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.18</v>
+        <v>15.67</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4264,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>15.78</v>
+        <v>15.48</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-21.06</v>
+        <v>-22.56</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-14.8</v>
+        <v>-17.48</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>346</v>
+        <v>329.5</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>14.53</v>
+        <v>9.07</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.12</v>
+        <v>25.28</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-5.78</v>
+        <v>-5.18</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>143</v>
+        <v>129.9</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.72</v>
+        <v>12.15</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-5.85</v>
+        <v>-10.07</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>57.25</v>
+        <v>56.15</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>80.34999999999999</v>
+        <v>82</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4756,13 +4756,13 @@
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-11.11</v>
+        <v>-11.33</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-6.02</v>
+        <v>-4.09</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.390000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-9.98</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.54</v>
+        <v>20.34</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4919,13 +4919,13 @@
         <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>21.68</v>
+        <v>21.72</v>
       </c>
       <c r="Q48" t="n">
         <v>16.16</v>
       </c>
       <c r="R48" t="n">
-        <v>18.47</v>
+        <v>18.69</v>
       </c>
       <c r="S48" t="n">
         <v>-11.69</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>18.11</v>
+        <v>16.96</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>23.02</v>
+        <v>22.62</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5002,13 +5002,13 @@
         <v>7</v>
       </c>
       <c r="P49" t="n">
-        <v>23.3</v>
+        <v>23.44</v>
       </c>
       <c r="Q49" t="n">
         <v>20.4</v>
       </c>
       <c r="R49" t="n">
-        <v>6.39</v>
+        <v>7.03</v>
       </c>
       <c r="S49" t="n">
         <v>-6.85</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>10.67</v>
+        <v>8.75</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-10.64</v>
+        <v>-10.99</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>94.34999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.98</v>
+        <v>1.7</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>154.6</v>
+        <v>148.7</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5254,13 +5254,13 @@
         <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>148.8</v>
+        <v>147.5</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>-13.74</v>
+        <v>-14.49</v>
       </c>
       <c r="T52" t="n">
         <v>14274.02</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-5.66</v>
+        <v>-9.26</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>27.62</v>
+        <v>26</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>22.16</v>
+        <v>14.99</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>346</v>
+        <v>329.5</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>0.26</v>
+        <v>-4.52</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>149.3</v>
+        <v>150.9</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5563,22 +5563,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>313</v>
+        <v>326.5</v>
       </c>
       <c r="N56" t="n">
-        <v>10.02</v>
+        <v>14.76</v>
       </c>
       <c r="O56" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P56" t="n">
-        <v>317</v>
+        <v>329.75</v>
       </c>
       <c r="Q56" t="n">
         <v>283.75</v>
       </c>
       <c r="R56" t="n">
-        <v>11.42</v>
+        <v>15.91</v>
       </c>
       <c r="S56" t="n">
         <v>-0.26</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>10.02</v>
+        <v>14.76</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,22 +5632,22 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>46.34</v>
+        <v>47.4</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>5.61</v>
       </c>
       <c r="O57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P57" t="n">
-        <v>46.88</v>
+        <v>48.36</v>
       </c>
       <c r="Q57" t="n">
         <v>43.64</v>
       </c>
       <c r="R57" t="n">
-        <v>4.46</v>
+        <v>7.75</v>
       </c>
       <c r="S57" t="n">
         <v>-2.76</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>3.25</v>
+        <v>5.61</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>368.75</v>
+        <v>395.5</v>
       </c>
       <c r="N58" t="n">
-        <v>13.99</v>
+        <v>22.26</v>
       </c>
       <c r="O58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P58" t="n">
-        <v>373.5</v>
+        <v>398.25</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>15.46</v>
+        <v>23.11</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>13.99</v>
+        <v>22.26</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>240.5</v>
+        <v>245.7</v>
       </c>
       <c r="N59" t="n">
-        <v>-2.59</v>
+        <v>-0.49</v>
       </c>
       <c r="O59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P59" t="n">
         <v>249</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-2.59</v>
+        <v>-0.49</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5839,22 +5839,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>103.8</v>
+        <v>113.1</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.86</v>
+        <v>8.02</v>
       </c>
       <c r="O60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>105</v>
+        <v>116.3</v>
       </c>
       <c r="Q60" t="n">
         <v>100.9</v>
       </c>
       <c r="R60" t="n">
-        <v>0.29</v>
+        <v>11.08</v>
       </c>
       <c r="S60" t="n">
         <v>-3.63</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>-0.86</v>
+        <v>8.02</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>22.02</v>
+        <v>21.88</v>
       </c>
       <c r="N61" t="n">
-        <v>5.66</v>
+        <v>4.99</v>
       </c>
       <c r="O61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P61" t="n">
         <v>22.1</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>5.66</v>
+        <v>4.99</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>149.3</v>
+        <v>150.9</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6021,7 +6021,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.75</v>
+        <v>-1.71</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6060,25 +6060,25 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>139.5</v>
+        <v>144.8</v>
       </c>
       <c r="N63" t="n">
-        <v>3.49</v>
+        <v>7.42</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P63" t="n">
-        <v>143.5</v>
+        <v>146</v>
       </c>
       <c r="Q63" t="n">
-        <v>132.1</v>
+        <v>130.2</v>
       </c>
       <c r="R63" t="n">
-        <v>6.45</v>
+        <v>8.31</v>
       </c>
       <c r="S63" t="n">
-        <v>-2</v>
+        <v>-3.41</v>
       </c>
       <c r="T63" t="n">
         <v>14274.02</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>3.49</v>
+        <v>7.42</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6125,26 +6125,37 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="n">
+        <v>46253</v>
+      </c>
+      <c r="J64" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="N64" t="n">
-        <v>21.01</v>
+        <v>12.29</v>
+      </c>
+      <c r="M64" t="n">
+        <v>8.949999999999999</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P64" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="Q64" t="n">
         <v>11.17</v>
       </c>
       <c r="R64" t="n">
-        <v>23.32</v>
+        <v>24.11</v>
       </c>
       <c r="S64" t="n">
         <v>-0.98</v>
@@ -6159,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>21.01</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19.08.2026 23:50:55</t>
+          <t>20.08.2026 23:29:52</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.4</v>
+        <v>26.6</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-8.17</v>
+        <v>-3.83</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>39.52</v>
+        <v>43.46</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-33.2</v>
+        <v>-26.54</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>169.2</v>
+        <v>170.3</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-11.37</v>
+        <v>-10.79</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>12.15</v>
+        <v>11.96</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.89</v>
+        <v>6.67</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>92</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>17.65</v>
+        <v>13.3</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>20</v>
+        <v>19.31</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-21.63</v>
+        <v>-24.33</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>34.34</v>
+        <v>34.04</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-25.83</v>
+        <v>-26.48</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>16.46</v>
+        <v>16.56</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-62.59</v>
+        <v>-62.36</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.08</v>
+        <v>7.09</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-14.6</v>
+        <v>-14.48</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>22.64</v>
+        <v>22.6</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1973,16 +1973,16 @@
         <v>1</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>134.1</v>
+        <v>26.82</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>21.4</v>
+        <v>18.93</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>5.26</v>
+        <v>-78.95</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>-83.2</v>
+        <v>-85.14</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>14493.09</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-81.29000000000001</v>
+        <v>-81.31999999999999</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>178</v>
+        <v>173.7</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>45.78</v>
+        <v>42.26</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>26.08</v>
+        <v>26.44</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>49.46</v>
+        <v>51.52</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>53</v>
+        <v>58.3</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2219,13 +2219,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>52.95</v>
+        <v>50.35</v>
       </c>
       <c r="R15" s="5" t="n">
         <v>31.02</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>-21.96</v>
+        <v>-25.79</v>
       </c>
       <c r="T15" s="5" t="n">
         <v>14734.5</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-17.77</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>140.1</v>
+        <v>132</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>78.2</v>
+        <v>77.45</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-18.96</v>
+        <v>-19.74</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-23.97</v>
+        <v>-23.55</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>15.67</v>
+        <v>16.16</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-16.6</v>
+        <v>-14</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.53</v>
+        <v>6.44</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-7.11</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-37.63</v>
+        <v>-38.45</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>33.78</v>
+        <v>33.86</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4505</v>
+        <v>4515</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-11.61</v>
+        <v>-11.41</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.95</v>
+        <v>18.06</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>94.45</v>
+        <v>92.75</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>0.37</v>
+        <v>-1.43</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>19.41</v>
+        <v>19.15</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.9</v>
+        <v>-4.2</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.63</v>
+        <v>16.65</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>5.65</v>
+        <v>5.78</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-9.98</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.960000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-11.02</v>
+        <v>-11.62</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>53</v>
+        <v>58.3</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3520,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>52.95</v>
+        <v>50.35</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-38.36</v>
+        <v>-41.39</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-35.06</v>
+        <v>-28.56</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-16.05</v>
+        <v>-16.32</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>50.5</v>
+        <v>51.45</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>5.06</v>
+        <v>7.03</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.84</v>
+        <v>8.73</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>3.76</v>
+        <v>2.46</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.34</v>
+        <v>20.98</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>38.18</v>
+        <v>42.53</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>215.8</v>
+        <v>217.1</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.76</v>
+        <v>-0.16</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-65.91</v>
+        <v>-66.08</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>85.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15.67</v>
+        <v>16.16</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-17.48</v>
+        <v>-14.9</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>329.5</v>
+        <v>317.75</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>9.07</v>
+        <v>5.18</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.28</v>
+        <v>25.16</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-5.18</v>
+        <v>-5.63</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>129.9</v>
+        <v>138</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12.15</v>
+        <v>11.96</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-10.07</v>
+        <v>-11.47</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>56.15</v>
+        <v>55.6</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>82</v>
+        <v>81.3</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-4.09</v>
+        <v>-4.91</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.4</v>
+        <v>8.83</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-9.869999999999999</v>
+        <v>-5.26</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.34</v>
+        <v>20.98</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>16.96</v>
+        <v>20.64</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.62</v>
+        <v>22.76</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>8.75</v>
+        <v>9.42</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-10.99</v>
+        <v>-9.93</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>96.90000000000001</v>
+        <v>103.4</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>1.7</v>
+        <v>8.52</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>148.7</v>
+        <v>153.6</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-9.26</v>
+        <v>-6.27</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>14.99</v>
+        <v>16.76</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>329.5</v>
+        <v>317.75</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>-4.52</v>
+        <v>-7.92</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>150.9</v>
+        <v>152</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>2.28</v>
+        <v>3.03</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5563,22 +5563,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>326.5</v>
+        <v>330</v>
       </c>
       <c r="N56" t="n">
-        <v>14.76</v>
+        <v>15.99</v>
       </c>
       <c r="O56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P56" t="n">
-        <v>329.75</v>
+        <v>332.5</v>
       </c>
       <c r="Q56" t="n">
         <v>283.75</v>
       </c>
       <c r="R56" t="n">
-        <v>15.91</v>
+        <v>16.87</v>
       </c>
       <c r="S56" t="n">
         <v>-0.26</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>14.76</v>
+        <v>15.99</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>47.4</v>
+        <v>46.08</v>
       </c>
       <c r="N57" t="n">
-        <v>5.61</v>
+        <v>2.67</v>
       </c>
       <c r="O57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P57" t="n">
         <v>48.36</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>5.61</v>
+        <v>2.67</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>395.5</v>
+        <v>395.25</v>
       </c>
       <c r="N58" t="n">
-        <v>22.26</v>
+        <v>22.18</v>
       </c>
       <c r="O58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P58" t="n">
-        <v>398.25</v>
+        <v>402.75</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>23.11</v>
+        <v>24.5</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>22.26</v>
+        <v>22.18</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>245.7</v>
+        <v>243</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.49</v>
+        <v>-1.58</v>
       </c>
       <c r="O59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P59" t="n">
         <v>249</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-0.49</v>
+        <v>-1.58</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5839,13 +5839,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>113.1</v>
+        <v>107.7</v>
       </c>
       <c r="N60" t="n">
-        <v>8.02</v>
+        <v>2.87</v>
       </c>
       <c r="O60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P60" t="n">
         <v>116.3</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>8.02</v>
+        <v>2.87</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5908,22 +5908,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>21.88</v>
+        <v>22.14</v>
       </c>
       <c r="N61" t="n">
-        <v>4.99</v>
+        <v>6.24</v>
       </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P61" t="n">
-        <v>22.1</v>
+        <v>22.54</v>
       </c>
       <c r="Q61" t="n">
         <v>20.82</v>
       </c>
       <c r="R61" t="n">
-        <v>6.05</v>
+        <v>8.16</v>
       </c>
       <c r="S61" t="n">
         <v>-0.1</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>4.99</v>
+        <v>6.24</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>150.9</v>
+        <v>152</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6021,7 +6021,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.71</v>
+        <v>-0.99</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6060,22 +6060,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>144.8</v>
+        <v>142.7</v>
       </c>
       <c r="N63" t="n">
-        <v>7.42</v>
+        <v>5.86</v>
       </c>
       <c r="O63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q63" t="n">
         <v>130.2</v>
       </c>
       <c r="R63" t="n">
-        <v>8.31</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S63" t="n">
         <v>-3.41</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>7.42</v>
+        <v>5.86</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>12.29</v>
+        <v>12.45</v>
       </c>
       <c r="M64" t="n">
         <v>8.949999999999999</v>
@@ -6173,6 +6173,186 @@
         <v>8.949999999999999</v>
       </c>
       <c r="Y64" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ISLEM-000064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BIOEN</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="G65" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ISLEM-000065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HURGZ</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ISLEM-000066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PASEU</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>202.3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>192.19</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>202.3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>202.3</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>202.3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.08.2026 23:29:52</t>
+          <t>21.08.2026 22:12:23</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:Y68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>26.6</v>
+        <v>26.58</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-3.83</v>
+        <v>-3.9</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>43.46</v>
+        <v>42.24</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-26.54</v>
+        <v>-28.6</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>170.3</v>
+        <v>169.8</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-10.79</v>
+        <v>-11.05</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.96</v>
+        <v>11.98</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.67</v>
+        <v>6.98</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>88.59999999999999</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>13.3</v>
+        <v>18.48</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>19.31</v>
+        <v>18.96</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-24.33</v>
+        <v>-25.71</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>34.04</v>
+        <v>34.2</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-26.48</v>
+        <v>-26.13</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>16.56</v>
+        <v>16.22</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-62.36</v>
+        <v>-63.14</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.09</v>
+        <v>7.12</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-14.48</v>
+        <v>-14.11</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-81.31999999999999</v>
+        <v>-81.48999999999999</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>173.7</v>
+        <v>170.8</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>42.26</v>
+        <v>39.89</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>26.44</v>
+        <v>26.48</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>51.52</v>
+        <v>51.75</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>58.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-9.539999999999999</v>
+        <v>-0.54</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>132</v>
+        <v>133.5</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>77.45</v>
+        <v>77.25</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-19.74</v>
+        <v>-19.95</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-23.55</v>
+        <v>-22.93</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.16</v>
+        <v>17.44</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-14</v>
+        <v>-7.18</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-42.14</v>
+        <v>-42.72</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-38.45</v>
+        <v>-37.22</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-20.2</v>
+        <v>-14.65</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>33.86</v>
+        <v>32.5</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4515</v>
+        <v>4522.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-11.41</v>
+        <v>-11.27</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.06</v>
+        <v>17.95</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>92.75</v>
+        <v>95.5</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>19.15</v>
+        <v>19.24</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.2</v>
+        <v>-3.75</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.65</v>
+        <v>16.57</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>5.78</v>
+        <v>5.27</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-8.380000000000001</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>58.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-28.56</v>
+        <v>-21.46</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>51.45</v>
+        <v>54.55</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>7.03</v>
+        <v>13.48</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.73</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>2.46</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.98</v>
+        <v>20.7</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>42.53</v>
+        <v>40.62</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>217.1</v>
+        <v>219.5</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>301.25</v>
+        <v>301</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.69</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>82</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.16</v>
+        <v>17.44</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-14.9</v>
+        <v>-8.16</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>317.75</v>
+        <v>349.5</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>5.18</v>
+        <v>15.69</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.16</v>
+        <v>24.66</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-5.63</v>
+        <v>-7.5</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>138</v>
+        <v>133.6</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.96</v>
+        <v>11.98</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-11.47</v>
+        <v>-11.32</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>55.6</v>
+        <v>53.4</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>81.3</v>
+        <v>83.2</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-4.91</v>
+        <v>-2.69</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.83</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-5.26</v>
+        <v>-7.4</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.98</v>
+        <v>20.7</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>20.64</v>
+        <v>19.03</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.76</v>
+        <v>22.56</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>9.42</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.93</v>
+        <v>-10.28</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>103.4</v>
+        <v>107.8</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5168,13 +5168,13 @@
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>106.2</v>
+        <v>109.6</v>
       </c>
       <c r="Q51" t="n">
         <v>87.45</v>
       </c>
       <c r="R51" t="n">
-        <v>5.88</v>
+        <v>9.27</v>
       </c>
       <c r="S51" t="n">
         <v>-12.81</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>8.52</v>
+        <v>13.14</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>153.6</v>
+        <v>168.6</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-6.27</v>
+        <v>2.88</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>16.76</v>
+        <v>14.99</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>317.75</v>
+        <v>349.5</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5420,13 +5420,13 @@
         <v>390.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>311.75</v>
+        <v>308</v>
       </c>
       <c r="R54" t="n">
         <v>7.5</v>
       </c>
       <c r="S54" t="n">
-        <v>-14.18</v>
+        <v>-15.21</v>
       </c>
       <c r="T54" t="n">
         <v>14274.02</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>-7.92</v>
+        <v>1.28</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>152</v>
+        <v>153.1</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>3.03</v>
+        <v>3.78</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5563,22 +5563,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="N56" t="n">
-        <v>15.99</v>
+        <v>18.45</v>
       </c>
       <c r="O56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P56" t="n">
-        <v>332.5</v>
+        <v>338</v>
       </c>
       <c r="Q56" t="n">
         <v>283.75</v>
       </c>
       <c r="R56" t="n">
-        <v>16.87</v>
+        <v>18.8</v>
       </c>
       <c r="S56" t="n">
         <v>-0.26</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>15.99</v>
+        <v>18.45</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>46.08</v>
+        <v>47.2</v>
       </c>
       <c r="N57" t="n">
-        <v>2.67</v>
+        <v>5.17</v>
       </c>
       <c r="O57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P57" t="n">
         <v>48.36</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>2.67</v>
+        <v>5.17</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>395.25</v>
+        <v>406.75</v>
       </c>
       <c r="N58" t="n">
-        <v>22.18</v>
+        <v>25.73</v>
       </c>
       <c r="O58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P58" t="n">
-        <v>402.75</v>
+        <v>406.75</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>24.5</v>
+        <v>25.73</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>22.18</v>
+        <v>25.73</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,25 +5770,25 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>243</v>
+        <v>241.4</v>
       </c>
       <c r="N59" t="n">
-        <v>-1.58</v>
+        <v>-2.23</v>
       </c>
       <c r="O59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P59" t="n">
         <v>249</v>
       </c>
       <c r="Q59" t="n">
-        <v>238.7</v>
+        <v>238.4</v>
       </c>
       <c r="R59" t="n">
         <v>0.85</v>
       </c>
       <c r="S59" t="n">
-        <v>-3.32</v>
+        <v>-3.44</v>
       </c>
       <c r="T59" t="n">
         <v>14274.02</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-1.58</v>
+        <v>-2.23</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5839,13 +5839,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>107.7</v>
+        <v>106.3</v>
       </c>
       <c r="N60" t="n">
-        <v>2.87</v>
+        <v>1.53</v>
       </c>
       <c r="O60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P60" t="n">
         <v>116.3</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2.87</v>
+        <v>1.53</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>22.14</v>
+        <v>22.08</v>
       </c>
       <c r="N61" t="n">
-        <v>6.24</v>
+        <v>5.95</v>
       </c>
       <c r="O61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P61" t="n">
         <v>22.54</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>6.24</v>
+        <v>5.95</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>152</v>
+        <v>153.1</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6021,7 +6021,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.99</v>
+        <v>-0.27</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>142.7</v>
+        <v>145</v>
       </c>
       <c r="N63" t="n">
-        <v>5.86</v>
+        <v>7.57</v>
       </c>
       <c r="O63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P63" t="n">
         <v>147</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>5.86</v>
+        <v>7.57</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>12.45</v>
+        <v>12.9</v>
       </c>
       <c r="M64" t="n">
         <v>8.949999999999999</v>
@@ -6209,28 +6209,37 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>19.54</v>
+        <v>19.67</v>
       </c>
       <c r="N65" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S65" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="T65" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U65" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V65" t="n">
         <v>0</v>
       </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>14274.02</v>
+      <c r="W65" t="n">
+        <v>0.67</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6269,28 +6278,37 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>8.130000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="N66" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="R66" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="T66" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U66" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V66" t="n">
         <v>0</v>
       </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>14274.02</v>
+      <c r="W66" t="n">
+        <v>-0.62</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -6335,24 +6353,93 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="T67" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U67" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V67" t="n">
         <v>0</v>
       </c>
-      <c r="P67" t="n">
-        <v>202.3</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>202.3</v>
-      </c>
-      <c r="R67" t="n">
+      <c r="W67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="n">
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ISLEM-000067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>IPEKE</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="G68" t="n">
+        <v>102.41</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="N68" t="n">
         <v>0</v>
       </c>
-      <c r="T67" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y67" t="inlineStr">
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.08.2026 22:12:23</t>
+          <t>25.08.2026 10:51:35</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>26.58</v>
+        <v>25.98</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-3.9</v>
+        <v>-6.07</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>42.24</v>
+        <v>42.32</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-28.6</v>
+        <v>-28.47</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>169.8</v>
+        <v>168.1</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-11.05</v>
+        <v>-11.94</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.98</v>
+        <v>11.95</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.98</v>
+        <v>6.64</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>92.65000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>18.48</v>
+        <v>13.43</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>18.96</v>
+        <v>18.38</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>18.4</v>
+        <v>17.93</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-31.5</v>
+        <v>-33.25</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-25.71</v>
+        <v>-27.98</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>34.2</v>
+        <v>35.04</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-26.13</v>
+        <v>-24.32</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>16.22</v>
+        <v>16.24</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-63.14</v>
+        <v>-63.09</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.12</v>
+        <v>7.16</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-14.11</v>
+        <v>-13.63</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>22.4</v>
+        <v>23.56</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-81.48999999999999</v>
+        <v>-80.53</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>170.8</v>
+        <v>170.6</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>39.89</v>
+        <v>39.72</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>26.48</v>
+        <v>26.74</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>51.75</v>
+        <v>53.24</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>64.09999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-0.54</v>
+        <v>-7.68</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>133.5</v>
+        <v>131.5</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>77.25</v>
+        <v>77.3</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>77.2</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-24.02</v>
+        <v>-24.36</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-19.95</v>
+        <v>-19.9</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-22.93</v>
+        <v>-21.49</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17.44</v>
+        <v>16.82</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-7.18</v>
+        <v>-10.48</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.4</v>
+        <v>6.39</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-8.960000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-37.22</v>
+        <v>-37.42</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-14.65</v>
+        <v>-16.16</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>32.5</v>
+        <v>34.56</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4522.5</v>
+        <v>4490</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-11.27</v>
+        <v>-11.9</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.95</v>
+        <v>18.05</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>95.5</v>
+        <v>97.05</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>1.49</v>
+        <v>3.13</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>19.24</v>
+        <v>19.07</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.75</v>
+        <v>-4.6</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.57</v>
+        <v>16.73</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>5.27</v>
+        <v>6.29</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.54</v>
+        <v>4.91</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-9.380000000000001</v>
+        <v>-2</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-11.62</v>
+        <v>-12.61</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>64.09999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-21.46</v>
+        <v>-27.09</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-16.32</v>
+        <v>-10.26</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54.55</v>
+        <v>54.8</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3683,13 +3683,13 @@
         <v>24</v>
       </c>
       <c r="P33" t="n">
-        <v>55.3</v>
+        <v>57.45</v>
       </c>
       <c r="Q33" t="n">
         <v>42.4</v>
       </c>
       <c r="R33" t="n">
-        <v>9.289999999999999</v>
+        <v>13.54</v>
       </c>
       <c r="S33" t="n">
         <v>-16.21</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>13.48</v>
+        <v>14</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.609999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.76</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.7</v>
+        <v>21.06</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>40.62</v>
+        <v>43.07</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>219.5</v>
+        <v>220.7</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.15</v>
+        <v>6.24</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-66.08</v>
+        <v>-65.58</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>301</v>
+        <v>300.5</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.69</v>
+        <v>-8.84</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>82.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>17.44</v>
+        <v>16.82</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-8.16</v>
+        <v>-11.43</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>349.5</v>
+        <v>354</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>15.69</v>
+        <v>17.18</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>24.66</v>
+        <v>25.38</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-7.5</v>
+        <v>-4.8</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>133.6</v>
+        <v>122.5</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.98</v>
+        <v>11.95</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-11.32</v>
+        <v>-11.55</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4676,13 +4676,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>-15.28</v>
+        <v>-16.1</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>83.2</v>
+        <v>77.95</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4756,13 +4756,13 @@
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>79.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-11.33</v>
+        <v>-13.44</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-2.69</v>
+        <v>-8.83</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.7</v>
+        <v>21.06</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>19.03</v>
+        <v>21.1</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.56</v>
+        <v>22.8</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>8.460000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-10.28</v>
+        <v>-9.57</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>107.8</v>
+        <v>107.7</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5168,13 +5168,13 @@
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>109.6</v>
+        <v>112.5</v>
       </c>
       <c r="Q51" t="n">
         <v>87.45</v>
       </c>
       <c r="R51" t="n">
-        <v>9.27</v>
+        <v>12.16</v>
       </c>
       <c r="S51" t="n">
         <v>-12.81</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>13.14</v>
+        <v>13.04</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>168.6</v>
+        <v>155.5</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>2.88</v>
+        <v>-5.11</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>26</v>
+        <v>26.08</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>14.99</v>
+        <v>15.35</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>349.5</v>
+        <v>354</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>153.1</v>
+        <v>156.4</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>3.78</v>
+        <v>6.01</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5563,22 +5563,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="N56" t="n">
-        <v>18.45</v>
+        <v>16.7</v>
       </c>
       <c r="O56" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P56" t="n">
-        <v>338</v>
+        <v>342.5</v>
       </c>
       <c r="Q56" t="n">
         <v>283.75</v>
       </c>
       <c r="R56" t="n">
-        <v>18.8</v>
+        <v>20.39</v>
       </c>
       <c r="S56" t="n">
         <v>-0.26</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>18.45</v>
+        <v>16.7</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,22 +5632,22 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>47.2</v>
+        <v>48.12</v>
       </c>
       <c r="N57" t="n">
-        <v>5.17</v>
+        <v>7.22</v>
       </c>
       <c r="O57" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P57" t="n">
-        <v>48.36</v>
+        <v>48.6</v>
       </c>
       <c r="Q57" t="n">
         <v>43.64</v>
       </c>
       <c r="R57" t="n">
-        <v>7.75</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S57" t="n">
         <v>-2.76</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>5.17</v>
+        <v>7.22</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>406.75</v>
+        <v>394</v>
       </c>
       <c r="N58" t="n">
-        <v>25.73</v>
+        <v>21.79</v>
       </c>
       <c r="O58" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P58" t="n">
-        <v>406.75</v>
+        <v>407.5</v>
       </c>
       <c r="Q58" t="n">
         <v>323.5</v>
       </c>
       <c r="R58" t="n">
-        <v>25.73</v>
+        <v>25.97</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>25.73</v>
+        <v>21.79</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>241.4</v>
+        <v>239.7</v>
       </c>
       <c r="N59" t="n">
-        <v>-2.23</v>
+        <v>-2.92</v>
       </c>
       <c r="O59" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P59" t="n">
         <v>249</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-2.23</v>
+        <v>-2.92</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5839,13 +5839,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>106.3</v>
+        <v>103</v>
       </c>
       <c r="N60" t="n">
-        <v>1.53</v>
+        <v>-1.62</v>
       </c>
       <c r="O60" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P60" t="n">
         <v>116.3</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.53</v>
+        <v>-1.62</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5908,22 +5908,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>22.08</v>
+        <v>22.62</v>
       </c>
       <c r="N61" t="n">
-        <v>5.95</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O61" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P61" t="n">
-        <v>22.54</v>
+        <v>22.78</v>
       </c>
       <c r="Q61" t="n">
         <v>20.82</v>
       </c>
       <c r="R61" t="n">
-        <v>8.16</v>
+        <v>9.31</v>
       </c>
       <c r="S61" t="n">
         <v>-0.1</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>5.95</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>153.1</v>
+        <v>156.4</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6021,7 +6021,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.27</v>
+        <v>1.88</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6060,22 +6060,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>145</v>
+        <v>147.6</v>
       </c>
       <c r="N63" t="n">
-        <v>7.57</v>
+        <v>9.5</v>
       </c>
       <c r="O63" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P63" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q63" t="n">
         <v>130.2</v>
       </c>
       <c r="R63" t="n">
-        <v>9.050000000000001</v>
+        <v>11.28</v>
       </c>
       <c r="S63" t="n">
         <v>-3.41</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>7.57</v>
+        <v>9.5</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>12.9</v>
+        <v>12.63</v>
       </c>
       <c r="M64" t="n">
         <v>8.949999999999999</v>
@@ -6209,22 +6209,22 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>19.67</v>
+        <v>20.12</v>
       </c>
       <c r="N65" t="n">
-        <v>0.67</v>
+        <v>2.97</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P65" t="n">
-        <v>19.79</v>
+        <v>20.5</v>
       </c>
       <c r="Q65" t="n">
         <v>19.08</v>
       </c>
       <c r="R65" t="n">
-        <v>1.28</v>
+        <v>4.91</v>
       </c>
       <c r="S65" t="n">
         <v>-2.35</v>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.67</v>
+        <v>2.97</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6274,29 +6274,40 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-0.62</v>
+        <v>7.66</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-5.04</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P66" t="n">
         <v>8.449999999999999</v>
       </c>
       <c r="Q66" t="n">
-        <v>8.039999999999999</v>
+        <v>7.71</v>
       </c>
       <c r="R66" t="n">
         <v>3.94</v>
       </c>
       <c r="S66" t="n">
-        <v>-1.11</v>
+        <v>-5.17</v>
       </c>
       <c r="T66" t="n">
         <v>14274.02</v>
@@ -6308,7 +6319,10 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>-0.62</v>
+        <v>-5.04</v>
+      </c>
+      <c r="X66" t="n">
+        <v>-0.78</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -6347,22 +6361,22 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>202.3</v>
+        <v>225.8</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>11.62</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>208.9</v>
+        <v>227.1</v>
       </c>
       <c r="Q67" t="n">
         <v>192.3</v>
       </c>
       <c r="R67" t="n">
-        <v>3.26</v>
+        <v>12.26</v>
       </c>
       <c r="S67" t="n">
         <v>-4.94</v>
@@ -6377,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>11.62</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -6416,28 +6430,37 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>107.8</v>
+        <v>107.7</v>
       </c>
       <c r="N68" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4</v>
+      </c>
+      <c r="P68" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="T68" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U68" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V68" t="n">
         <v>0</v>
       </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>107.8</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>107.8</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>14274.02</v>
+      <c r="W68" t="n">
+        <v>-0.09</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.08.2026 10:51:35</t>
+          <t>27.08.2026 09:25:28</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y68"/>
+  <dimension ref="A1:Y71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.98</v>
+        <v>25.46</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-6.07</v>
+        <v>-7.95</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>42.32</v>
+        <v>41.42</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-28.47</v>
+        <v>-29.99</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>168.1</v>
+        <v>166.8</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1332,13 +1332,13 @@
         <v>209.1</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>167.6</v>
+        <v>166</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>4.08</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-16.58</v>
+        <v>-17.37</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>13744.64</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-11.94</v>
+        <v>-12.62</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.95</v>
+        <v>11.88</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>11.6</v>
+        <v>11.52</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-9.869999999999999</v>
+        <v>-10.49</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>88.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>13.43</v>
+        <v>13.68</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>18.38</v>
+        <v>17.76</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>17.93</v>
+        <v>17.7</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-33.25</v>
+        <v>-34.1</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-27.98</v>
+        <v>-30.41</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>35.04</v>
+        <v>38.12</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-24.32</v>
+        <v>-17.67</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>16.24</v>
+        <v>15.91</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-63.09</v>
+        <v>-63.84</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.16</v>
+        <v>7.22</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-13.63</v>
+        <v>-12.91</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>23.56</v>
+        <v>23.6</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-80.53</v>
+        <v>-80.5</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>170.6</v>
+        <v>167.5</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>39.72</v>
+        <v>37.18</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>26.74</v>
+        <v>25.98</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>53.24</v>
+        <v>48.88</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>59.5</v>
+        <v>57.9</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-7.68</v>
+        <v>-10.16</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>131.5</v>
+        <v>132.6</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>77.3</v>
+        <v>78</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>76.84999999999999</v>
+        <v>76.45</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-24.36</v>
+        <v>-24.75</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-19.9</v>
+        <v>-19.17</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-21.49</v>
+        <v>-20.87</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.82</v>
+        <v>16.7</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-10.48</v>
+        <v>-11.12</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.39</v>
+        <v>6.32</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-9.1</v>
+        <v>-10.1</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-16.16</v>
+        <v>-18.69</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>34.56</v>
+        <v>33.1</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4490</v>
+        <v>4402.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-11.9</v>
+        <v>-13.62</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.05</v>
+        <v>18.25</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>97.05</v>
+        <v>97.95</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>3.13</v>
+        <v>4.09</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>19.07</v>
+        <v>18.9</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.6</v>
+        <v>-5.45</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>6.29</v>
+        <v>6.42</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.91</v>
+        <v>5.02</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-2</v>
+        <v>0.2</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-12.61</v>
+        <v>-9.73</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>59.5</v>
+        <v>57.9</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-27.09</v>
+        <v>-29.05</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-10.26</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54.8</v>
+        <v>54.45</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>13.27</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.67</v>
+        <v>8.9</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.76</v>
+        <v>4.46</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>21.06</v>
+        <v>20.62</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3849,13 +3849,13 @@
         <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>21.72</v>
+        <v>21.86</v>
       </c>
       <c r="Q35" t="n">
         <v>13.9</v>
       </c>
       <c r="R35" t="n">
-        <v>40.13</v>
+        <v>41.03</v>
       </c>
       <c r="S35" t="n">
         <v>-10.32</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>43.07</v>
+        <v>40.08</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>220.7</v>
+        <v>221.2</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.24</v>
+        <v>6.26</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-65.58</v>
+        <v>-65.47</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>300.5</v>
+        <v>308.5</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.84</v>
+        <v>-6.42</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>81.09999999999999</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.82</v>
+        <v>16.7</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-11.43</v>
+        <v>-12.06</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>354</v>
+        <v>379.5</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4344,13 +4344,13 @@
         <v>6</v>
       </c>
       <c r="P41" t="n">
-        <v>390.5</v>
+        <v>391</v>
       </c>
       <c r="Q41" t="n">
         <v>262.25</v>
       </c>
       <c r="R41" t="n">
-        <v>22.8</v>
+        <v>22.96</v>
       </c>
       <c r="S41" t="n">
         <v>-17.53</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>17.18</v>
+        <v>25.62</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.38</v>
+        <v>25.48</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-4.8</v>
+        <v>-4.43</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>122.5</v>
+        <v>125</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.95</v>
+        <v>11.88</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4593,13 +4593,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.6</v>
+        <v>11.52</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-18.42</v>
+        <v>-18.99</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-11.55</v>
+        <v>-12.07</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>52.8</v>
+        <v>51</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4676,13 +4676,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>-16.1</v>
+        <v>-17.42</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>77.95</v>
+        <v>78.95</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4756,13 +4756,13 @@
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>77.90000000000001</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-13.44</v>
+        <v>-14.28</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-8.83</v>
+        <v>-7.66</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.630000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-7.4</v>
+        <v>-6.65</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>21.06</v>
+        <v>20.62</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4919,13 +4919,13 @@
         <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>21.72</v>
+        <v>21.86</v>
       </c>
       <c r="Q48" t="n">
         <v>16.16</v>
       </c>
       <c r="R48" t="n">
-        <v>18.69</v>
+        <v>19.45</v>
       </c>
       <c r="S48" t="n">
         <v>-11.69</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>21.1</v>
+        <v>18.57</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.8</v>
+        <v>22.46</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>9.619999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.57</v>
+        <v>-10.99</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>107.7</v>
+        <v>110.5</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>13.04</v>
+        <v>15.97</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>155.5</v>
+        <v>151.2</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-5.11</v>
+        <v>-7.74</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>26.08</v>
+        <v>24.52</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>15.35</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>354</v>
+        <v>379.5</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5417,13 +5417,13 @@
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>390.5</v>
+        <v>391</v>
       </c>
       <c r="Q54" t="n">
         <v>308</v>
       </c>
       <c r="R54" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="S54" t="n">
         <v>-15.21</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>2.58</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>156.4</v>
+        <v>164</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>6.01</v>
+        <v>11.16</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5559,14 +5559,25 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="n">
+        <v>46259</v>
+      </c>
+      <c r="J56" t="n">
+        <v>319</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>332</v>
-      </c>
-      <c r="N56" t="n">
-        <v>16.7</v>
+        <v>320.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>12.13</v>
       </c>
       <c r="O56" t="n">
         <v>18</v>
@@ -5593,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>16.7</v>
+        <v>12.13</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5632,13 +5643,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>48.12</v>
+        <v>47.1</v>
       </c>
       <c r="N57" t="n">
-        <v>7.22</v>
+        <v>4.95</v>
       </c>
       <c r="O57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P57" t="n">
         <v>48.6</v>
@@ -5662,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>7.22</v>
+        <v>4.95</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5697,14 +5708,25 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="n">
+        <v>46259</v>
+      </c>
+      <c r="J58" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>394</v>
-      </c>
-      <c r="N58" t="n">
-        <v>21.79</v>
+        <v>380</v>
+      </c>
+      <c r="M58" t="n">
+        <v>15.53</v>
       </c>
       <c r="O58" t="n">
         <v>18</v>
@@ -5731,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>21.79</v>
+        <v>15.53</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5770,25 +5792,25 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>239.7</v>
+        <v>245.8</v>
       </c>
       <c r="N59" t="n">
-        <v>-2.92</v>
+        <v>-0.45</v>
       </c>
       <c r="O59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P59" t="n">
         <v>249</v>
       </c>
       <c r="Q59" t="n">
-        <v>238.4</v>
+        <v>237.9</v>
       </c>
       <c r="R59" t="n">
         <v>0.85</v>
       </c>
       <c r="S59" t="n">
-        <v>-3.44</v>
+        <v>-3.65</v>
       </c>
       <c r="T59" t="n">
         <v>14274.02</v>
@@ -5800,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-2.92</v>
+        <v>-0.45</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5839,13 +5861,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>103</v>
+        <v>108.5</v>
       </c>
       <c r="N60" t="n">
-        <v>-1.62</v>
+        <v>3.63</v>
       </c>
       <c r="O60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P60" t="n">
         <v>116.3</v>
@@ -5869,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>-1.62</v>
+        <v>3.63</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5908,22 +5930,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>22.62</v>
+        <v>23.12</v>
       </c>
       <c r="N61" t="n">
-        <v>8.539999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="O61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P61" t="n">
-        <v>22.78</v>
+        <v>23.2</v>
       </c>
       <c r="Q61" t="n">
         <v>20.82</v>
       </c>
       <c r="R61" t="n">
-        <v>9.31</v>
+        <v>11.32</v>
       </c>
       <c r="S61" t="n">
         <v>-0.1</v>
@@ -5938,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>8.539999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -5988,7 +6010,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>156.4</v>
+        <v>164</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -5997,13 +6019,13 @@
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>163</v>
+        <v>164.1</v>
       </c>
       <c r="Q62" t="n">
         <v>146.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0.87</v>
+        <v>1.55</v>
       </c>
       <c r="S62" t="n">
         <v>-9.34</v>
@@ -6021,7 +6043,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>1.88</v>
+        <v>6.83</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6060,22 +6082,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>147.6</v>
+        <v>165</v>
       </c>
       <c r="N63" t="n">
-        <v>9.5</v>
+        <v>22.4</v>
       </c>
       <c r="O63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P63" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="Q63" t="n">
         <v>130.2</v>
       </c>
       <c r="R63" t="n">
-        <v>11.28</v>
+        <v>22.4</v>
       </c>
       <c r="S63" t="n">
         <v>-3.41</v>
@@ -6090,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>9.5</v>
+        <v>22.4</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6140,7 +6162,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>12.63</v>
+        <v>12.92</v>
       </c>
       <c r="M64" t="n">
         <v>8.949999999999999</v>
@@ -6209,13 +6231,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>20.12</v>
+        <v>19.94</v>
       </c>
       <c r="N65" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="O65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P65" t="n">
         <v>20.5</v>
@@ -6239,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6289,7 +6311,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.66</v>
+        <v>7.75</v>
       </c>
       <c r="M66" t="n">
         <v>-5.04</v>
@@ -6301,13 +6323,13 @@
         <v>8.449999999999999</v>
       </c>
       <c r="Q66" t="n">
-        <v>7.71</v>
+        <v>7.6</v>
       </c>
       <c r="R66" t="n">
         <v>3.94</v>
       </c>
       <c r="S66" t="n">
-        <v>-5.17</v>
+        <v>-6.52</v>
       </c>
       <c r="T66" t="n">
         <v>14274.02</v>
@@ -6322,7 +6344,7 @@
         <v>-5.04</v>
       </c>
       <c r="X66" t="n">
-        <v>-0.78</v>
+        <v>0.39</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -6361,22 +6383,22 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>225.8</v>
+        <v>242</v>
       </c>
       <c r="N67" t="n">
-        <v>11.62</v>
+        <v>19.62</v>
       </c>
       <c r="O67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>227.1</v>
+        <v>242</v>
       </c>
       <c r="Q67" t="n">
         <v>192.3</v>
       </c>
       <c r="R67" t="n">
-        <v>12.26</v>
+        <v>19.62</v>
       </c>
       <c r="S67" t="n">
         <v>-4.94</v>
@@ -6391,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>11.62</v>
+        <v>19.62</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -6430,25 +6452,25 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>107.7</v>
+        <v>110.5</v>
       </c>
       <c r="N68" t="n">
-        <v>-0.09</v>
+        <v>2.5</v>
       </c>
       <c r="O68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P68" t="n">
         <v>112.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>107.3</v>
+        <v>104.2</v>
       </c>
       <c r="R68" t="n">
         <v>4.36</v>
       </c>
       <c r="S68" t="n">
-        <v>-0.46</v>
+        <v>-3.34</v>
       </c>
       <c r="T68" t="n">
         <v>14274.02</v>
@@ -6460,9 +6482,189 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>-0.09</v>
+        <v>2.5</v>
       </c>
       <c r="Y68" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ISLEM-000068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CEOEM</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="G69" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ISLEM-000069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="G70" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ISLEM-000070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TNZTP</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="G71" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y71" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27.08.2026 09:25:28</t>
+          <t>28.08.2026 09:11:59</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:Y74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.46</v>
+        <v>25.68</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-7.95</v>
+        <v>-7.16</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>41.42</v>
+        <v>41.8</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-29.99</v>
+        <v>-29.34</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>166.8</v>
+        <v>166.6</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-12.62</v>
+        <v>-12.73</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.88</v>
+        <v>11.83</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>13.68</v>
+        <v>12.66</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>17.76</v>
+        <v>17.6</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-34.1</v>
+        <v>-34.48</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-30.41</v>
+        <v>-31.03</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>38.12</v>
+        <v>41.92</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-17.67</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>15.91</v>
+        <v>15.73</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-63.84</v>
+        <v>-64.25</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.22</v>
+        <v>7.29</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-12.91</v>
+        <v>-12.06</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>23.6</v>
+        <v>23.92</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-80.5</v>
+        <v>-80.23</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>167.5</v>
+        <v>162</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>37.18</v>
+        <v>32.68</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>25.98</v>
+        <v>25.48</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>48.88</v>
+        <v>46.02</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>57.9</v>
+        <v>56.15</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-10.16</v>
+        <v>-12.88</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>132.6</v>
+        <v>133</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>78</v>
+        <v>77.45</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-19.17</v>
+        <v>-19.74</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-20.87</v>
+        <v>-22.11</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-11.12</v>
+        <v>-12.19</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.32</v>
+        <v>6.24</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-10.1</v>
+        <v>-11.24</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-37.42</v>
+        <v>-37.01</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4402.5</v>
+        <v>4305</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-13.62</v>
+        <v>-15.53</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.25</v>
+        <v>18.41</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>97.95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.09</v>
+        <v>3.72</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>18.9</v>
+        <v>18.53</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3188,13 +3188,13 @@
         <v>22.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>18.74</v>
+        <v>18.47</v>
       </c>
       <c r="R27" t="n">
         <v>7.03</v>
       </c>
       <c r="S27" t="n">
-        <v>-10.93</v>
+        <v>-12.21</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-5.45</v>
+        <v>-7.3</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.75</v>
+        <v>16.4</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>6.42</v>
+        <v>4.19</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.09</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.73</v>
+        <v>-10.13</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>57.9</v>
+        <v>56.15</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-29.05</v>
+        <v>-31.2</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54.45</v>
+        <v>54.3</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>13.27</v>
+        <v>12.96</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.9</v>
+        <v>8.65</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>4.46</v>
+        <v>1.53</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.62</v>
+        <v>20.3</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>40.08</v>
+        <v>37.91</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>221.2</v>
+        <v>219.5</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>1.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.26</v>
+        <v>6.29</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-65.47</v>
+        <v>-65.31</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>308.5</v>
+        <v>307.25</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-6.42</v>
+        <v>-6.8</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>81.84999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-12.06</v>
+        <v>-13.11</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>379.5</v>
+        <v>381.5</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>25.62</v>
+        <v>26.28</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.48</v>
+        <v>24.9</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-4.43</v>
+        <v>-6.6</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>125</v>
+        <v>126.7</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.88</v>
+        <v>11.83</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-12.07</v>
+        <v>-12.44</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>78.95</v>
+        <v>77.5</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-7.66</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>8.699999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-6.65</v>
+        <v>-2.68</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.62</v>
+        <v>20.3</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>18.57</v>
+        <v>16.73</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.46</v>
+        <v>22.08</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>7.98</v>
+        <v>6.15</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-10.99</v>
+        <v>-9.93</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>110.5</v>
+        <v>108.5</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>15.97</v>
+        <v>13.87</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>151.2</v>
+        <v>151.6</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-7.74</v>
+        <v>-7.49</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>24.52</v>
+        <v>25.56</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>8.449999999999999</v>
+        <v>13.05</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>379.5</v>
+        <v>381.5</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>9.970000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>164</v>
+        <v>168.5</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5500,13 +5500,13 @@
         <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>167.2</v>
+        <v>169.3</v>
       </c>
       <c r="Q55" t="n">
         <v>142.6</v>
       </c>
       <c r="R55" t="n">
-        <v>7.66</v>
+        <v>9.01</v>
       </c>
       <c r="S55" t="n">
         <v>-8.18</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>11.16</v>
+        <v>14.21</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>320.5</v>
+        <v>319.5</v>
       </c>
       <c r="M56" t="n">
         <v>12.13</v>
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>47.1</v>
+        <v>46.98</v>
       </c>
       <c r="N57" t="n">
-        <v>4.95</v>
+        <v>4.68</v>
       </c>
       <c r="O57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P57" t="n">
         <v>48.6</v>
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>4.95</v>
+        <v>4.68</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>380</v>
+        <v>380.75</v>
       </c>
       <c r="M58" t="n">
         <v>15.53</v>
@@ -5735,13 +5735,13 @@
         <v>407.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>323.5</v>
+        <v>323.75</v>
       </c>
       <c r="R58" t="n">
         <v>25.97</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T58" t="n">
         <v>14274.02</v>
@@ -5792,22 +5792,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>245.8</v>
+        <v>248.6</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q59" t="n">
         <v>237.9</v>
       </c>
       <c r="R59" t="n">
-        <v>0.85</v>
+        <v>2.07</v>
       </c>
       <c r="S59" t="n">
         <v>-3.65</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>108.5</v>
+        <v>109.6</v>
       </c>
       <c r="N60" t="n">
-        <v>3.63</v>
+        <v>4.68</v>
       </c>
       <c r="O60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P60" t="n">
         <v>116.3</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>3.63</v>
+        <v>4.68</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5930,22 +5930,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>23.12</v>
+        <v>23.02</v>
       </c>
       <c r="N61" t="n">
-        <v>10.94</v>
+        <v>10.46</v>
       </c>
       <c r="O61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P61" t="n">
-        <v>23.2</v>
+        <v>23.28</v>
       </c>
       <c r="Q61" t="n">
         <v>20.82</v>
       </c>
       <c r="R61" t="n">
-        <v>11.32</v>
+        <v>11.71</v>
       </c>
       <c r="S61" t="n">
         <v>-0.1</v>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>10.94</v>
+        <v>10.46</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>164</v>
+        <v>168.5</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6019,13 +6019,13 @@
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>164.1</v>
+        <v>169.3</v>
       </c>
       <c r="Q62" t="n">
         <v>146.5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.55</v>
+        <v>4.76</v>
       </c>
       <c r="S62" t="n">
         <v>-9.34</v>
@@ -6043,7 +6043,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>6.83</v>
+        <v>9.76</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6082,22 +6082,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="N63" t="n">
-        <v>22.4</v>
+        <v>33.53</v>
       </c>
       <c r="O63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P63" t="n">
-        <v>165</v>
+        <v>181.5</v>
       </c>
       <c r="Q63" t="n">
         <v>130.2</v>
       </c>
       <c r="R63" t="n">
-        <v>22.4</v>
+        <v>34.64</v>
       </c>
       <c r="S63" t="n">
         <v>-3.41</v>
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>22.4</v>
+        <v>33.53</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
       <c r="M64" t="n">
         <v>8.949999999999999</v>
@@ -6231,25 +6231,25 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>19.94</v>
+        <v>19</v>
       </c>
       <c r="N65" t="n">
-        <v>2.05</v>
+        <v>-2.76</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P65" t="n">
         <v>20.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>19.08</v>
+        <v>18.84</v>
       </c>
       <c r="R65" t="n">
         <v>4.91</v>
       </c>
       <c r="S65" t="n">
-        <v>-2.35</v>
+        <v>-3.58</v>
       </c>
       <c r="T65" t="n">
         <v>14274.02</v>
@@ -6261,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>2.05</v>
+        <v>-2.76</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.75</v>
+        <v>7.7</v>
       </c>
       <c r="M66" t="n">
         <v>-5.04</v>
@@ -6344,7 +6344,7 @@
         <v>-5.04</v>
       </c>
       <c r="X66" t="n">
-        <v>0.39</v>
+        <v>-0.26</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="N67" t="n">
-        <v>19.62</v>
+        <v>27.53</v>
       </c>
       <c r="O67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P67" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="Q67" t="n">
         <v>192.3</v>
       </c>
       <c r="R67" t="n">
-        <v>19.62</v>
+        <v>27.53</v>
       </c>
       <c r="S67" t="n">
         <v>-4.94</v>
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>19.62</v>
+        <v>27.53</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -6452,13 +6452,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>110.5</v>
+        <v>108.5</v>
       </c>
       <c r="N68" t="n">
-        <v>2.5</v>
+        <v>0.65</v>
       </c>
       <c r="O68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P68" t="n">
         <v>112.5</v>
@@ -6482,7 +6482,7 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>2.5</v>
+        <v>0.65</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -6521,28 +6521,37 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>25.48</v>
+        <v>24.9</v>
       </c>
       <c r="N69" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="T69" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U69" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V69" t="n">
         <v>0</v>
       </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>25.48</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>25.48</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>14274.02</v>
+      <c r="W69" t="n">
+        <v>-2.28</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -6581,22 +6590,22 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>180.7</v>
+        <v>185</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>180.7</v>
+        <v>187.5</v>
       </c>
       <c r="Q70" t="n">
         <v>180.7</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -6604,6 +6613,15 @@
       <c r="T70" t="n">
         <v>14274.02</v>
       </c>
+      <c r="U70" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>2.38</v>
+      </c>
       <c r="Y70" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
@@ -6641,30 +6659,219 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>29.88</v>
+        <v>30.28</v>
       </c>
       <c r="N71" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S71" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="T71" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U71" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V71" t="n">
         <v>0</v>
       </c>
-      <c r="O71" t="n">
+      <c r="W71" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ISLEM-000071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>349</v>
+      </c>
+      <c r="G72" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>349</v>
+      </c>
+      <c r="N72" t="n">
         <v>0</v>
       </c>
-      <c r="P71" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="R71" t="n">
+      <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="n">
+      <c r="P72" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>349</v>
+      </c>
+      <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="T71" t="n">
-        <v>14274.02</v>
-      </c>
-      <c r="Y71" t="inlineStr">
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ISLEM-000072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FLAP</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>11</v>
+      </c>
+      <c r="G73" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>11</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>11</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ISLEM-000073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KENT</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y74" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28.08.2026 09:11:59</t>
+          <t>31.08.2026 20:49:06</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.68</v>
+        <v>25.3</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-7.16</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>41.8</v>
+        <v>40.72</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-29.34</v>
+        <v>-31.17</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>166.6</v>
+        <v>163.8</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1332,13 +1332,13 @@
         <v>209.1</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>166</v>
+        <v>163.4</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>4.08</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-17.37</v>
+        <v>-18.67</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>13744.64</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-12.73</v>
+        <v>-14.2</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.83</v>
+        <v>11.51</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>11.52</v>
+        <v>11.38</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-10.49</v>
+        <v>-11.58</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>88.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>12.66</v>
+        <v>7.42</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>17.6</v>
+        <v>17.62</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>17.6</v>
+        <v>17.48</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-34.48</v>
+        <v>-34.92</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-31.03</v>
+        <v>-30.96</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>41.92</v>
+        <v>42.18</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-9.460000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>15.73</v>
+        <v>16.76</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-64.25</v>
+        <v>-61.91</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.29</v>
+        <v>7.06</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-12.06</v>
+        <v>-14.84</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>23.92</v>
+        <v>24.02</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-80.23</v>
+        <v>-80.15000000000001</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>162</v>
+        <v>165.6</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>32.68</v>
+        <v>35.63</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>25.48</v>
+        <v>24.56</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>46.02</v>
+        <v>40.74</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>56.15</v>
+        <v>57.75</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-12.88</v>
+        <v>-10.4</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>133</v>
+        <v>133.8</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>77.45</v>
+        <v>75.7</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>76.45</v>
+        <v>75.25</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-24.75</v>
+        <v>-25.94</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-19.74</v>
+        <v>-21.55</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-22.11</v>
+        <v>-21.07</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>16.5</v>
+        <v>15.65</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-12.19</v>
+        <v>-16.71</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.24</v>
+        <v>6.04</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-11.24</v>
+        <v>-14.08</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-37.01</v>
+        <v>-38.24</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-18.69</v>
+        <v>-22.73</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4305</v>
+        <v>4190</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4182.5</v>
+        <v>4175</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-22.04</v>
+        <v>-22.18</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-15.53</v>
+        <v>-17.79</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.41</v>
+        <v>19.52</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>97.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>3.72</v>
+        <v>2.55</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>18.53</v>
+        <v>17.84</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3188,13 +3188,13 @@
         <v>22.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>18.47</v>
+        <v>17.77</v>
       </c>
       <c r="R27" t="n">
         <v>7.03</v>
       </c>
       <c r="S27" t="n">
-        <v>-12.21</v>
+        <v>-15.54</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.3</v>
+        <v>-10.76</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.4</v>
+        <v>16.45</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>4.19</v>
+        <v>4.51</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>-1.4</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.050000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-10.13</v>
+        <v>-11.72</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>56.15</v>
+        <v>57.75</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-31.2</v>
+        <v>-29.24</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-8.949999999999999</v>
+        <v>-10.53</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54.3</v>
+        <v>52.9</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>12.96</v>
+        <v>10.05</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.65</v>
+        <v>8.77</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1.53</v>
+        <v>2.93</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.3</v>
+        <v>19.08</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>37.91</v>
+        <v>29.62</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>219.5</v>
+        <v>216.1</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.62</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.29</v>
+        <v>6.24</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-65.31</v>
+        <v>-65.58</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>307.25</v>
+        <v>302.25</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-6.8</v>
+        <v>-8.31</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>83.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16.5</v>
+        <v>15.65</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-13.11</v>
+        <v>-17.59</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>381.5</v>
+        <v>344.75</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4344,13 +4344,13 @@
         <v>6</v>
       </c>
       <c r="P41" t="n">
-        <v>391</v>
+        <v>399.5</v>
       </c>
       <c r="Q41" t="n">
         <v>262.25</v>
       </c>
       <c r="R41" t="n">
-        <v>22.96</v>
+        <v>25.63</v>
       </c>
       <c r="S41" t="n">
         <v>-17.53</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>26.28</v>
+        <v>14.12</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>24.9</v>
+        <v>25.14</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>126.7</v>
+        <v>114.1</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.83</v>
+        <v>11.51</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4593,13 +4593,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.52</v>
+        <v>11.38</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-18.99</v>
+        <v>-19.97</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-12.44</v>
+        <v>-14.8</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>50.5</v>
+        <v>47.66</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4676,13 +4676,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>50</v>
+        <v>47.66</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>-17.42</v>
+        <v>-21.29</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>77.5</v>
+        <v>75.2</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4756,13 +4756,13 @@
         <v>93.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>77.15000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="R46" t="n">
         <v>3.89</v>
       </c>
       <c r="S46" t="n">
-        <v>-14.28</v>
+        <v>-16.44</v>
       </c>
       <c r="T46" t="n">
         <v>14274.02</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.359999999999999</v>
+        <v>-12.05</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.07</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>-4.99</v>
@@ -4860,7 +4860,7 @@
         <v>-4.99</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.68</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20.3</v>
+        <v>19.08</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>16.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>22.08</v>
+        <v>21.8</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>6.15</v>
+        <v>4.81</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5088,13 +5088,13 @@
         <v>3.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R50" t="n">
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>-17.51</v>
+        <v>-19.19</v>
       </c>
       <c r="T50" t="n">
         <v>14274.02</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.93</v>
+        <v>-13.48</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>108.5</v>
+        <v>106.9</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>13.87</v>
+        <v>12.2</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>151.6</v>
+        <v>153.1</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-7.49</v>
+        <v>-6.58</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>25.56</v>
+        <v>24.96</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>13.05</v>
+        <v>10.39</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>381.5</v>
+        <v>344.75</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5417,13 +5417,13 @@
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>391</v>
+        <v>399.5</v>
       </c>
       <c r="Q54" t="n">
         <v>308</v>
       </c>
       <c r="R54" t="n">
-        <v>7.64</v>
+        <v>9.98</v>
       </c>
       <c r="S54" t="n">
         <v>-15.21</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>10.55</v>
+        <v>-0.1</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>168.5</v>
+        <v>145</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5500,13 +5500,13 @@
         <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>169.3</v>
+        <v>171</v>
       </c>
       <c r="Q55" t="n">
         <v>142.6</v>
       </c>
       <c r="R55" t="n">
-        <v>9.01</v>
+        <v>10.11</v>
       </c>
       <c r="S55" t="n">
         <v>-8.18</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>14.21</v>
+        <v>-1.71</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>319.5</v>
+        <v>335</v>
       </c>
       <c r="M56" t="n">
         <v>12.13</v>
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>46.98</v>
+        <v>47.16</v>
       </c>
       <c r="N57" t="n">
-        <v>4.68</v>
+        <v>5.08</v>
       </c>
       <c r="O57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P57" t="n">
         <v>48.6</v>
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>4.68</v>
+        <v>5.08</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>380.75</v>
+        <v>400.25</v>
       </c>
       <c r="M58" t="n">
         <v>15.53</v>
@@ -5792,13 +5792,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>248.6</v>
+        <v>241.4</v>
       </c>
       <c r="N59" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.23</v>
       </c>
       <c r="O59" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P59" t="n">
         <v>252</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.23</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>109.6</v>
+        <v>108.3</v>
       </c>
       <c r="N60" t="n">
-        <v>4.68</v>
+        <v>3.44</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
         <v>116.3</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>4.68</v>
+        <v>3.44</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5930,13 +5930,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>23.02</v>
+        <v>22.48</v>
       </c>
       <c r="N61" t="n">
-        <v>10.46</v>
+        <v>7.87</v>
       </c>
       <c r="O61" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P61" t="n">
         <v>23.28</v>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>10.46</v>
+        <v>7.87</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>168.5</v>
+        <v>145</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6019,16 +6019,16 @@
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>169.3</v>
+        <v>171</v>
       </c>
       <c r="Q62" t="n">
-        <v>146.5</v>
+        <v>144.9</v>
       </c>
       <c r="R62" t="n">
-        <v>4.76</v>
+        <v>5.82</v>
       </c>
       <c r="S62" t="n">
-        <v>-9.34</v>
+        <v>-10.33</v>
       </c>
       <c r="T62" t="n">
         <v>14274.02</v>
@@ -6043,7 +6043,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>9.76</v>
+        <v>-5.55</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6082,22 +6082,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>180</v>
+        <v>190.5</v>
       </c>
       <c r="N63" t="n">
-        <v>33.53</v>
+        <v>41.32</v>
       </c>
       <c r="O63" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P63" t="n">
-        <v>181.5</v>
+        <v>197.5</v>
       </c>
       <c r="Q63" t="n">
         <v>130.2</v>
       </c>
       <c r="R63" t="n">
-        <v>34.64</v>
+        <v>46.51</v>
       </c>
       <c r="S63" t="n">
         <v>-3.41</v>
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>33.53</v>
+        <v>41.32</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>12.93</v>
+        <v>13.05</v>
       </c>
       <c r="M64" t="n">
         <v>8.949999999999999</v>
@@ -6231,25 +6231,25 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N65" t="n">
-        <v>-2.76</v>
+        <v>-2.25</v>
       </c>
       <c r="O65" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P65" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>18.84</v>
+        <v>18.63</v>
       </c>
       <c r="R65" t="n">
-        <v>4.91</v>
+        <v>6.96</v>
       </c>
       <c r="S65" t="n">
-        <v>-3.58</v>
+        <v>-4.66</v>
       </c>
       <c r="T65" t="n">
         <v>14274.02</v>
@@ -6261,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>-2.76</v>
+        <v>-2.25</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.7</v>
+        <v>6.85</v>
       </c>
       <c r="M66" t="n">
         <v>-5.04</v>
@@ -6323,13 +6323,13 @@
         <v>8.449999999999999</v>
       </c>
       <c r="Q66" t="n">
-        <v>7.6</v>
+        <v>6.85</v>
       </c>
       <c r="R66" t="n">
         <v>3.94</v>
       </c>
       <c r="S66" t="n">
-        <v>-6.52</v>
+        <v>-15.74</v>
       </c>
       <c r="T66" t="n">
         <v>14274.02</v>
@@ -6344,7 +6344,7 @@
         <v>-5.04</v>
       </c>
       <c r="X66" t="n">
-        <v>-0.26</v>
+        <v>-11.27</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -6379,26 +6379,37 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="J67" t="n">
+        <v>241.2</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>KAR STOP</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>258</v>
-      </c>
-      <c r="N67" t="n">
-        <v>27.53</v>
+        <v>241.2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>19.23</v>
       </c>
       <c r="O67" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P67" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="Q67" t="n">
         <v>192.3</v>
       </c>
       <c r="R67" t="n">
-        <v>27.53</v>
+        <v>32.48</v>
       </c>
       <c r="S67" t="n">
         <v>-4.94</v>
@@ -6413,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>27.53</v>
+        <v>19.23</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -6452,13 +6463,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>108.5</v>
+        <v>106.9</v>
       </c>
       <c r="N68" t="n">
-        <v>0.65</v>
+        <v>-0.83</v>
       </c>
       <c r="O68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P68" t="n">
         <v>112.5</v>
@@ -6482,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0.65</v>
+        <v>-0.83</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -6521,25 +6532,25 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>24.9</v>
+        <v>25.14</v>
       </c>
       <c r="N69" t="n">
-        <v>-2.28</v>
+        <v>-1.33</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P69" t="n">
         <v>26.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>24.86</v>
+        <v>24.7</v>
       </c>
       <c r="R69" t="n">
         <v>2.43</v>
       </c>
       <c r="S69" t="n">
-        <v>-2.43</v>
+        <v>-3.06</v>
       </c>
       <c r="T69" t="n">
         <v>14274.02</v>
@@ -6551,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>-2.28</v>
+        <v>-1.33</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -6590,22 +6601,22 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>185</v>
+        <v>187.5</v>
       </c>
       <c r="N70" t="n">
-        <v>2.38</v>
+        <v>3.76</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P70" t="n">
-        <v>187.5</v>
+        <v>192.9</v>
       </c>
       <c r="Q70" t="n">
         <v>180.7</v>
       </c>
       <c r="R70" t="n">
-        <v>3.76</v>
+        <v>6.75</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -6620,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>2.38</v>
+        <v>3.76</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
@@ -6659,25 +6670,25 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>30.28</v>
+        <v>32</v>
       </c>
       <c r="N71" t="n">
-        <v>1.34</v>
+        <v>7.1</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P71" t="n">
-        <v>30.3</v>
+        <v>32.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>29.84</v>
+        <v>29.04</v>
       </c>
       <c r="R71" t="n">
-        <v>1.41</v>
+        <v>8.77</v>
       </c>
       <c r="S71" t="n">
-        <v>-0.13</v>
+        <v>-2.81</v>
       </c>
       <c r="T71" t="n">
         <v>14274.02</v>
@@ -6689,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.34</v>
+        <v>7.1</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -6724,32 +6735,55 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="J72" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>349</v>
-      </c>
-      <c r="N72" t="n">
+        <v>325.75</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4</v>
+      </c>
+      <c r="P72" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>317</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S72" t="n">
+        <v>-9.17</v>
+      </c>
+      <c r="T72" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U72" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V72" t="n">
         <v>0</v>
       </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>349</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>349</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>14274.02</v>
+      <c r="W72" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-1.75</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -6788,28 +6822,37 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4</v>
+      </c>
+      <c r="P73" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="R73" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="S73" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="T73" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U73" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V73" t="n">
         <v>0</v>
       </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>11</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>14274.02</v>
+      <c r="W73" t="n">
+        <v>1</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -6844,34 +6887,237 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="J74" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>403.5</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
+        <v>369.25</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-5</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P74" t="n">
         <v>403.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>403.5</v>
+        <v>369.25</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
       <c r="S74" t="n">
+        <v>-8.49</v>
+      </c>
+      <c r="T74" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U74" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V74" t="n">
         <v>0</v>
       </c>
-      <c r="T74" t="n">
-        <v>14274.02</v>
+      <c r="W74" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-3.67</v>
       </c>
       <c r="Y74" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ISLEM-000074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CANTE</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ISLEM-000075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CWENE</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ISLEM-000076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>YGGYO</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>233.9</v>
+      </c>
+      <c r="G77" t="n">
+        <v>222.2</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>233.9</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>233.9</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>233.9</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y77" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde .xlsx
+++ b/Yüzde .xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.08.2026 20:49:06</t>
+          <t>07.09.2026 23:08:18</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>25.3</v>
+        <v>23.1</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>-4.62</v>
@@ -1191,7 +1191,7 @@
         <v>-4.61</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>-8.529999999999999</v>
+        <v>-16.49</v>
       </c>
       <c r="Y2" s="9" t="n"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>40.72</v>
+        <v>39.68</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>-4.98</v>
@@ -1251,13 +1251,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <v>39.38</v>
+        <v>37.6</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>3.44</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>-36.75</v>
+        <v>-39.61</v>
       </c>
       <c r="T3" s="5" t="n">
         <v>13744.64</v>
@@ -1272,7 +1272,7 @@
         <v>-4.97</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>-31.17</v>
+        <v>-32.93</v>
       </c>
       <c r="Y3" s="6" t="n"/>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>163.8</v>
+        <v>163.5</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>-4.98</v>
@@ -1332,13 +1332,13 @@
         <v>209.1</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>163.4</v>
+        <v>159.1</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>4.08</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-18.67</v>
+        <v>-20.81</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>13744.64</v>
@@ -1353,7 +1353,7 @@
         <v>-10.76</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>-14.2</v>
+        <v>-14.35</v>
       </c>
       <c r="Y4" s="9" t="n"/>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11.51</v>
+        <v>11.64</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>8.470000000000001</v>
@@ -1413,13 +1413,13 @@
         <v>15.4</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>11.38</v>
+        <v>11.14</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>19.66</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-11.58</v>
+        <v>-13.44</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13743.5</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5.9</v>
+        <v>4.62</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>27.27</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>84</v>
+        <v>81.5</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>-4.98</v>
@@ -1592,7 +1592,7 @@
         <v>-10.43</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>7.42</v>
+        <v>4.22</v>
       </c>
       <c r="Y7" s="6" t="n"/>
     </row>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>17.62</v>
+        <v>16.97</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>-4.99</v>
@@ -1652,13 +1652,13 @@
         <v>28.92</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>17.48</v>
+        <v>16.5</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>7.67</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>-34.92</v>
+        <v>-38.57</v>
       </c>
       <c r="T8" s="8" t="n">
         <v>13938.48</v>
@@ -1673,7 +1673,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>-30.96</v>
+        <v>-33.5</v>
       </c>
       <c r="Y8" s="9" t="n"/>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>42.18</v>
+        <v>49.92</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>-5.01</v>
@@ -1730,13 +1730,13 @@
         <v>8</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>52.2</v>
+        <v>54.35</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>32.14</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>7.1</v>
+        <v>11.51</v>
       </c>
       <c r="S9" s="5" t="n">
         <v>-34.06</v>
@@ -1754,7 +1754,7 @@
         <v>-5.66</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>-8.9</v>
+        <v>7.82</v>
       </c>
       <c r="Y9" s="6" t="n"/>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>16.76</v>
+        <v>15.76</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>-5.01</v>
@@ -1835,7 +1835,7 @@
         <v>-4.51</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>-61.91</v>
+        <v>-64.18000000000001</v>
       </c>
       <c r="Y10" s="9" t="n"/>
     </row>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.06</v>
+        <v>7.32</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>-5.04</v>
@@ -1916,7 +1916,7 @@
         <v>-3.53</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-14.84</v>
+        <v>-11.7</v>
       </c>
       <c r="Y11" s="6" t="n"/>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>24.02</v>
+        <v>23</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>-5.02</v>
@@ -1997,7 +1997,7 @@
         <v>-4.52</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>-80.15000000000001</v>
+        <v>-80.98999999999999</v>
       </c>
       <c r="Y12" s="9" t="n"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>165.6</v>
+        <v>161.1</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>-4.98</v>
@@ -2078,7 +2078,7 @@
         <v>-7.8</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>35.63</v>
+        <v>31.94</v>
       </c>
       <c r="Y13" s="6" t="n"/>
     </row>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>24.56</v>
+        <v>24.42</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>-5.01</v>
@@ -2159,7 +2159,7 @@
         <v>-3.69</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>40.74</v>
+        <v>39.94</v>
       </c>
       <c r="Y14" s="9" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>57.75</v>
+        <v>53.95</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>-5.01</v>
@@ -2219,13 +2219,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>50.35</v>
+        <v>50.05</v>
       </c>
       <c r="R15" s="5" t="n">
         <v>31.02</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>-25.79</v>
+        <v>-26.23</v>
       </c>
       <c r="T15" s="5" t="n">
         <v>14734.5</v>
@@ -2240,7 +2240,7 @@
         <v>-4.98</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>-10.4</v>
+        <v>-16.29</v>
       </c>
       <c r="Y15" s="6" t="n"/>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>133.8</v>
+        <v>104</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>6.13</v>
@@ -2300,13 +2300,13 @@
         <v>145.5</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>120.4</v>
+        <v>95.45</v>
       </c>
       <c r="R16" s="8" t="n">
         <v>17.34</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>-2.9</v>
+        <v>-23.02</v>
       </c>
       <c r="T16" s="8" t="n">
         <v>14729.65</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>75.7</v>
+        <v>70.95</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>-5.02</v>
@@ -2379,13 +2379,13 @@
         <v>108.6</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>75.25</v>
+        <v>70.3</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>-25.94</v>
+        <v>-30.81</v>
       </c>
       <c r="T17" s="5" t="n">
         <v>14539.61</v>
@@ -2400,7 +2400,7 @@
         <v>-3.59</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>-21.55</v>
+        <v>-26.48</v>
       </c>
       <c r="Y17" s="6" t="n"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>3.82</v>
+        <v>3.57</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>-4.91</v>
@@ -2460,13 +2460,13 @@
         <v>5.24</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>3.67</v>
+        <v>3.51</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>2.95</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>-27.9</v>
+        <v>-31.04</v>
       </c>
       <c r="T18" s="8" t="n">
         <v>14539.61</v>
@@ -2481,7 +2481,7 @@
         <v>-3.48</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>-21.07</v>
+        <v>-26.24</v>
       </c>
       <c r="Y18" s="9" t="n"/>
     </row>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>15.65</v>
+        <v>14.82</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>-5.01</v>
@@ -2541,13 +2541,13 @@
         <v>20.64</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>15.48</v>
+        <v>14.52</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>4.35</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>-21.74</v>
+        <v>-26.59</v>
       </c>
       <c r="T19" s="5" t="n">
         <v>14331.21</v>
@@ -2562,7 +2562,7 @@
         <v>-4.61</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>-16.71</v>
+        <v>-21.13</v>
       </c>
       <c r="Y19" s="6" t="n"/>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>6.04</v>
+        <v>5.77</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>-5</v>
@@ -2622,13 +2622,13 @@
         <v>7.76</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>4.86</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>-18.92</v>
+        <v>-23.38</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>14259.75</v>
@@ -2643,7 +2643,7 @@
         <v>-5.1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>-14.08</v>
+        <v>-17.92</v>
       </c>
       <c r="Y20" s="9" t="n"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>-5.05</v>
@@ -2703,13 +2703,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="R21" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>-42.72</v>
+        <v>-46.41</v>
       </c>
       <c r="T21" s="5" t="n">
         <v>14259.75</v>
@@ -2724,7 +2724,7 @@
         <v>-5.15</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>-38.24</v>
+        <v>-41.31</v>
       </c>
       <c r="Y21" s="6" t="n"/>
     </row>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>-3.41</v>
@@ -2784,13 +2784,13 @@
         <v>2.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>2.44</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>-25.85</v>
+        <v>-27.8</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>14259.75</v>
@@ -2805,7 +2805,7 @@
         <v>-3.51</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>-22.73</v>
+        <v>-20.71</v>
       </c>
       <c r="Y22" s="9" t="n"/>
     </row>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>33.1</v>
+        <v>39.6</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>11.4</v>
@@ -2862,13 +2862,13 @@
         <v>24</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>35.48</v>
+        <v>40.06</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>26.96</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>18.27</v>
+        <v>33.53</v>
       </c>
       <c r="S23" s="5" t="n">
         <v>-10.13</v>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4190</v>
+        <v>4002.5</v>
       </c>
       <c r="M24" t="n">
         <v>-5</v>
@@ -2942,13 +2942,13 @@
         <v>5725</v>
       </c>
       <c r="Q24" t="n">
-        <v>4175</v>
+        <v>3950</v>
       </c>
       <c r="R24" t="n">
         <v>6.71</v>
       </c>
       <c r="S24" t="n">
-        <v>-22.18</v>
+        <v>-26.37</v>
       </c>
       <c r="T24" t="n">
         <v>14274.02</v>
@@ -2963,7 +2963,7 @@
         <v>-5</v>
       </c>
       <c r="X24" t="n">
-        <v>-17.79</v>
+        <v>-21.47</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>19.52</v>
+        <v>19.14</v>
       </c>
       <c r="M25" t="n">
         <v>13.69</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>96.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-5</v>
@@ -3126,7 +3126,7 @@
         <v>-5</v>
       </c>
       <c r="X26" t="n">
-        <v>2.55</v>
+        <v>-0.74</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>17.84</v>
+        <v>18.79</v>
       </c>
       <c r="M27" t="n">
         <v>-4.99</v>
@@ -3188,13 +3188,13 @@
         <v>22.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>17.77</v>
+        <v>17.74</v>
       </c>
       <c r="R27" t="n">
         <v>7.03</v>
       </c>
       <c r="S27" t="n">
-        <v>-15.54</v>
+        <v>-15.68</v>
       </c>
       <c r="T27" t="n">
         <v>14274.02</v>
@@ -3209,7 +3209,7 @@
         <v>-4.99</v>
       </c>
       <c r="X27" t="n">
-        <v>-10.76</v>
+        <v>-6</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>16.45</v>
+        <v>16.82</v>
       </c>
       <c r="M28" t="n">
         <v>-5.01</v>
@@ -3292,7 +3292,7 @@
         <v>-5.01</v>
       </c>
       <c r="X28" t="n">
-        <v>4.51</v>
+        <v>6.86</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.94</v>
+        <v>4.72</v>
       </c>
       <c r="M29" t="n">
         <v>-4.93</v>
@@ -3375,7 +3375,7 @@
         <v>-4.93</v>
       </c>
       <c r="X29" t="n">
-        <v>-1.4</v>
+        <v>-5.79</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.890000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="M30" t="n">
         <v>-5</v>
@@ -3458,7 +3458,7 @@
         <v>-5</v>
       </c>
       <c r="X30" t="n">
-        <v>-11.72</v>
+        <v>-12.12</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>57.75</v>
+        <v>53.95</v>
       </c>
       <c r="M31" t="n">
         <v>-4.99</v>
@@ -3520,13 +3520,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>50.35</v>
+        <v>50.05</v>
       </c>
       <c r="R31" t="n">
         <v>3.49</v>
       </c>
       <c r="S31" t="n">
-        <v>-41.39</v>
+        <v>-41.73</v>
       </c>
       <c r="T31" t="n">
         <v>14274.02</v>
@@ -3541,7 +3541,7 @@
         <v>-4.99</v>
       </c>
       <c r="X31" t="n">
-        <v>-29.24</v>
+        <v>-33.89</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="M32" t="n">
         <v>-5</v>
@@ -3624,7 +3624,7 @@
         <v>-5</v>
       </c>
       <c r="X32" t="n">
-        <v>-10.53</v>
+        <v>-15</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>52.9</v>
+        <v>51.3</v>
       </c>
       <c r="M33" t="n">
         <v>-5</v>
@@ -3707,7 +3707,7 @@
         <v>-5</v>
       </c>
       <c r="X33" t="n">
-        <v>10.05</v>
+        <v>6.72</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.77</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M34" t="n">
         <v>-5.02</v>
@@ -3790,7 +3790,7 @@
         <v>-5.02</v>
       </c>
       <c r="X34" t="n">
-        <v>2.93</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>19.08</v>
+        <v>13.96</v>
       </c>
       <c r="M35" t="n">
         <v>-5.03</v>
@@ -3852,13 +3852,13 @@
         <v>21.86</v>
       </c>
       <c r="Q35" t="n">
-        <v>13.9</v>
+        <v>13.17</v>
       </c>
       <c r="R35" t="n">
         <v>41.03</v>
       </c>
       <c r="S35" t="n">
-        <v>-10.32</v>
+        <v>-15.03</v>
       </c>
       <c r="T35" t="n">
         <v>14274.02</v>
@@ -3873,7 +3873,7 @@
         <v>-5.03</v>
       </c>
       <c r="X35" t="n">
-        <v>29.62</v>
+        <v>-5.16</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>216.1</v>
+        <v>215</v>
       </c>
       <c r="M36" t="n">
         <v>-5</v>
@@ -3935,13 +3935,13 @@
         <v>231.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>214.1</v>
+        <v>207.6</v>
       </c>
       <c r="R36" t="n">
         <v>0.96</v>
       </c>
       <c r="S36" t="n">
-        <v>-6.47</v>
+        <v>-9.31</v>
       </c>
       <c r="T36" t="n">
         <v>14274.02</v>
@@ -3956,7 +3956,7 @@
         <v>-5</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.62</v>
+        <v>-1.13</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="M37" t="n">
         <v>-4.98</v>
@@ -4039,7 +4039,7 @@
         <v>-4.98</v>
       </c>
       <c r="X37" t="n">
-        <v>-65.58</v>
+        <v>-65.53</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>302.25</v>
+        <v>296.75</v>
       </c>
       <c r="M38" t="n">
         <v>-5</v>
@@ -4101,13 +4101,13 @@
         <v>355.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>295.25</v>
+        <v>289.25</v>
       </c>
       <c r="R38" t="n">
         <v>2.45</v>
       </c>
       <c r="S38" t="n">
-        <v>-14.91</v>
+        <v>-16.64</v>
       </c>
       <c r="T38" t="n">
         <v>14274.02</v>
@@ -4122,7 +4122,7 @@
         <v>-5</v>
       </c>
       <c r="X38" t="n">
-        <v>-8.31</v>
+        <v>-9.98</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>79.40000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="M39" t="n">
         <v>16.19</v>
@@ -4184,13 +4184,13 @@
         <v>117.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>78.09999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="R39" t="n">
         <v>30.77</v>
       </c>
       <c r="S39" t="n">
-        <v>-13.08</v>
+        <v>-14.58</v>
       </c>
       <c r="T39" t="n">
         <v>14274.02</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>15.65</v>
+        <v>14.82</v>
       </c>
       <c r="M40" t="n">
         <v>-5</v>
@@ -4264,13 +4264,13 @@
         <v>20.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>15.48</v>
+        <v>14.52</v>
       </c>
       <c r="R40" t="n">
         <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>-22.56</v>
+        <v>-27.36</v>
       </c>
       <c r="T40" t="n">
         <v>14274.02</v>
@@ -4285,7 +4285,7 @@
         <v>-5</v>
       </c>
       <c r="X40" t="n">
-        <v>-17.59</v>
+        <v>-21.96</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>344.75</v>
+        <v>297</v>
       </c>
       <c r="M41" t="n">
         <v>-5</v>
@@ -4368,7 +4368,7 @@
         <v>-5</v>
       </c>
       <c r="X41" t="n">
-        <v>14.12</v>
+        <v>-1.69</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>25.14</v>
+        <v>24.2</v>
       </c>
       <c r="M42" t="n">
         <v>-4.99</v>
@@ -4451,7 +4451,7 @@
         <v>-4.99</v>
       </c>
       <c r="X42" t="n">
-        <v>-5.7</v>
+        <v>-9.23</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>114.1</v>
+        <v>111.4</v>
       </c>
       <c r="M43" t="n">
         <v>12.18</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>11.51</v>
+        <v>11.64</v>
       </c>
       <c r="M44" t="n">
         <v>-4.99</v>
@@ -4593,13 +4593,13 @@
         <v>14.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.38</v>
+        <v>11.14</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-19.97</v>
+        <v>-21.66</v>
       </c>
       <c r="T44" t="n">
         <v>14274.02</v>
@@ -4614,7 +4614,7 @@
         <v>-4.99</v>
       </c>
       <c r="X44" t="n">
-        <v>-14.8</v>
+        <v>-13.84</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>47.66</v>
+        <v>51.35</v>
       </c>
       <c r="M45" t="n">
         <v>16.6</v>
@@ -4676,13 +4676,13 @@
         <v>79</v>
       </c>
       <c r="Q45" t="n">
-        <v>47.66</v>
+        <v>42.88</v>
       </c>
       <c r="R45" t="n">
         <v>30.47</v>
       </c>
       <c r="S45" t="n">
-        <v>-21.29</v>
+        <v>-29.18</v>
       </c>
       <c r="T45" t="n">
         <v>14274.02</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>75.2</v>
+        <v>79.45</v>
       </c>
       <c r="M46" t="n">
         <v>-5</v>
@@ -4777,7 +4777,7 @@
         <v>-5</v>
       </c>
       <c r="X46" t="n">
-        <v>-12.05</v>
+        <v>-7.08</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>19.08</v>
+        <v>13.96</v>
       </c>
       <c r="M48" t="n">
         <v>-4.97</v>
@@ -4922,13 +4922,13 @@
         <v>21.86</v>
       </c>
       <c r="Q48" t="n">
-        <v>16.16</v>
+        <v>13.17</v>
       </c>
       <c r="R48" t="n">
         <v>19.45</v>
       </c>
       <c r="S48" t="n">
-        <v>-11.69</v>
+        <v>-28.03</v>
       </c>
       <c r="T48" t="n">
         <v>14274.02</v>
@@ -4943,7 +4943,7 @@
         <v>-4.97</v>
       </c>
       <c r="X48" t="n">
-        <v>9.720000000000001</v>
+        <v>-19.72</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>21.8</v>
+        <v>23.18</v>
       </c>
       <c r="M49" t="n">
         <v>-5.02</v>
@@ -5026,7 +5026,7 @@
         <v>-5.02</v>
       </c>
       <c r="X49" t="n">
-        <v>4.81</v>
+        <v>11.44</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="M50" t="n">
         <v>-5.05</v>
@@ -5088,13 +5088,13 @@
         <v>3.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R50" t="n">
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>-19.19</v>
+        <v>-19.87</v>
       </c>
       <c r="T50" t="n">
         <v>14274.02</v>
@@ -5109,7 +5109,7 @@
         <v>-5.05</v>
       </c>
       <c r="X50" t="n">
-        <v>-13.48</v>
+        <v>-14.54</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>106.9</v>
+        <v>105</v>
       </c>
       <c r="M51" t="n">
         <v>-5</v>
@@ -5192,7 +5192,7 @@
         <v>-5</v>
       </c>
       <c r="X51" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>153.1</v>
+        <v>137.5</v>
       </c>
       <c r="M52" t="n">
         <v>-5</v>
@@ -5254,13 +5254,13 @@
         <v>175</v>
       </c>
       <c r="Q52" t="n">
-        <v>147.5</v>
+        <v>135</v>
       </c>
       <c r="R52" t="n">
         <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>-14.49</v>
+        <v>-21.74</v>
       </c>
       <c r="T52" t="n">
         <v>14274.02</v>
@@ -5275,7 +5275,7 @@
         <v>-5</v>
       </c>
       <c r="X52" t="n">
-        <v>-6.58</v>
+        <v>-16.1</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>24.96</v>
+        <v>23.74</v>
       </c>
       <c r="M53" t="n">
         <v>-5</v>
@@ -5358,7 +5358,7 @@
         <v>-5</v>
       </c>
       <c r="X53" t="n">
-        <v>10.39</v>
+        <v>5</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>344.75</v>
+        <v>297</v>
       </c>
       <c r="M54" t="n">
         <v>-5</v>
@@ -5420,13 +5420,13 @@
         <v>399.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="R54" t="n">
         <v>9.98</v>
       </c>
       <c r="S54" t="n">
-        <v>-15.21</v>
+        <v>-22.09</v>
       </c>
       <c r="T54" t="n">
         <v>14274.02</v>
@@ -5441,7 +5441,7 @@
         <v>-5</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.1</v>
+        <v>-13.94</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>145</v>
+        <v>119.9</v>
       </c>
       <c r="M55" t="n">
         <v>-5</v>
@@ -5503,13 +5503,13 @@
         <v>171</v>
       </c>
       <c r="Q55" t="n">
-        <v>142.6</v>
+        <v>109.9</v>
       </c>
       <c r="R55" t="n">
         <v>10.11</v>
       </c>
       <c r="S55" t="n">
-        <v>-8.18</v>
+        <v>-29.23</v>
       </c>
       <c r="T55" t="n">
         <v>14274.02</v>
@@ -5524,7 +5524,7 @@
         <v>-5</v>
       </c>
       <c r="X55" t="n">
-        <v>-1.71</v>
+        <v>-18.73</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>335</v>
+        <v>318.5</v>
       </c>
       <c r="M56" t="n">
         <v>12.13</v>
@@ -5583,13 +5583,13 @@
         <v>18</v>
       </c>
       <c r="P56" t="n">
-        <v>342.5</v>
+        <v>346.5</v>
       </c>
       <c r="Q56" t="n">
         <v>283.75</v>
       </c>
       <c r="R56" t="n">
-        <v>20.39</v>
+        <v>21.79</v>
       </c>
       <c r="S56" t="n">
         <v>-0.26</v>
@@ -5643,22 +5643,22 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>47.16</v>
+        <v>48.86</v>
       </c>
       <c r="N57" t="n">
-        <v>5.08</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="P57" t="n">
-        <v>48.6</v>
+        <v>49.9</v>
       </c>
       <c r="Q57" t="n">
         <v>43.64</v>
       </c>
       <c r="R57" t="n">
-        <v>8.289999999999999</v>
+        <v>11.19</v>
       </c>
       <c r="S57" t="n">
         <v>-2.76</v>
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>5.08</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>400.25</v>
+        <v>394.25</v>
       </c>
       <c r="M58" t="n">
         <v>15.53</v>
@@ -5732,13 +5732,13 @@
         <v>18</v>
       </c>
       <c r="P58" t="n">
-        <v>407.5</v>
+        <v>417.25</v>
       </c>
       <c r="Q58" t="n">
         <v>323.75</v>
       </c>
       <c r="R58" t="n">
-        <v>25.97</v>
+        <v>28.98</v>
       </c>
       <c r="S58" t="n">
         <v>0.08</v>
@@ -5792,25 +5792,25 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>241.4</v>
+        <v>248.8</v>
       </c>
       <c r="N59" t="n">
-        <v>-2.23</v>
+        <v>0.77</v>
       </c>
       <c r="O59" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="P59" t="n">
         <v>252</v>
       </c>
       <c r="Q59" t="n">
-        <v>237.9</v>
+        <v>236.3</v>
       </c>
       <c r="R59" t="n">
         <v>2.07</v>
       </c>
       <c r="S59" t="n">
-        <v>-3.65</v>
+        <v>-4.29</v>
       </c>
       <c r="T59" t="n">
         <v>14274.02</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>-2.23</v>
+        <v>0.77</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>108.3</v>
+        <v>113.9</v>
       </c>
       <c r="N60" t="n">
-        <v>3.44</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="P60" t="n">
         <v>116.3</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>3.44</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -5930,13 +5930,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>22.48</v>
+        <v>21.88</v>
       </c>
       <c r="N61" t="n">
-        <v>7.87</v>
+        <v>4.99</v>
       </c>
       <c r="O61" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="P61" t="n">
         <v>23.28</v>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>7.87</v>
+        <v>4.99</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>145</v>
+        <v>119.9</v>
       </c>
       <c r="M62" t="n">
         <v>-5</v>
@@ -6022,13 +6022,13 @@
         <v>171</v>
       </c>
       <c r="Q62" t="n">
-        <v>144.9</v>
+        <v>109.9</v>
       </c>
       <c r="R62" t="n">
         <v>5.82</v>
       </c>
       <c r="S62" t="n">
-        <v>-10.33</v>
+        <v>-31.99</v>
       </c>
       <c r="T62" t="n">
         <v>14274.02</v>
@@ -6043,7 +6043,7 @@
         <v>-5</v>
       </c>
       <c r="X62" t="n">
-        <v>-5.55</v>
+        <v>-21.9</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6082,22 +6082,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>190.5</v>
+        <v>214.8</v>
       </c>
       <c r="N63" t="n">
-        <v>41.32</v>
+        <v>59.35</v>
       </c>
       <c r="O63" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="P63" t="n">
-        <v>197.5</v>
+        <v>214.8</v>
       </c>
       <c r="Q63" t="n">
         <v>130.2</v>
       </c>
       <c r="R63" t="n">
-        <v>46.51</v>
+        <v>59.35</v>
       </c>
       <c r="S63" t="n">
         <v>-3.41</v>
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>41.32</v>
+        <v>59.35</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>13.05</v>
+        <v>11.89</v>
       </c>
       <c r="M64" t="n">
         <v>8.949999999999999</v>
@@ -6174,13 +6174,13 @@
         <v>14</v>
       </c>
       <c r="Q64" t="n">
-        <v>11.17</v>
+        <v>10.7</v>
       </c>
       <c r="R64" t="n">
         <v>24.11</v>
       </c>
       <c r="S64" t="n">
-        <v>-0.98</v>
+        <v>-5.14</v>
       </c>
       <c r="T64" t="n">
         <v>14274.02</v>
@@ -6227,29 +6227,40 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J65" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>19.1</v>
       </c>
-      <c r="N65" t="n">
-        <v>-2.25</v>
+      <c r="M65" t="n">
+        <v>-5.02</v>
       </c>
       <c r="O65" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P65" t="n">
         <v>20.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>18.63</v>
+        <v>18.51</v>
       </c>
       <c r="R65" t="n">
         <v>6.96</v>
       </c>
       <c r="S65" t="n">
-        <v>-4.66</v>
+        <v>-5.27</v>
       </c>
       <c r="T65" t="n">
         <v>14274.02</v>
@@ -6261,7 +6272,10 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>-2.25</v>
+        <v>-5.02</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.91</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6311,7 +6325,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>6.85</v>
+        <v>7.44</v>
       </c>
       <c r="M66" t="n">
         <v>-5.04</v>
@@ -6344,7 +6358,7 @@
         <v>-5.04</v>
       </c>
       <c r="X66" t="n">
-        <v>-11.27</v>
+        <v>-3.63</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -6394,7 +6408,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>241.2</v>
+        <v>142.6</v>
       </c>
       <c r="M67" t="n">
         <v>19.23</v>
@@ -6406,13 +6420,13 @@
         <v>268</v>
       </c>
       <c r="Q67" t="n">
-        <v>192.3</v>
+        <v>142.6</v>
       </c>
       <c r="R67" t="n">
         <v>32.48</v>
       </c>
       <c r="S67" t="n">
-        <v>-4.94</v>
+        <v>-29.51</v>
       </c>
       <c r="T67" t="n">
         <v>14274.02</v>
@@ -6459,29 +6473,40 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J68" t="n">
+        <v>102.41</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="N68" t="n">
-        <v>-0.83</v>
+        <v>105</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-5</v>
       </c>
       <c r="O68" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P68" t="n">
         <v>112.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>104.2</v>
+        <v>101.9</v>
       </c>
       <c r="R68" t="n">
         <v>4.36</v>
       </c>
       <c r="S68" t="n">
-        <v>-3.34</v>
+        <v>-5.47</v>
       </c>
       <c r="T68" t="n">
         <v>14274.02</v>
@@ -6493,7 +6518,10 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>-0.83</v>
+        <v>-5</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2.53</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -6528,29 +6556,40 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J69" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>25.14</v>
-      </c>
-      <c r="N69" t="n">
-        <v>-1.33</v>
+        <v>24.2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-4.98</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P69" t="n">
         <v>26.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>24.7</v>
+        <v>23.7</v>
       </c>
       <c r="R69" t="n">
         <v>2.43</v>
       </c>
       <c r="S69" t="n">
-        <v>-3.06</v>
+        <v>-6.99</v>
       </c>
       <c r="T69" t="n">
         <v>14274.02</v>
@@ -6562,7 +6601,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>-1.33</v>
+        <v>-4.98</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.04</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -6601,22 +6643,22 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187.5</v>
+        <v>195</v>
       </c>
       <c r="N70" t="n">
-        <v>3.76</v>
+        <v>7.91</v>
       </c>
       <c r="O70" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P70" t="n">
-        <v>192.9</v>
+        <v>195.8</v>
       </c>
       <c r="Q70" t="n">
         <v>180.7</v>
       </c>
       <c r="R70" t="n">
-        <v>6.75</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -6631,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>3.76</v>
+        <v>7.91</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
@@ -6670,25 +6712,25 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>32</v>
+        <v>28.82</v>
       </c>
       <c r="N71" t="n">
-        <v>7.1</v>
+        <v>-3.55</v>
       </c>
       <c r="O71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P71" t="n">
         <v>32.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>29.04</v>
+        <v>28.62</v>
       </c>
       <c r="R71" t="n">
         <v>8.77</v>
       </c>
       <c r="S71" t="n">
-        <v>-2.81</v>
+        <v>-4.22</v>
       </c>
       <c r="T71" t="n">
         <v>14274.02</v>
@@ -6700,7 +6742,7 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>7.1</v>
+        <v>-3.55</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -6750,7 +6792,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>325.75</v>
+        <v>301</v>
       </c>
       <c r="M72" t="n">
         <v>-5</v>
@@ -6762,13 +6804,13 @@
         <v>355.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>317</v>
+        <v>289.75</v>
       </c>
       <c r="R72" t="n">
         <v>1.79</v>
       </c>
       <c r="S72" t="n">
-        <v>-9.17</v>
+        <v>-16.98</v>
       </c>
       <c r="T72" t="n">
         <v>14274.02</v>
@@ -6783,7 +6825,7 @@
         <v>-5</v>
       </c>
       <c r="X72" t="n">
-        <v>-1.75</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -6822,22 +6864,22 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>11.11</v>
+        <v>11.39</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>3.55</v>
       </c>
       <c r="O73" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P73" t="n">
-        <v>11.34</v>
+        <v>11.9</v>
       </c>
       <c r="Q73" t="n">
         <v>10.51</v>
       </c>
       <c r="R73" t="n">
-        <v>3.09</v>
+        <v>8.18</v>
       </c>
       <c r="S73" t="n">
         <v>-4.45</v>
@@ -6852,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1</v>
+        <v>3.55</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -6902,7 +6944,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>369.25</v>
+        <v>349.75</v>
       </c>
       <c r="M74" t="n">
         <v>-5</v>
@@ -6914,13 +6956,13 @@
         <v>403.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>369.25</v>
+        <v>339</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>-8.49</v>
+        <v>-15.99</v>
       </c>
       <c r="T74" t="n">
         <v>14274.02</v>
@@ -6935,7 +6977,7 @@
         <v>-5</v>
       </c>
       <c r="X74" t="n">
-        <v>-3.67</v>
+        <v>-8.76</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -6970,32 +7012,55 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="N75" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S75" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="T75" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U75" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V75" t="n">
         <v>0</v>
       </c>
-      <c r="O75" t="n">
+      <c r="W75" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="X75" t="n">
         <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>14274.02</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
@@ -7030,32 +7095,55 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J76" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-5.01</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" t="n">
         <v>37.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>37.5</v>
+        <v>34.4</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
       <c r="S76" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="T76" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U76" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V76" t="n">
         <v>0</v>
       </c>
-      <c r="T76" t="n">
-        <v>14274.02</v>
+      <c r="W76" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="X76" t="n">
+        <v>-10.16</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -7090,34 +7178,237 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>AÇIK</t>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="n">
+        <v>46268</v>
+      </c>
+      <c r="J77" t="n">
+        <v>222.2</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>STOP</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>233.9</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
+        <v>218.2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-5</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P77" t="n">
         <v>233.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>233.9</v>
+        <v>213</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
       <c r="S77" t="n">
+        <v>-8.94</v>
+      </c>
+      <c r="T77" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="U77" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="V77" t="n">
         <v>0</v>
       </c>
-      <c r="T77" t="n">
-        <v>14274.02</v>
+      <c r="W77" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X77" t="n">
+        <v>-1.8</v>
       </c>
       <c r="Y77" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ISLEM-000077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BLCYT</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ZAYIF AL</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ISLEM-000078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KRPLS</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="G79" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ISLEM-000079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>288</v>
+      </c>
+      <c r="G80" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>288</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>288</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>14274.02</v>
+      </c>
+      <c r="Y80" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>
